--- a/BASE DATOS MODO APS.xlsx
+++ b/BASE DATOS MODO APS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanvidalp/Documents/clon carrera funcionaria/carrera-aps-digital/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1686024B-B799-0B48-9525-09AF7DB35285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B112CC2A-96BF-EE4A-90E2-8984ECD6D2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="17820" xr2:uid="{A9505C21-DF7A-114D-A7E6-2CB0B98403BE}"/>
+    <workbookView xWindow="-30240" yWindow="1480" windowWidth="30240" windowHeight="18980" xr2:uid="{A9505C21-DF7A-114D-A7E6-2CB0B98403BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="1357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3095" uniqueCount="927">
   <si>
     <t>RUT</t>
   </si>
@@ -1656,1296 +1656,6 @@
   </si>
   <si>
     <t>INDEFINIDO</t>
-  </si>
-  <si>
-    <t>1980-01-12</t>
-  </si>
-  <si>
-    <t>1987-07-14</t>
-  </si>
-  <si>
-    <t>1986-08-30</t>
-  </si>
-  <si>
-    <t>1966-05-07</t>
-  </si>
-  <si>
-    <t>1983-10-08</t>
-  </si>
-  <si>
-    <t>1964-06-10</t>
-  </si>
-  <si>
-    <t>1985-08-27</t>
-  </si>
-  <si>
-    <t>1986-06-26</t>
-  </si>
-  <si>
-    <t>1988-12-22</t>
-  </si>
-  <si>
-    <t>1992-10-30</t>
-  </si>
-  <si>
-    <t>1996-12-09</t>
-  </si>
-  <si>
-    <t>1985-11-23</t>
-  </si>
-  <si>
-    <t>1995-04-26</t>
-  </si>
-  <si>
-    <t>1981-09-08</t>
-  </si>
-  <si>
-    <t>1982-09-17</t>
-  </si>
-  <si>
-    <t>1994-01-19</t>
-  </si>
-  <si>
-    <t>1977-11-12</t>
-  </si>
-  <si>
-    <t>1985-08-22</t>
-  </si>
-  <si>
-    <t>1999-11-21</t>
-  </si>
-  <si>
-    <t>1999-01-20</t>
-  </si>
-  <si>
-    <t>1992-02-14</t>
-  </si>
-  <si>
-    <t>1970-06-03</t>
-  </si>
-  <si>
-    <t>1968-09-30</t>
-  </si>
-  <si>
-    <t>1976-04-03</t>
-  </si>
-  <si>
-    <t>1981-12-04</t>
-  </si>
-  <si>
-    <t>1985-11-11</t>
-  </si>
-  <si>
-    <t>1978-12-10</t>
-  </si>
-  <si>
-    <t>1984-03-01</t>
-  </si>
-  <si>
-    <t>1976-01-20</t>
-  </si>
-  <si>
-    <t>1987-02-09</t>
-  </si>
-  <si>
-    <t>1991-04-24</t>
-  </si>
-  <si>
-    <t>1979-04-10</t>
-  </si>
-  <si>
-    <t>1966-10-21</t>
-  </si>
-  <si>
-    <t>1993-12-31</t>
-  </si>
-  <si>
-    <t>1979-02-11</t>
-  </si>
-  <si>
-    <t>1979-07-28</t>
-  </si>
-  <si>
-    <t>1972-09-28</t>
-  </si>
-  <si>
-    <t>1991-05-08</t>
-  </si>
-  <si>
-    <t>1996-10-19</t>
-  </si>
-  <si>
-    <t>1983-09-01</t>
-  </si>
-  <si>
-    <t>1981-11-06</t>
-  </si>
-  <si>
-    <t>1992-03-10</t>
-  </si>
-  <si>
-    <t>1994-10-16</t>
-  </si>
-  <si>
-    <t>1994-08-21</t>
-  </si>
-  <si>
-    <t>1988-02-15</t>
-  </si>
-  <si>
-    <t>1986-06-13</t>
-  </si>
-  <si>
-    <t>1986-08-12</t>
-  </si>
-  <si>
-    <t>1988-05-25</t>
-  </si>
-  <si>
-    <t>1996-07-05</t>
-  </si>
-  <si>
-    <t>1970-05-12</t>
-  </si>
-  <si>
-    <t>1981-07-08</t>
-  </si>
-  <si>
-    <t>1988-05-14</t>
-  </si>
-  <si>
-    <t>1982-05-22</t>
-  </si>
-  <si>
-    <t>1987-12-30</t>
-  </si>
-  <si>
-    <t>1990-02-24</t>
-  </si>
-  <si>
-    <t>1998-08-17</t>
-  </si>
-  <si>
-    <t>1985-10-03</t>
-  </si>
-  <si>
-    <t>1996-12-08</t>
-  </si>
-  <si>
-    <t>1977-03-08</t>
-  </si>
-  <si>
-    <t>1992-03-06</t>
-  </si>
-  <si>
-    <t>1998-01-07</t>
-  </si>
-  <si>
-    <t>1982-03-02</t>
-  </si>
-  <si>
-    <t>1988-04-07</t>
-  </si>
-  <si>
-    <t>1992-12-03</t>
-  </si>
-  <si>
-    <t>1992-08-27</t>
-  </si>
-  <si>
-    <t>1993-03-23</t>
-  </si>
-  <si>
-    <t>1972-10-13</t>
-  </si>
-  <si>
-    <t>1965-10-15</t>
-  </si>
-  <si>
-    <t>1964-09-16</t>
-  </si>
-  <si>
-    <t>1981-10-03</t>
-  </si>
-  <si>
-    <t>1994-01-31</t>
-  </si>
-  <si>
-    <t>1981-02-12</t>
-  </si>
-  <si>
-    <t>1978-11-10</t>
-  </si>
-  <si>
-    <t>1993-05-13</t>
-  </si>
-  <si>
-    <t>1993-05-27</t>
-  </si>
-  <si>
-    <t>1998-07-19</t>
-  </si>
-  <si>
-    <t>1989-09-09</t>
-  </si>
-  <si>
-    <t>1979-07-19</t>
-  </si>
-  <si>
-    <t>1993-08-11</t>
-  </si>
-  <si>
-    <t>1988-11-28</t>
-  </si>
-  <si>
-    <t>1993-07-10</t>
-  </si>
-  <si>
-    <t>1960-04-20</t>
-  </si>
-  <si>
-    <t>1971-05-12</t>
-  </si>
-  <si>
-    <t>1979-03-13</t>
-  </si>
-  <si>
-    <t>1991-07-29</t>
-  </si>
-  <si>
-    <t>2000-09-27</t>
-  </si>
-  <si>
-    <t>1989-06-16</t>
-  </si>
-  <si>
-    <t>1963-06-10</t>
-  </si>
-  <si>
-    <t>1994-11-13</t>
-  </si>
-  <si>
-    <t>1989-03-21</t>
-  </si>
-  <si>
-    <t>1992-04-30</t>
-  </si>
-  <si>
-    <t>1996-03-18</t>
-  </si>
-  <si>
-    <t>1980-11-07</t>
-  </si>
-  <si>
-    <t>1986-09-19</t>
-  </si>
-  <si>
-    <t>1984-05-03</t>
-  </si>
-  <si>
-    <t>1980-10-28</t>
-  </si>
-  <si>
-    <t>1982-07-08</t>
-  </si>
-  <si>
-    <t>1971-06-28</t>
-  </si>
-  <si>
-    <t>1973-10-21</t>
-  </si>
-  <si>
-    <t>1975-09-23</t>
-  </si>
-  <si>
-    <t>1981-03-05</t>
-  </si>
-  <si>
-    <t>1975-01-18</t>
-  </si>
-  <si>
-    <t>1983-04-14</t>
-  </si>
-  <si>
-    <t>1984-08-09</t>
-  </si>
-  <si>
-    <t>1980-12-04</t>
-  </si>
-  <si>
-    <t>1990-10-24</t>
-  </si>
-  <si>
-    <t>1994-01-16</t>
-  </si>
-  <si>
-    <t>1976-11-25</t>
-  </si>
-  <si>
-    <t>1990-05-07</t>
-  </si>
-  <si>
-    <t>1998-06-09</t>
-  </si>
-  <si>
-    <t>1990-07-03</t>
-  </si>
-  <si>
-    <t>1990-01-12</t>
-  </si>
-  <si>
-    <t>1976-01-08</t>
-  </si>
-  <si>
-    <t>1993-02-05</t>
-  </si>
-  <si>
-    <t>1989-12-17</t>
-  </si>
-  <si>
-    <t>1989-05-30</t>
-  </si>
-  <si>
-    <t>1965-11-19</t>
-  </si>
-  <si>
-    <t>1959-01-01</t>
-  </si>
-  <si>
-    <t>1966-11-19</t>
-  </si>
-  <si>
-    <t>1982-02-21</t>
-  </si>
-  <si>
-    <t>1995-12-24</t>
-  </si>
-  <si>
-    <t>1964-02-28</t>
-  </si>
-  <si>
-    <t>1986-08-08</t>
-  </si>
-  <si>
-    <t>1996-06-12</t>
-  </si>
-  <si>
-    <t>1989-08-06</t>
-  </si>
-  <si>
-    <t>1992-10-08</t>
-  </si>
-  <si>
-    <t>1985-11-05</t>
-  </si>
-  <si>
-    <t>1975-06-20</t>
-  </si>
-  <si>
-    <t>1977-09-18</t>
-  </si>
-  <si>
-    <t>1980-12-09</t>
-  </si>
-  <si>
-    <t>1962-03-15</t>
-  </si>
-  <si>
-    <t>1974-10-11</t>
-  </si>
-  <si>
-    <t>1974-12-26</t>
-  </si>
-  <si>
-    <t>1978-10-08</t>
-  </si>
-  <si>
-    <t>1979-02-16</t>
-  </si>
-  <si>
-    <t>1986-10-17</t>
-  </si>
-  <si>
-    <t>1979-06-15</t>
-  </si>
-  <si>
-    <t>1973-01-16</t>
-  </si>
-  <si>
-    <t>1980-08-14</t>
-  </si>
-  <si>
-    <t>1998-01-16</t>
-  </si>
-  <si>
-    <t>1978-09-27</t>
-  </si>
-  <si>
-    <t>2004-06-25</t>
-  </si>
-  <si>
-    <t>1994-03-09</t>
-  </si>
-  <si>
-    <t>1988-05-31</t>
-  </si>
-  <si>
-    <t>1994-10-21</t>
-  </si>
-  <si>
-    <t>1988-02-14</t>
-  </si>
-  <si>
-    <t>1991-11-09</t>
-  </si>
-  <si>
-    <t>1987-10-31</t>
-  </si>
-  <si>
-    <t>1992-05-18</t>
-  </si>
-  <si>
-    <t>1992-09-03</t>
-  </si>
-  <si>
-    <t>1985-04-25</t>
-  </si>
-  <si>
-    <t>1965-01-28</t>
-  </si>
-  <si>
-    <t>1989-05-19</t>
-  </si>
-  <si>
-    <t>1989-06-10</t>
-  </si>
-  <si>
-    <t>1975-08-08</t>
-  </si>
-  <si>
-    <t>1982-05-20</t>
-  </si>
-  <si>
-    <t>1994-01-21</t>
-  </si>
-  <si>
-    <t>1964-05-11</t>
-  </si>
-  <si>
-    <t>1995-12-03</t>
-  </si>
-  <si>
-    <t>1984-09-26</t>
-  </si>
-  <si>
-    <t>1959-05-22</t>
-  </si>
-  <si>
-    <t>1975-11-17</t>
-  </si>
-  <si>
-    <t>1984-05-19</t>
-  </si>
-  <si>
-    <t>1986-07-07</t>
-  </si>
-  <si>
-    <t>1986-11-24</t>
-  </si>
-  <si>
-    <t>1987-07-20</t>
-  </si>
-  <si>
-    <t>1992-06-20</t>
-  </si>
-  <si>
-    <t>1993-04-08</t>
-  </si>
-  <si>
-    <t>1994-07-08</t>
-  </si>
-  <si>
-    <t>2002-10-10</t>
-  </si>
-  <si>
-    <t>1992-01-08</t>
-  </si>
-  <si>
-    <t>1991-05-18</t>
-  </si>
-  <si>
-    <t>1997-07-07</t>
-  </si>
-  <si>
-    <t>1983-11-13</t>
-  </si>
-  <si>
-    <t>1983-04-20</t>
-  </si>
-  <si>
-    <t>1996-01-25</t>
-  </si>
-  <si>
-    <t>1999-06-19</t>
-  </si>
-  <si>
-    <t>1984-06-07</t>
-  </si>
-  <si>
-    <t>1990-10-08</t>
-  </si>
-  <si>
-    <t>1983-05-04</t>
-  </si>
-  <si>
-    <t>1998-12-21</t>
-  </si>
-  <si>
-    <t>1971-03-25</t>
-  </si>
-  <si>
-    <t>1975-01-11</t>
-  </si>
-  <si>
-    <t>1976-12-09</t>
-  </si>
-  <si>
-    <t>1984-11-10</t>
-  </si>
-  <si>
-    <t>1996-03-13</t>
-  </si>
-  <si>
-    <t>1969-09-02</t>
-  </si>
-  <si>
-    <t>1994-02-27</t>
-  </si>
-  <si>
-    <t>1972-11-18</t>
-  </si>
-  <si>
-    <t>1991-10-09</t>
-  </si>
-  <si>
-    <t>1991-04-22</t>
-  </si>
-  <si>
-    <t>1981-07-24</t>
-  </si>
-  <si>
-    <t>1991-10-06</t>
-  </si>
-  <si>
-    <t>1961-04-10</t>
-  </si>
-  <si>
-    <t>1989-07-11</t>
-  </si>
-  <si>
-    <t>1994-09-02</t>
-  </si>
-  <si>
-    <t>1995-01-31</t>
-  </si>
-  <si>
-    <t>1981-11-22</t>
-  </si>
-  <si>
-    <t>1989-10-13</t>
-  </si>
-  <si>
-    <t>1991-11-01</t>
-  </si>
-  <si>
-    <t>1985-07-15</t>
-  </si>
-  <si>
-    <t>1993-12-09</t>
-  </si>
-  <si>
-    <t>1975-08-23</t>
-  </si>
-  <si>
-    <t>1977-02-04</t>
-  </si>
-  <si>
-    <t>1993-02-24</t>
-  </si>
-  <si>
-    <t>1990-04-20</t>
-  </si>
-  <si>
-    <t>2001-11-11</t>
-  </si>
-  <si>
-    <t>1976-01-04</t>
-  </si>
-  <si>
-    <t>1983-02-05</t>
-  </si>
-  <si>
-    <t>1976-06-09</t>
-  </si>
-  <si>
-    <t>1975-12-14</t>
-  </si>
-  <si>
-    <t>1966-03-14</t>
-  </si>
-  <si>
-    <t>1987-01-07</t>
-  </si>
-  <si>
-    <t>1983-05-02</t>
-  </si>
-  <si>
-    <t>1985-05-23</t>
-  </si>
-  <si>
-    <t>1992-03-01</t>
-  </si>
-  <si>
-    <t>1990-06-27</t>
-  </si>
-  <si>
-    <t>1978-03-01</t>
-  </si>
-  <si>
-    <t>1980-12-03</t>
-  </si>
-  <si>
-    <t>1985-01-16</t>
-  </si>
-  <si>
-    <t>1990-06-19</t>
-  </si>
-  <si>
-    <t>1991-05-21</t>
-  </si>
-  <si>
-    <t>1994-01-13</t>
-  </si>
-  <si>
-    <t>1997-09-18</t>
-  </si>
-  <si>
-    <t>1959-08-21</t>
-  </si>
-  <si>
-    <t>1991-05-02</t>
-  </si>
-  <si>
-    <t>1983-10-11</t>
-  </si>
-  <si>
-    <t>1979-09-22</t>
-  </si>
-  <si>
-    <t>1973-09-11</t>
-  </si>
-  <si>
-    <t>1985-11-28</t>
-  </si>
-  <si>
-    <t>1993-07-20</t>
-  </si>
-  <si>
-    <t>1975-01-23</t>
-  </si>
-  <si>
-    <t>1975-10-17</t>
-  </si>
-  <si>
-    <t>1963-08-01</t>
-  </si>
-  <si>
-    <t>1974-04-01</t>
-  </si>
-  <si>
-    <t>1992-05-04</t>
-  </si>
-  <si>
-    <t>1990-03-02</t>
-  </si>
-  <si>
-    <t>1982-09-28</t>
-  </si>
-  <si>
-    <t>1965-11-17</t>
-  </si>
-  <si>
-    <t>1974-05-06</t>
-  </si>
-  <si>
-    <t>1975-08-20</t>
-  </si>
-  <si>
-    <t>1980-01-02</t>
-  </si>
-  <si>
-    <t>1978-08-20</t>
-  </si>
-  <si>
-    <t>1989-07-25</t>
-  </si>
-  <si>
-    <t>1975-07-02</t>
-  </si>
-  <si>
-    <t>1985-10-05</t>
-  </si>
-  <si>
-    <t>1995-05-31</t>
-  </si>
-  <si>
-    <t>1984-08-24</t>
-  </si>
-  <si>
-    <t>1961-07-29</t>
-  </si>
-  <si>
-    <t>1964-01-31</t>
-  </si>
-  <si>
-    <t>1988-10-06</t>
-  </si>
-  <si>
-    <t>1995-07-11</t>
-  </si>
-  <si>
-    <t>1979-07-12</t>
-  </si>
-  <si>
-    <t>1989-03-29</t>
-  </si>
-  <si>
-    <t>2000-04-11</t>
-  </si>
-  <si>
-    <t>1966-12-09</t>
-  </si>
-  <si>
-    <t>1969-03-17</t>
-  </si>
-  <si>
-    <t>1983-10-25</t>
-  </si>
-  <si>
-    <t>1987-01-24</t>
-  </si>
-  <si>
-    <t>1971-05-21</t>
-  </si>
-  <si>
-    <t>1984-11-21</t>
-  </si>
-  <si>
-    <t>1966-04-03</t>
-  </si>
-  <si>
-    <t>1984-02-19</t>
-  </si>
-  <si>
-    <t>1991-08-30</t>
-  </si>
-  <si>
-    <t>1980-07-23</t>
-  </si>
-  <si>
-    <t>1993-07-19</t>
-  </si>
-  <si>
-    <t>1990-11-17</t>
-  </si>
-  <si>
-    <t>1976-05-05</t>
-  </si>
-  <si>
-    <t>1962-11-11</t>
-  </si>
-  <si>
-    <t>1999-07-03</t>
-  </si>
-  <si>
-    <t>1964-04-03</t>
-  </si>
-  <si>
-    <t>1974-06-30</t>
-  </si>
-  <si>
-    <t>1982-01-08</t>
-  </si>
-  <si>
-    <t>1986-12-16</t>
-  </si>
-  <si>
-    <t>1994-06-08</t>
-  </si>
-  <si>
-    <t>1996-01-23</t>
-  </si>
-  <si>
-    <t>1990-04-29</t>
-  </si>
-  <si>
-    <t>1981-08-22</t>
-  </si>
-  <si>
-    <t>1992-07-03</t>
-  </si>
-  <si>
-    <t>1985-01-15</t>
-  </si>
-  <si>
-    <t>1995-07-06</t>
-  </si>
-  <si>
-    <t>1982-09-02</t>
-  </si>
-  <si>
-    <t>1985-03-01</t>
-  </si>
-  <si>
-    <t>1992-11-13</t>
-  </si>
-  <si>
-    <t>1991-08-02</t>
-  </si>
-  <si>
-    <t>1997-10-16</t>
-  </si>
-  <si>
-    <t>1979-04-09</t>
-  </si>
-  <si>
-    <t>1979-08-14</t>
-  </si>
-  <si>
-    <t>1989-08-17</t>
-  </si>
-  <si>
-    <t>1981-08-20</t>
-  </si>
-  <si>
-    <t>1995-06-26</t>
-  </si>
-  <si>
-    <t>1992-07-08</t>
-  </si>
-  <si>
-    <t>1992-02-27</t>
-  </si>
-  <si>
-    <t>1979-07-25</t>
-  </si>
-  <si>
-    <t>1992-12-01</t>
-  </si>
-  <si>
-    <t>1980-02-26</t>
-  </si>
-  <si>
-    <t>1980-08-05</t>
-  </si>
-  <si>
-    <t>1990-07-11</t>
-  </si>
-  <si>
-    <t>1981-08-28</t>
-  </si>
-  <si>
-    <t>1993-10-15</t>
-  </si>
-  <si>
-    <t>1966-03-20</t>
-  </si>
-  <si>
-    <t>1996-11-13</t>
-  </si>
-  <si>
-    <t>2000-01-04</t>
-  </si>
-  <si>
-    <t>1985-08-03</t>
-  </si>
-  <si>
-    <t>1992-10-05</t>
-  </si>
-  <si>
-    <t>1994-06-21</t>
-  </si>
-  <si>
-    <t>1988-04-28</t>
-  </si>
-  <si>
-    <t>1992-01-10</t>
-  </si>
-  <si>
-    <t>1963-08-14</t>
-  </si>
-  <si>
-    <t>1967-05-16</t>
-  </si>
-  <si>
-    <t>1994-04-24</t>
-  </si>
-  <si>
-    <t>1994-10-07</t>
-  </si>
-  <si>
-    <t>1978-08-12</t>
-  </si>
-  <si>
-    <t>1984-11-14</t>
-  </si>
-  <si>
-    <t>1989-03-09</t>
-  </si>
-  <si>
-    <t>1994-05-24</t>
-  </si>
-  <si>
-    <t>1981-02-18</t>
-  </si>
-  <si>
-    <t>1993-01-06</t>
-  </si>
-  <si>
-    <t>1990-01-17</t>
-  </si>
-  <si>
-    <t>1979-03-21</t>
-  </si>
-  <si>
-    <t>1995-10-07</t>
-  </si>
-  <si>
-    <t>1998-07-13</t>
-  </si>
-  <si>
-    <t>1980-04-09</t>
-  </si>
-  <si>
-    <t>1992-09-06</t>
-  </si>
-  <si>
-    <t>1972-06-29</t>
-  </si>
-  <si>
-    <t>1992-07-27</t>
-  </si>
-  <si>
-    <t>1969-03-20</t>
-  </si>
-  <si>
-    <t>1992-05-01</t>
-  </si>
-  <si>
-    <t>1995-07-29</t>
-  </si>
-  <si>
-    <t>1996-02-01</t>
-  </si>
-  <si>
-    <t>1981-06-27</t>
-  </si>
-  <si>
-    <t>1988-08-07</t>
-  </si>
-  <si>
-    <t>1988-12-06</t>
-  </si>
-  <si>
-    <t>1990-11-03</t>
-  </si>
-  <si>
-    <t>1993-06-19</t>
-  </si>
-  <si>
-    <t>1984-02-25</t>
-  </si>
-  <si>
-    <t>1969-04-07</t>
-  </si>
-  <si>
-    <t>1987-11-16</t>
-  </si>
-  <si>
-    <t>1972-10-31</t>
-  </si>
-  <si>
-    <t>1982-09-24</t>
-  </si>
-  <si>
-    <t>1995-02-13</t>
-  </si>
-  <si>
-    <t>1987-12-20</t>
-  </si>
-  <si>
-    <t>1965-11-16</t>
-  </si>
-  <si>
-    <t>1993-06-05</t>
-  </si>
-  <si>
-    <t>1976-11-17</t>
-  </si>
-  <si>
-    <t>1990-02-07</t>
-  </si>
-  <si>
-    <t>1986-09-14</t>
-  </si>
-  <si>
-    <t>1989-08-05</t>
-  </si>
-  <si>
-    <t>1988-08-21</t>
-  </si>
-  <si>
-    <t>1991-07-09</t>
-  </si>
-  <si>
-    <t>1986-12-19</t>
-  </si>
-  <si>
-    <t>1991-12-22</t>
-  </si>
-  <si>
-    <t>1998-11-19</t>
-  </si>
-  <si>
-    <t>1988-12-16</t>
-  </si>
-  <si>
-    <t>1985-06-05</t>
-  </si>
-  <si>
-    <t>1988-12-12</t>
-  </si>
-  <si>
-    <t>1994-07-09</t>
-  </si>
-  <si>
-    <t>1971-04-26</t>
-  </si>
-  <si>
-    <t>1979-05-23</t>
-  </si>
-  <si>
-    <t>1962-12-18</t>
-  </si>
-  <si>
-    <t>1992-01-17</t>
-  </si>
-  <si>
-    <t>1992-12-05</t>
-  </si>
-  <si>
-    <t>1970-09-10</t>
-  </si>
-  <si>
-    <t>1968-10-30</t>
-  </si>
-  <si>
-    <t>1973-08-07</t>
-  </si>
-  <si>
-    <t>1980-11-17</t>
-  </si>
-  <si>
-    <t>1990-08-19</t>
-  </si>
-  <si>
-    <t>1990-06-20</t>
-  </si>
-  <si>
-    <t>1993-03-01</t>
-  </si>
-  <si>
-    <t>1997-10-25</t>
-  </si>
-  <si>
-    <t>1980-06-21</t>
-  </si>
-  <si>
-    <t>1990-05-17</t>
-  </si>
-  <si>
-    <t>1990-09-08</t>
-  </si>
-  <si>
-    <t>1991-09-30</t>
-  </si>
-  <si>
-    <t>1959-07-27</t>
-  </si>
-  <si>
-    <t>1980-09-15</t>
-  </si>
-  <si>
-    <t>1962-11-20</t>
-  </si>
-  <si>
-    <t>1990-04-21</t>
-  </si>
-  <si>
-    <t>1993-11-19</t>
-  </si>
-  <si>
-    <t>1989-09-01</t>
-  </si>
-  <si>
-    <t>1967-02-15</t>
-  </si>
-  <si>
-    <t>1982-12-31</t>
-  </si>
-  <si>
-    <t>1991-10-08</t>
-  </si>
-  <si>
-    <t>1993-11-08</t>
-  </si>
-  <si>
-    <t>1989-11-16</t>
-  </si>
-  <si>
-    <t>1994-08-06</t>
-  </si>
-  <si>
-    <t>1982-05-28</t>
-  </si>
-  <si>
-    <t>1982-06-28</t>
-  </si>
-  <si>
-    <t>1992-06-18</t>
-  </si>
-  <si>
-    <t>1977-03-05</t>
-  </si>
-  <si>
-    <t>1979-10-23</t>
-  </si>
-  <si>
-    <t>1984-09-28</t>
-  </si>
-  <si>
-    <t>1992-08-15</t>
-  </si>
-  <si>
-    <t>1995-10-14</t>
-  </si>
-  <si>
-    <t>2003-01-04</t>
-  </si>
-  <si>
-    <t>1992-10-07</t>
-  </si>
-  <si>
-    <t>1978-08-10</t>
-  </si>
-  <si>
-    <t>1987-06-29</t>
-  </si>
-  <si>
-    <t>1968-07-19</t>
-  </si>
-  <si>
-    <t>1965-01-01</t>
-  </si>
-  <si>
-    <t>1991-01-21</t>
-  </si>
-  <si>
-    <t>1993-01-02</t>
-  </si>
-  <si>
-    <t>1980-08-04</t>
-  </si>
-  <si>
-    <t>1974-08-30</t>
-  </si>
-  <si>
-    <t>1982-11-23</t>
-  </si>
-  <si>
-    <t>1964-03-08</t>
-  </si>
-  <si>
-    <t>1976-06-06</t>
-  </si>
-  <si>
-    <t>1979-04-13</t>
-  </si>
-  <si>
-    <t>1969-08-11</t>
-  </si>
-  <si>
-    <t>1968-05-01</t>
-  </si>
-  <si>
-    <t>1992-12-16</t>
-  </si>
-  <si>
-    <t>1992-10-27</t>
-  </si>
-  <si>
-    <t>1987-09-16</t>
-  </si>
-  <si>
-    <t>1975-09-02</t>
-  </si>
-  <si>
-    <t>1977-11-02</t>
-  </si>
-  <si>
-    <t>1982-03-03</t>
-  </si>
-  <si>
-    <t>1987-01-31</t>
-  </si>
-  <si>
-    <t>1981-12-10</t>
-  </si>
-  <si>
-    <t>1987-10-19</t>
-  </si>
-  <si>
-    <t>1981-03-02</t>
-  </si>
-  <si>
-    <t>1978-12-30</t>
-  </si>
-  <si>
-    <t>1979-01-23</t>
-  </si>
-  <si>
-    <t>1973-07-25</t>
-  </si>
-  <si>
-    <t>1988-02-04</t>
-  </si>
-  <si>
-    <t>1984-12-25</t>
-  </si>
-  <si>
-    <t>1965-07-25</t>
-  </si>
-  <si>
-    <t>1964-03-25</t>
-  </si>
-  <si>
-    <t>1985-11-19</t>
-  </si>
-  <si>
-    <t>1989-04-09</t>
-  </si>
-  <si>
-    <t>1986-10-18</t>
   </si>
   <si>
     <t>CAROLINA ELISA ABARZUA HENRIQUEZ</t>
@@ -4116,6 +2826,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -4167,13 +2880,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4511,9 +3228,12 @@
   <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="22.1640625" customWidth="1"/>
     <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -4538,7 +3258,7 @@
       <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4547,7 +3267,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>969</v>
+        <v>539</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -4558,14 +3278,14 @@
       <c r="E2" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="7" t="s">
         <v>532</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>539</v>
+      <c r="H2" s="5">
+        <v>29232</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -4573,7 +3293,7 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>970</v>
+        <v>540</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -4590,8 +3310,8 @@
       <c r="G3" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>540</v>
+      <c r="H3" s="5">
+        <v>31972</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -4599,7 +3319,7 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>971</v>
+        <v>541</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -4616,8 +3336,8 @@
       <c r="G4" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>541</v>
+      <c r="H4" s="5">
+        <v>31654</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -4625,7 +3345,7 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>972</v>
+        <v>542</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -4642,8 +3362,8 @@
       <c r="G5" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>542</v>
+      <c r="H5" s="5">
+        <v>24234</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -4651,7 +3371,7 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>973</v>
+        <v>543</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -4668,8 +3388,8 @@
       <c r="G6" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>543</v>
+      <c r="H6" s="5">
+        <v>30597</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -4677,7 +3397,7 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>974</v>
+        <v>544</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
@@ -4694,8 +3414,8 @@
       <c r="G7" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>544</v>
+      <c r="H7" s="5">
+        <v>23538</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -4703,7 +3423,7 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>975</v>
+        <v>545</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
@@ -4720,8 +3440,8 @@
       <c r="G8" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>545</v>
+      <c r="H8" s="5">
+        <v>31286</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -4729,7 +3449,7 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>976</v>
+        <v>546</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
@@ -4746,8 +3466,8 @@
       <c r="G9" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>546</v>
+      <c r="H9" s="5">
+        <v>31589</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -4755,7 +3475,7 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>977</v>
+        <v>547</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>9</v>
@@ -4772,8 +3492,8 @@
       <c r="G10" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>547</v>
+      <c r="H10" s="5">
+        <v>32499</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -4781,7 +3501,7 @@
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>978</v>
+        <v>548</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>10</v>
@@ -4798,8 +3518,8 @@
       <c r="G11" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>548</v>
+      <c r="H11" s="5">
+        <v>33907</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -4807,7 +3527,7 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>979</v>
+        <v>549</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -4824,8 +3544,8 @@
       <c r="G12" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>549</v>
+      <c r="H12" s="5">
+        <v>35408</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -4833,7 +3553,7 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>980</v>
+        <v>550</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>9</v>
@@ -4850,8 +3570,8 @@
       <c r="G13" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>550</v>
+      <c r="H13" s="5">
+        <v>31374</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -4859,7 +3579,7 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>981</v>
+        <v>551</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>7</v>
@@ -4876,8 +3596,8 @@
       <c r="G14" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>551</v>
+      <c r="H14" s="5">
+        <v>34815</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -4885,7 +3605,7 @@
         <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>982</v>
+        <v>552</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>7</v>
@@ -4902,8 +3622,8 @@
       <c r="G15" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>552</v>
+      <c r="H15" s="5">
+        <v>29837</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -4911,7 +3631,7 @@
         <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>983</v>
+        <v>553</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>9</v>
@@ -4928,8 +3648,8 @@
       <c r="G16" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>553</v>
+      <c r="H16" s="5">
+        <v>30211</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -4937,7 +3657,7 @@
         <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>984</v>
+        <v>554</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>10</v>
@@ -4954,8 +3674,8 @@
       <c r="G17" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>554</v>
+      <c r="H17" s="5">
+        <v>34353</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -4963,7 +3683,7 @@
         <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>985</v>
+        <v>555</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>11</v>
@@ -4980,8 +3700,8 @@
       <c r="G18" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>555</v>
+      <c r="H18" s="5">
+        <v>28441</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -4989,7 +3709,7 @@
         <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>986</v>
+        <v>556</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>9</v>
@@ -5006,8 +3726,8 @@
       <c r="G19" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>556</v>
+      <c r="H19" s="5">
+        <v>31281</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -5015,7 +3735,7 @@
         <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>987</v>
+        <v>557</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>11</v>
@@ -5032,8 +3752,8 @@
       <c r="G20" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>557</v>
+      <c r="H20" s="5">
+        <v>36485</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -5041,7 +3761,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>988</v>
+        <v>558</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>7</v>
@@ -5058,8 +3778,8 @@
       <c r="G21" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>558</v>
+      <c r="H21" s="5">
+        <v>36180</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -5067,7 +3787,7 @@
         <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>989</v>
+        <v>559</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>7</v>
@@ -5084,8 +3804,8 @@
       <c r="G22" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>559</v>
+      <c r="H22" s="5">
+        <v>33648</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -5093,7 +3813,7 @@
         <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>990</v>
+        <v>560</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>7</v>
@@ -5110,8 +3830,8 @@
       <c r="G23" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>560</v>
+      <c r="H23" s="5">
+        <v>25722</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -5119,7 +3839,7 @@
         <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>991</v>
+        <v>561</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>10</v>
@@ -5136,8 +3856,8 @@
       <c r="G24" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>561</v>
+      <c r="H24" s="5">
+        <v>25111</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -5145,7 +3865,7 @@
         <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>992</v>
+        <v>562</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>7</v>
@@ -5162,8 +3882,8 @@
       <c r="G25" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>562</v>
+      <c r="H25" s="5">
+        <v>27853</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -5171,7 +3891,7 @@
         <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>993</v>
+        <v>563</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>7</v>
@@ -5188,8 +3908,8 @@
       <c r="G26" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>563</v>
+      <c r="H26" s="5">
+        <v>29924</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -5197,7 +3917,7 @@
         <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>994</v>
+        <v>564</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>7</v>
@@ -5214,8 +3934,8 @@
       <c r="G27" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>564</v>
+      <c r="H27" s="5">
+        <v>31362</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -5223,7 +3943,7 @@
         <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>995</v>
+        <v>565</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>9</v>
@@ -5240,8 +3960,8 @@
       <c r="G28" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>565</v>
+      <c r="H28" s="5">
+        <v>28834</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -5249,7 +3969,7 @@
         <v>47</v>
       </c>
       <c r="B29" t="s">
-        <v>996</v>
+        <v>566</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>11</v>
@@ -5266,8 +3986,8 @@
       <c r="G29" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>566</v>
+      <c r="H29" s="5">
+        <v>30742</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -5275,7 +3995,7 @@
         <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>997</v>
+        <v>567</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>7</v>
@@ -5292,8 +4012,8 @@
       <c r="G30" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>567</v>
+      <c r="H30" s="5">
+        <v>27779</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -5301,7 +4021,7 @@
         <v>49</v>
       </c>
       <c r="B31" t="s">
-        <v>998</v>
+        <v>568</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>7</v>
@@ -5318,8 +4038,8 @@
       <c r="G31" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>568</v>
+      <c r="H31" s="5">
+        <v>31817</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -5327,7 +4047,7 @@
         <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>999</v>
+        <v>569</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>7</v>
@@ -5344,8 +4064,8 @@
       <c r="G32" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>569</v>
+      <c r="H32" s="5">
+        <v>33352</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -5353,7 +4073,7 @@
         <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>10</v>
@@ -5370,8 +4090,8 @@
       <c r="G33" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>570</v>
+      <c r="H33" s="5">
+        <v>28955</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -5379,7 +4099,7 @@
         <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>1001</v>
+        <v>571</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>7</v>
@@ -5396,8 +4116,8 @@
       <c r="G34" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>571</v>
+      <c r="H34" s="5">
+        <v>24401</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -5405,7 +4125,7 @@
         <v>53</v>
       </c>
       <c r="B35" t="s">
-        <v>1002</v>
+        <v>572</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>10</v>
@@ -5422,8 +4142,8 @@
       <c r="G35" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>572</v>
+      <c r="H35" s="5">
+        <v>34334</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -5431,7 +4151,7 @@
         <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>1003</v>
+        <v>573</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>7</v>
@@ -5448,8 +4168,8 @@
       <c r="G36" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>573</v>
+      <c r="H36" s="5">
+        <v>28897</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -5457,7 +4177,7 @@
         <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>1004</v>
+        <v>574</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>9</v>
@@ -5474,8 +4194,8 @@
       <c r="G37" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>574</v>
+      <c r="H37" s="5">
+        <v>29064</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -5483,7 +4203,7 @@
         <v>56</v>
       </c>
       <c r="B38" t="s">
-        <v>1005</v>
+        <v>575</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>12</v>
@@ -5500,8 +4220,8 @@
       <c r="G38" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H38" s="1" t="s">
-        <v>575</v>
+      <c r="H38" s="5">
+        <v>26570</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -5509,7 +4229,7 @@
         <v>57</v>
       </c>
       <c r="B39" t="s">
-        <v>1006</v>
+        <v>576</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>7</v>
@@ -5526,8 +4246,8 @@
       <c r="G39" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>576</v>
+      <c r="H39" s="5">
+        <v>33366</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -5535,7 +4255,7 @@
         <v>58</v>
       </c>
       <c r="B40" t="s">
-        <v>1007</v>
+        <v>577</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>7</v>
@@ -5552,8 +4272,8 @@
       <c r="G40" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H40" s="1" t="s">
-        <v>577</v>
+      <c r="H40" s="5">
+        <v>35357</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -5561,7 +4281,7 @@
         <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>1008</v>
+        <v>578</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>11</v>
@@ -5578,8 +4298,8 @@
       <c r="G41" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>578</v>
+      <c r="H41" s="5">
+        <v>30560</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -5587,7 +4307,7 @@
         <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>1009</v>
+        <v>579</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>8</v>
@@ -5604,8 +4324,8 @@
       <c r="G42" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>579</v>
+      <c r="H42" s="5">
+        <v>29896</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -5613,7 +4333,7 @@
         <v>61</v>
       </c>
       <c r="B43" t="s">
-        <v>1010</v>
+        <v>580</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>10</v>
@@ -5630,8 +4350,8 @@
       <c r="G43" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>580</v>
+      <c r="H43" s="5">
+        <v>33673</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -5639,7 +4359,7 @@
         <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>1011</v>
+        <v>581</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>12</v>
@@ -5656,8 +4376,8 @@
       <c r="G44" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>581</v>
+      <c r="H44" s="5">
+        <v>34623</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -5665,7 +4385,7 @@
         <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>1012</v>
+        <v>582</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>11</v>
@@ -5682,8 +4402,8 @@
       <c r="G45" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>582</v>
+      <c r="H45" s="5">
+        <v>34567</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -5691,7 +4411,7 @@
         <v>64</v>
       </c>
       <c r="B46" t="s">
-        <v>1013</v>
+        <v>583</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>10</v>
@@ -5708,8 +4428,8 @@
       <c r="G46" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>583</v>
+      <c r="H46" s="5">
+        <v>32188</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -5717,7 +4437,7 @@
         <v>65</v>
       </c>
       <c r="B47" t="s">
-        <v>1014</v>
+        <v>584</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>10</v>
@@ -5734,8 +4454,8 @@
       <c r="G47" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>584</v>
+      <c r="H47" s="5">
+        <v>31576</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -5743,7 +4463,7 @@
         <v>66</v>
       </c>
       <c r="B48" t="s">
-        <v>1015</v>
+        <v>585</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>10</v>
@@ -5760,8 +4480,8 @@
       <c r="G48" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>585</v>
+      <c r="H48" s="5">
+        <v>31636</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -5769,7 +4489,7 @@
         <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>1016</v>
+        <v>586</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>9</v>
@@ -5786,8 +4506,8 @@
       <c r="G49" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>586</v>
+      <c r="H49" s="5">
+        <v>32288</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -5795,7 +4515,7 @@
         <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>1017</v>
+        <v>587</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>12</v>
@@ -5812,8 +4532,8 @@
       <c r="G50" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H50" s="1" t="s">
-        <v>587</v>
+      <c r="H50" s="5">
+        <v>35251</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -5821,7 +4541,7 @@
         <v>69</v>
       </c>
       <c r="B51" t="s">
-        <v>1018</v>
+        <v>588</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>7</v>
@@ -5838,8 +4558,8 @@
       <c r="G51" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H51" s="1" t="s">
-        <v>588</v>
+      <c r="H51" s="5">
+        <v>25700</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -5847,7 +4567,7 @@
         <v>70</v>
       </c>
       <c r="B52" t="s">
-        <v>1019</v>
+        <v>589</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
@@ -5864,8 +4584,8 @@
       <c r="G52" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H52" s="1" t="s">
-        <v>589</v>
+      <c r="H52" s="5">
+        <v>29775</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -5873,7 +4593,7 @@
         <v>71</v>
       </c>
       <c r="B53" t="s">
-        <v>1020</v>
+        <v>590</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>9</v>
@@ -5890,8 +4610,8 @@
       <c r="G53" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>590</v>
+      <c r="H53" s="5">
+        <v>32277</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -5899,7 +4619,7 @@
         <v>72</v>
       </c>
       <c r="B54" t="s">
-        <v>1021</v>
+        <v>591</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>8</v>
@@ -5916,8 +4636,8 @@
       <c r="G54" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>591</v>
+      <c r="H54" s="5">
+        <v>30093</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -5925,7 +4645,7 @@
         <v>73</v>
       </c>
       <c r="B55" t="s">
-        <v>1022</v>
+        <v>592</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>10</v>
@@ -5942,8 +4662,8 @@
       <c r="G55" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H55" s="1" t="s">
-        <v>592</v>
+      <c r="H55" s="5">
+        <v>32141</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -5951,7 +4671,7 @@
         <v>74</v>
       </c>
       <c r="B56" t="s">
-        <v>1023</v>
+        <v>593</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>10</v>
@@ -5968,8 +4688,8 @@
       <c r="G56" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H56" s="1" t="s">
-        <v>593</v>
+      <c r="H56" s="5">
+        <v>32928</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -5977,7 +4697,7 @@
         <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>1024</v>
+        <v>594</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>8</v>
@@ -5994,8 +4714,8 @@
       <c r="G57" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>594</v>
+      <c r="H57" s="5">
+        <v>36024</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -6003,7 +4723,7 @@
         <v>76</v>
       </c>
       <c r="B58" t="s">
-        <v>1025</v>
+        <v>595</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>7</v>
@@ -6020,8 +4740,8 @@
       <c r="G58" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H58" s="1" t="s">
-        <v>595</v>
+      <c r="H58" s="5">
+        <v>31323</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -6029,7 +4749,7 @@
         <v>77</v>
       </c>
       <c r="B59" t="s">
-        <v>1026</v>
+        <v>596</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>9</v>
@@ -6046,8 +4766,8 @@
       <c r="G59" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>596</v>
+      <c r="H59" s="5">
+        <v>35407</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -6055,7 +4775,7 @@
         <v>78</v>
       </c>
       <c r="B60" t="s">
-        <v>1027</v>
+        <v>597</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>7</v>
@@ -6072,8 +4792,8 @@
       <c r="G60" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>597</v>
+      <c r="H60" s="5">
+        <v>28192</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -6081,7 +4801,7 @@
         <v>79</v>
       </c>
       <c r="B61" t="s">
-        <v>1028</v>
+        <v>598</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>8</v>
@@ -6098,8 +4818,8 @@
       <c r="G61" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>598</v>
+      <c r="H61" s="5">
+        <v>33669</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -6107,7 +4827,7 @@
         <v>79</v>
       </c>
       <c r="B62" t="s">
-        <v>1029</v>
+        <v>599</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>8</v>
@@ -6124,8 +4844,8 @@
       <c r="G62" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>598</v>
+      <c r="H62" s="5">
+        <v>33669</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -6133,7 +4853,7 @@
         <v>80</v>
       </c>
       <c r="B63" t="s">
-        <v>1030</v>
+        <v>600</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>7</v>
@@ -6150,8 +4870,8 @@
       <c r="G63" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>599</v>
+      <c r="H63" s="5">
+        <v>35802</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -6159,7 +4879,7 @@
         <v>81</v>
       </c>
       <c r="B64" t="s">
-        <v>1031</v>
+        <v>601</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>10</v>
@@ -6176,8 +4896,8 @@
       <c r="G64" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>600</v>
+      <c r="H64" s="5">
+        <v>30012</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -6185,7 +4905,7 @@
         <v>82</v>
       </c>
       <c r="B65" t="s">
-        <v>1032</v>
+        <v>602</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>12</v>
@@ -6202,8 +4922,8 @@
       <c r="G65" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>601</v>
+      <c r="H65" s="5">
+        <v>32240</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -6211,7 +4931,7 @@
         <v>83</v>
       </c>
       <c r="B66" t="s">
-        <v>1033</v>
+        <v>603</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>8</v>
@@ -6228,8 +4948,8 @@
       <c r="G66" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H66" s="1" t="s">
-        <v>602</v>
+      <c r="H66" s="5">
+        <v>33941</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -6237,7 +4957,7 @@
         <v>84</v>
       </c>
       <c r="B67" t="s">
-        <v>1034</v>
+        <v>604</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>9</v>
@@ -6254,8 +4974,8 @@
       <c r="G67" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H67" s="1" t="s">
-        <v>603</v>
+      <c r="H67" s="5">
+        <v>33843</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -6263,7 +4983,7 @@
         <v>85</v>
       </c>
       <c r="B68" t="s">
-        <v>1035</v>
+        <v>605</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>13</v>
@@ -6280,8 +5000,8 @@
       <c r="G68" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H68" s="1" t="s">
-        <v>604</v>
+      <c r="H68" s="5">
+        <v>34051</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -6289,7 +5009,7 @@
         <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>1036</v>
+        <v>606</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>11</v>
@@ -6306,8 +5026,8 @@
       <c r="G69" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H69" s="1" t="s">
-        <v>605</v>
+      <c r="H69" s="5">
+        <v>26585</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -6315,7 +5035,7 @@
         <v>87</v>
       </c>
       <c r="B70" t="s">
-        <v>1037</v>
+        <v>607</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>8</v>
@@ -6332,8 +5052,8 @@
       <c r="G70" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H70" s="1" t="s">
-        <v>606</v>
+      <c r="H70" s="5">
+        <v>24030</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -6341,7 +5061,7 @@
         <v>88</v>
       </c>
       <c r="B71" t="s">
-        <v>1038</v>
+        <v>608</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>7</v>
@@ -6358,8 +5078,8 @@
       <c r="G71" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H71" s="1" t="s">
-        <v>607</v>
+      <c r="H71" s="5">
+        <v>23636</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -6367,7 +5087,7 @@
         <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>1039</v>
+        <v>609</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>7</v>
@@ -6384,8 +5104,8 @@
       <c r="G72" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H72" s="1" t="s">
-        <v>608</v>
+      <c r="H72" s="5">
+        <v>29862</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -6393,7 +5113,7 @@
         <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>1040</v>
+        <v>610</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>12</v>
@@ -6410,8 +5130,8 @@
       <c r="G73" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H73" s="1" t="s">
-        <v>609</v>
+      <c r="H73" s="5">
+        <v>34365</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
@@ -6419,7 +5139,7 @@
         <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>1041</v>
+        <v>611</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>8</v>
@@ -6436,8 +5156,8 @@
       <c r="G74" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>610</v>
+      <c r="H74" s="5">
+        <v>29629</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -6445,7 +5165,7 @@
         <v>92</v>
       </c>
       <c r="B75" t="s">
-        <v>1042</v>
+        <v>612</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>7</v>
@@ -6462,8 +5182,8 @@
       <c r="G75" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H75" s="1" t="s">
-        <v>611</v>
+      <c r="H75" s="5">
+        <v>28804</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -6471,7 +5191,7 @@
         <v>93</v>
       </c>
       <c r="B76" t="s">
-        <v>1043</v>
+        <v>613</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>9</v>
@@ -6488,8 +5208,8 @@
       <c r="G76" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H76" s="1" t="s">
-        <v>612</v>
+      <c r="H76" s="5">
+        <v>34102</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -6497,7 +5217,7 @@
         <v>94</v>
       </c>
       <c r="B77" t="s">
-        <v>1044</v>
+        <v>614</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>7</v>
@@ -6514,8 +5234,8 @@
       <c r="G77" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H77" s="1" t="s">
-        <v>613</v>
+      <c r="H77" s="5">
+        <v>34116</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -6523,7 +5243,7 @@
         <v>95</v>
       </c>
       <c r="B78" t="s">
-        <v>1045</v>
+        <v>615</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>7</v>
@@ -6540,8 +5260,8 @@
       <c r="G78" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H78" s="1" t="s">
-        <v>614</v>
+      <c r="H78" s="5">
+        <v>35995</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -6549,7 +5269,7 @@
         <v>96</v>
       </c>
       <c r="B79" t="s">
-        <v>1046</v>
+        <v>616</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>7</v>
@@ -6566,8 +5286,8 @@
       <c r="G79" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>615</v>
+      <c r="H79" s="5">
+        <v>32760</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -6575,7 +5295,7 @@
         <v>97</v>
       </c>
       <c r="B80" t="s">
-        <v>1047</v>
+        <v>617</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>10</v>
@@ -6592,8 +5312,8 @@
       <c r="G80" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>616</v>
+      <c r="H80" s="5">
+        <v>29055</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -6601,7 +5321,7 @@
         <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>1048</v>
+        <v>618</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>8</v>
@@ -6618,8 +5338,8 @@
       <c r="G81" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>617</v>
+      <c r="H81" s="5">
+        <v>34192</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -6627,7 +5347,7 @@
         <v>99</v>
       </c>
       <c r="B82" t="s">
-        <v>1049</v>
+        <v>619</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>11</v>
@@ -6644,8 +5364,8 @@
       <c r="G82" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H82" s="1" t="s">
-        <v>618</v>
+      <c r="H82" s="5">
+        <v>32475</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -6653,7 +5373,7 @@
         <v>100</v>
       </c>
       <c r="B83" t="s">
-        <v>1050</v>
+        <v>620</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>7</v>
@@ -6670,8 +5390,8 @@
       <c r="G83" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H83" s="1" t="s">
-        <v>619</v>
+      <c r="H83" s="5">
+        <v>34160</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -6679,7 +5399,7 @@
         <v>101</v>
       </c>
       <c r="B84" t="s">
-        <v>1051</v>
+        <v>621</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>8</v>
@@ -6696,8 +5416,8 @@
       <c r="G84" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H84" s="1" t="s">
-        <v>620</v>
+      <c r="H84" s="5">
+        <v>22026</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -6705,7 +5425,7 @@
         <v>102</v>
       </c>
       <c r="B85" t="s">
-        <v>1052</v>
+        <v>622</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>12</v>
@@ -6722,8 +5442,8 @@
       <c r="G85" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H85" s="1" t="s">
-        <v>621</v>
+      <c r="H85" s="5">
+        <v>26065</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -6731,7 +5451,7 @@
         <v>103</v>
       </c>
       <c r="B86" t="s">
-        <v>1053</v>
+        <v>623</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>7</v>
@@ -6748,8 +5468,8 @@
       <c r="G86" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>622</v>
+      <c r="H86" s="5">
+        <v>28927</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -6757,7 +5477,7 @@
         <v>104</v>
       </c>
       <c r="B87" t="s">
-        <v>1054</v>
+        <v>624</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>11</v>
@@ -6774,8 +5494,8 @@
       <c r="G87" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>623</v>
+      <c r="H87" s="5">
+        <v>33448</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -6783,7 +5503,7 @@
         <v>105</v>
       </c>
       <c r="B88" t="s">
-        <v>1055</v>
+        <v>625</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>12</v>
@@ -6800,8 +5520,8 @@
       <c r="G88" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H88" s="1" t="s">
-        <v>624</v>
+      <c r="H88" s="5">
+        <v>36796</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -6809,7 +5529,7 @@
         <v>106</v>
       </c>
       <c r="B89" t="s">
-        <v>1056</v>
+        <v>626</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>10</v>
@@ -6826,8 +5546,8 @@
       <c r="G89" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>625</v>
+      <c r="H89" s="5">
+        <v>32675</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -6835,7 +5555,7 @@
         <v>107</v>
       </c>
       <c r="B90" t="s">
-        <v>1057</v>
+        <v>627</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>10</v>
@@ -6852,8 +5572,8 @@
       <c r="G90" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H90" s="1" t="s">
-        <v>626</v>
+      <c r="H90" s="5">
+        <v>23172</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -6861,7 +5581,7 @@
         <v>108</v>
       </c>
       <c r="B91" t="s">
-        <v>1058</v>
+        <v>628</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>10</v>
@@ -6878,8 +5598,8 @@
       <c r="G91" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>627</v>
+      <c r="H91" s="5">
+        <v>34651</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -6887,7 +5607,7 @@
         <v>109</v>
       </c>
       <c r="B92" t="s">
-        <v>1059</v>
+        <v>629</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>14</v>
@@ -6904,8 +5624,8 @@
       <c r="G92" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H92" s="1" t="s">
-        <v>628</v>
+      <c r="H92" s="5">
+        <v>32588</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -6913,7 +5633,7 @@
         <v>110</v>
       </c>
       <c r="B93" t="s">
-        <v>1060</v>
+        <v>630</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>10</v>
@@ -6930,8 +5650,8 @@
       <c r="G93" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H93" s="1" t="s">
-        <v>629</v>
+      <c r="H93" s="5">
+        <v>33724</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -6939,7 +5659,7 @@
         <v>111</v>
       </c>
       <c r="B94" t="s">
-        <v>1061</v>
+        <v>631</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>10</v>
@@ -6956,8 +5676,8 @@
       <c r="G94" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H94" s="1" t="s">
-        <v>630</v>
+      <c r="H94" s="5">
+        <v>35142</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -6965,7 +5685,7 @@
         <v>112</v>
       </c>
       <c r="B95" t="s">
-        <v>1062</v>
+        <v>632</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>15</v>
@@ -6982,8 +5702,8 @@
       <c r="G95" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H95" s="1" t="s">
-        <v>631</v>
+      <c r="H95" s="5">
+        <v>29532</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -6991,7 +5711,7 @@
         <v>113</v>
       </c>
       <c r="B96" t="s">
-        <v>1063</v>
+        <v>633</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>7</v>
@@ -7008,8 +5728,8 @@
       <c r="G96" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H96" s="1" t="s">
-        <v>632</v>
+      <c r="H96" s="5">
+        <v>31674</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -7017,7 +5737,7 @@
         <v>114</v>
       </c>
       <c r="B97" t="s">
-        <v>1064</v>
+        <v>634</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>8</v>
@@ -7034,8 +5754,8 @@
       <c r="G97" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H97" s="1" t="s">
-        <v>633</v>
+      <c r="H97" s="5">
+        <v>30805</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -7043,7 +5763,7 @@
         <v>115</v>
       </c>
       <c r="B98" t="s">
-        <v>1065</v>
+        <v>635</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>7</v>
@@ -7060,8 +5780,8 @@
       <c r="G98" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>634</v>
+      <c r="H98" s="5">
+        <v>29522</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -7069,7 +5789,7 @@
         <v>116</v>
       </c>
       <c r="B99" t="s">
-        <v>1066</v>
+        <v>636</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>7</v>
@@ -7086,8 +5806,8 @@
       <c r="G99" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>635</v>
+      <c r="H99" s="5">
+        <v>30140</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -7095,7 +5815,7 @@
         <v>117</v>
       </c>
       <c r="B100" t="s">
-        <v>1067</v>
+        <v>637</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>7</v>
@@ -7112,8 +5832,8 @@
       <c r="G100" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H100" s="1" t="s">
-        <v>636</v>
+      <c r="H100" s="5">
+        <v>26112</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -7121,7 +5841,7 @@
         <v>118</v>
       </c>
       <c r="B101" t="s">
-        <v>1068</v>
+        <v>638</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>7</v>
@@ -7138,8 +5858,8 @@
       <c r="G101" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H101" s="1" t="s">
-        <v>637</v>
+      <c r="H101" s="5">
+        <v>26958</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
@@ -7147,7 +5867,7 @@
         <v>119</v>
       </c>
       <c r="B102" t="s">
-        <v>1069</v>
+        <v>639</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>7</v>
@@ -7164,8 +5884,8 @@
       <c r="G102" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H102" s="1" t="s">
-        <v>638</v>
+      <c r="H102" s="5">
+        <v>27660</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
@@ -7173,7 +5893,7 @@
         <v>120</v>
       </c>
       <c r="B103" t="s">
-        <v>1070</v>
+        <v>640</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>7</v>
@@ -7190,8 +5910,8 @@
       <c r="G103" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H103" s="1" t="s">
-        <v>639</v>
+      <c r="H103" s="5">
+        <v>29650</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
@@ -7199,7 +5919,7 @@
         <v>121</v>
       </c>
       <c r="B104" t="s">
-        <v>1071</v>
+        <v>641</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>16</v>
@@ -7216,8 +5936,8 @@
       <c r="G104" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>640</v>
+      <c r="H104" s="5">
+        <v>27412</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
@@ -7225,7 +5945,7 @@
         <v>122</v>
       </c>
       <c r="B105" t="s">
-        <v>1072</v>
+        <v>642</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>10</v>
@@ -7242,8 +5962,8 @@
       <c r="G105" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H105" s="1" t="s">
-        <v>641</v>
+      <c r="H105" s="5">
+        <v>30420</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
@@ -7251,7 +5971,7 @@
         <v>123</v>
       </c>
       <c r="B106" t="s">
-        <v>1073</v>
+        <v>643</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>10</v>
@@ -7268,8 +5988,8 @@
       <c r="G106" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H106" s="1" t="s">
-        <v>642</v>
+      <c r="H106" s="5">
+        <v>30903</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
@@ -7277,7 +5997,7 @@
         <v>124</v>
       </c>
       <c r="B107" t="s">
-        <v>1074</v>
+        <v>644</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>10</v>
@@ -7294,8 +6014,8 @@
       <c r="G107" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>643</v>
+      <c r="H107" s="5">
+        <v>29559</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
@@ -7303,7 +6023,7 @@
         <v>125</v>
       </c>
       <c r="B108" t="s">
-        <v>1075</v>
+        <v>645</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>8</v>
@@ -7320,8 +6040,8 @@
       <c r="G108" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H108" s="1" t="s">
-        <v>644</v>
+      <c r="H108" s="5">
+        <v>33170</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
@@ -7329,7 +6049,7 @@
         <v>126</v>
       </c>
       <c r="B109" t="s">
-        <v>1076</v>
+        <v>646</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>8</v>
@@ -7346,8 +6066,8 @@
       <c r="G109" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H109" s="1" t="s">
-        <v>645</v>
+      <c r="H109" s="5">
+        <v>34350</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
@@ -7355,7 +6075,7 @@
         <v>127</v>
       </c>
       <c r="B110" t="s">
-        <v>1077</v>
+        <v>647</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>7</v>
@@ -7372,8 +6092,8 @@
       <c r="G110" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H110" s="1" t="s">
-        <v>646</v>
+      <c r="H110" s="5">
+        <v>28089</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
@@ -7381,7 +6101,7 @@
         <v>128</v>
       </c>
       <c r="B111" t="s">
-        <v>1078</v>
+        <v>648</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>7</v>
@@ -7398,8 +6118,8 @@
       <c r="G111" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H111" s="1" t="s">
-        <v>647</v>
+      <c r="H111" s="5">
+        <v>33000</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
@@ -7407,7 +6127,7 @@
         <v>129</v>
       </c>
       <c r="B112" t="s">
-        <v>1079</v>
+        <v>649</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>11</v>
@@ -7424,8 +6144,8 @@
       <c r="G112" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H112" s="1" t="s">
-        <v>648</v>
+      <c r="H112" s="5">
+        <v>35955</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
@@ -7433,7 +6153,7 @@
         <v>130</v>
       </c>
       <c r="B113" t="s">
-        <v>1080</v>
+        <v>650</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>9</v>
@@ -7450,8 +6170,8 @@
       <c r="G113" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H113" s="1" t="s">
-        <v>649</v>
+      <c r="H113" s="5">
+        <v>33057</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
@@ -7459,7 +6179,7 @@
         <v>131</v>
       </c>
       <c r="B114" t="s">
-        <v>1081</v>
+        <v>651</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>12</v>
@@ -7476,8 +6196,8 @@
       <c r="G114" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H114" s="1" t="s">
-        <v>650</v>
+      <c r="H114" s="5">
+        <v>32885</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
@@ -7485,7 +6205,7 @@
         <v>132</v>
       </c>
       <c r="B115" t="s">
-        <v>1082</v>
+        <v>652</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>7</v>
@@ -7502,8 +6222,8 @@
       <c r="G115" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H115" s="1" t="s">
-        <v>651</v>
+      <c r="H115" s="5">
+        <v>27767</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
@@ -7511,7 +6231,7 @@
         <v>133</v>
       </c>
       <c r="B116" t="s">
-        <v>1083</v>
+        <v>653</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>7</v>
@@ -7528,8 +6248,8 @@
       <c r="G116" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H116" s="1" t="s">
-        <v>652</v>
+      <c r="H116" s="5">
+        <v>34005</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
@@ -7537,7 +6257,7 @@
         <v>134</v>
       </c>
       <c r="B117" t="s">
-        <v>1084</v>
+        <v>654</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>8</v>
@@ -7554,8 +6274,8 @@
       <c r="G117" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H117" s="1" t="s">
-        <v>653</v>
+      <c r="H117" s="5">
+        <v>32859</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
@@ -7563,7 +6283,7 @@
         <v>135</v>
       </c>
       <c r="B118" t="s">
-        <v>1085</v>
+        <v>655</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>10</v>
@@ -7580,8 +6300,8 @@
       <c r="G118" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H118" s="1" t="s">
-        <v>654</v>
+      <c r="H118" s="5">
+        <v>32658</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -7589,7 +6309,7 @@
         <v>136</v>
       </c>
       <c r="B119" t="s">
-        <v>1086</v>
+        <v>656</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>10</v>
@@ -7606,8 +6326,8 @@
       <c r="G119" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H119" s="1" t="s">
-        <v>655</v>
+      <c r="H119" s="5">
+        <v>24065</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
@@ -7615,7 +6335,7 @@
         <v>137</v>
       </c>
       <c r="B120" t="s">
-        <v>1087</v>
+        <v>657</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>7</v>
@@ -7632,8 +6352,8 @@
       <c r="G120" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H120" s="1" t="s">
-        <v>656</v>
+      <c r="H120" s="5">
+        <v>21551</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -7641,7 +6361,7 @@
         <v>138</v>
       </c>
       <c r="B121" t="s">
-        <v>1088</v>
+        <v>658</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>9</v>
@@ -7658,8 +6378,8 @@
       <c r="G121" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H121" s="1" t="s">
-        <v>657</v>
+      <c r="H121" s="5">
+        <v>24430</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -7667,7 +6387,7 @@
         <v>139</v>
       </c>
       <c r="B122" t="s">
-        <v>1089</v>
+        <v>659</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>17</v>
@@ -7684,8 +6404,8 @@
       <c r="G122" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H122" s="1" t="s">
-        <v>658</v>
+      <c r="H122" s="5">
+        <v>30003</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -7693,7 +6413,7 @@
         <v>140</v>
       </c>
       <c r="B123" t="s">
-        <v>1090</v>
+        <v>660</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>10</v>
@@ -7710,8 +6430,8 @@
       <c r="G123" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H123" s="1" t="s">
-        <v>659</v>
+      <c r="H123" s="5">
+        <v>35057</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -7719,7 +6439,7 @@
         <v>141</v>
       </c>
       <c r="B124" t="s">
-        <v>1091</v>
+        <v>661</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>7</v>
@@ -7736,8 +6456,8 @@
       <c r="G124" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H124" s="1" t="s">
-        <v>660</v>
+      <c r="H124" s="5">
+        <v>23435</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
@@ -7745,7 +6465,7 @@
         <v>142</v>
       </c>
       <c r="B125" t="s">
-        <v>1092</v>
+        <v>662</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>10</v>
@@ -7762,8 +6482,8 @@
       <c r="G125" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H125" s="1" t="s">
-        <v>661</v>
+      <c r="H125" s="5">
+        <v>31632</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
@@ -7771,7 +6491,7 @@
         <v>143</v>
       </c>
       <c r="B126" t="s">
-        <v>1093</v>
+        <v>663</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>9</v>
@@ -7788,8 +6508,8 @@
       <c r="G126" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H126" s="1" t="s">
-        <v>662</v>
+      <c r="H126" s="5">
+        <v>35228</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
@@ -7797,7 +6517,7 @@
         <v>144</v>
       </c>
       <c r="B127" t="s">
-        <v>1094</v>
+        <v>664</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>7</v>
@@ -7814,8 +6534,8 @@
       <c r="G127" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H127" s="1" t="s">
-        <v>663</v>
+      <c r="H127" s="5">
+        <v>32726</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
@@ -7823,7 +6543,7 @@
         <v>145</v>
       </c>
       <c r="B128" t="s">
-        <v>1095</v>
+        <v>665</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>9</v>
@@ -7840,8 +6560,8 @@
       <c r="G128" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H128" s="1" t="s">
-        <v>664</v>
+      <c r="H128" s="5">
+        <v>33885</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -7849,7 +6569,7 @@
         <v>145</v>
       </c>
       <c r="B129" t="s">
-        <v>1096</v>
+        <v>666</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>9</v>
@@ -7866,8 +6586,8 @@
       <c r="G129" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H129" s="1" t="s">
-        <v>664</v>
+      <c r="H129" s="5">
+        <v>33885</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -7875,7 +6595,7 @@
         <v>146</v>
       </c>
       <c r="B130" t="s">
-        <v>1097</v>
+        <v>667</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>10</v>
@@ -7892,8 +6612,8 @@
       <c r="G130" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H130" s="1" t="s">
-        <v>665</v>
+      <c r="H130" s="5">
+        <v>31356</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -7901,7 +6621,7 @@
         <v>147</v>
       </c>
       <c r="B131" t="s">
-        <v>1098</v>
+        <v>668</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>17</v>
@@ -7918,8 +6638,8 @@
       <c r="G131" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H131" s="1" t="s">
-        <v>666</v>
+      <c r="H131" s="5">
+        <v>27565</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
@@ -7927,7 +6647,7 @@
         <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>1099</v>
+        <v>669</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>7</v>
@@ -7944,8 +6664,8 @@
       <c r="G132" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H132" s="1" t="s">
-        <v>667</v>
+      <c r="H132" s="5">
+        <v>28386</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
@@ -7953,7 +6673,7 @@
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>1100</v>
+        <v>670</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>7</v>
@@ -7970,8 +6690,8 @@
       <c r="G133" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H133" s="1" t="s">
-        <v>668</v>
+      <c r="H133" s="5">
+        <v>29564</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
@@ -7979,7 +6699,7 @@
         <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>1101</v>
+        <v>671</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>11</v>
@@ -7996,8 +6716,8 @@
       <c r="G134" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H134" s="1" t="s">
-        <v>669</v>
+      <c r="H134" s="5">
+        <v>22720</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
@@ -8005,7 +6725,7 @@
         <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>1102</v>
+        <v>672</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>10</v>
@@ -8022,8 +6742,8 @@
       <c r="G135" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H135" s="1" t="s">
-        <v>670</v>
+      <c r="H135" s="5">
+        <v>27313</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
@@ -8031,7 +6751,7 @@
         <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>1103</v>
+        <v>673</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>7</v>
@@ -8048,8 +6768,8 @@
       <c r="G136" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H136" s="1" t="s">
-        <v>671</v>
+      <c r="H136" s="5">
+        <v>27389</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
@@ -8057,7 +6777,7 @@
         <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>1104</v>
+        <v>674</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>11</v>
@@ -8074,8 +6794,8 @@
       <c r="G137" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H137" s="1" t="s">
-        <v>672</v>
+      <c r="H137" s="5">
+        <v>28771</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
@@ -8083,7 +6803,7 @@
         <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>1105</v>
+        <v>675</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>7</v>
@@ -8100,8 +6820,8 @@
       <c r="G138" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H138" s="1" t="s">
-        <v>673</v>
+      <c r="H138" s="5">
+        <v>28902</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
@@ -8109,7 +6829,7 @@
         <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>1106</v>
+        <v>676</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>7</v>
@@ -8126,8 +6846,8 @@
       <c r="G139" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H139" s="1" t="s">
-        <v>674</v>
+      <c r="H139" s="5">
+        <v>31702</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
@@ -8135,7 +6855,7 @@
         <v>156</v>
       </c>
       <c r="B140" t="s">
-        <v>1107</v>
+        <v>677</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>7</v>
@@ -8152,8 +6872,8 @@
       <c r="G140" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H140" s="1" t="s">
-        <v>675</v>
+      <c r="H140" s="5">
+        <v>29021</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -8161,7 +6881,7 @@
         <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>1108</v>
+        <v>678</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>7</v>
@@ -8178,8 +6898,8 @@
       <c r="G141" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H141" s="1" t="s">
-        <v>676</v>
+      <c r="H141" s="5">
+        <v>26680</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -8187,7 +6907,7 @@
         <v>158</v>
       </c>
       <c r="B142" t="s">
-        <v>1109</v>
+        <v>679</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>10</v>
@@ -8204,8 +6924,8 @@
       <c r="G142" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H142" s="1" t="s">
-        <v>677</v>
+      <c r="H142" s="5">
+        <v>29447</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
@@ -8213,7 +6933,7 @@
         <v>159</v>
       </c>
       <c r="B143" t="s">
-        <v>1110</v>
+        <v>680</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>7</v>
@@ -8230,8 +6950,8 @@
       <c r="G143" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H143" s="1" t="s">
-        <v>678</v>
+      <c r="H143" s="5">
+        <v>35811</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
@@ -8239,7 +6959,7 @@
         <v>160</v>
       </c>
       <c r="B144" t="s">
-        <v>1111</v>
+        <v>681</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>7</v>
@@ -8256,8 +6976,8 @@
       <c r="G144" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H144" s="1" t="s">
-        <v>679</v>
+      <c r="H144" s="5">
+        <v>28760</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -8265,7 +6985,7 @@
         <v>161</v>
       </c>
       <c r="B145" t="s">
-        <v>1112</v>
+        <v>682</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>7</v>
@@ -8282,8 +7002,8 @@
       <c r="G145" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H145" s="1" t="s">
-        <v>680</v>
+      <c r="H145" s="5">
+        <v>38163</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -8291,7 +7011,7 @@
         <v>162</v>
       </c>
       <c r="B146" t="s">
-        <v>1113</v>
+        <v>683</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>7</v>
@@ -8308,8 +7028,8 @@
       <c r="G146" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H146" s="1" t="s">
-        <v>681</v>
+      <c r="H146" s="5">
+        <v>34402</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -8317,7 +7037,7 @@
         <v>163</v>
       </c>
       <c r="B147" t="s">
-        <v>1114</v>
+        <v>684</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>7</v>
@@ -8334,8 +7054,8 @@
       <c r="G147" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H147" s="1" t="s">
-        <v>682</v>
+      <c r="H147" s="5">
+        <v>32294</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -8343,7 +7063,7 @@
         <v>164</v>
       </c>
       <c r="B148" t="s">
-        <v>1115</v>
+        <v>685</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>10</v>
@@ -8360,8 +7080,8 @@
       <c r="G148" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H148" s="1" t="s">
-        <v>683</v>
+      <c r="H148" s="5">
+        <v>34628</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -8369,7 +7089,7 @@
         <v>165</v>
       </c>
       <c r="B149" t="s">
-        <v>1116</v>
+        <v>686</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>7</v>
@@ -8386,8 +7106,8 @@
       <c r="G149" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H149" s="1" t="s">
-        <v>684</v>
+      <c r="H149" s="5">
+        <v>32187</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -8395,7 +7115,7 @@
         <v>166</v>
       </c>
       <c r="B150" t="s">
-        <v>1117</v>
+        <v>687</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>11</v>
@@ -8412,8 +7132,8 @@
       <c r="G150" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H150" s="1" t="s">
-        <v>685</v>
+      <c r="H150" s="5">
+        <v>33551</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -8421,7 +7141,7 @@
         <v>167</v>
       </c>
       <c r="B151" t="s">
-        <v>1118</v>
+        <v>688</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>7</v>
@@ -8438,8 +7158,8 @@
       <c r="G151" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H151" s="1" t="s">
-        <v>686</v>
+      <c r="H151" s="5">
+        <v>32081</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -8447,7 +7167,7 @@
         <v>168</v>
       </c>
       <c r="B152" t="s">
-        <v>1119</v>
+        <v>689</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>11</v>
@@ -8464,8 +7184,8 @@
       <c r="G152" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H152" s="1" t="s">
-        <v>687</v>
+      <c r="H152" s="5">
+        <v>33742</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
@@ -8473,7 +7193,7 @@
         <v>169</v>
       </c>
       <c r="B153" t="s">
-        <v>1120</v>
+        <v>690</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>17</v>
@@ -8490,8 +7210,8 @@
       <c r="G153" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H153" s="1" t="s">
-        <v>688</v>
+      <c r="H153" s="5">
+        <v>33850</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -8499,7 +7219,7 @@
         <v>170</v>
       </c>
       <c r="B154" t="s">
-        <v>1121</v>
+        <v>691</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>7</v>
@@ -8516,8 +7236,8 @@
       <c r="G154" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H154" s="1" t="s">
-        <v>689</v>
+      <c r="H154" s="5">
+        <v>31162</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -8525,7 +7245,7 @@
         <v>171</v>
       </c>
       <c r="B155" t="s">
-        <v>1122</v>
+        <v>692</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>7</v>
@@ -8542,8 +7262,8 @@
       <c r="G155" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H155" s="1" t="s">
-        <v>690</v>
+      <c r="H155" s="5">
+        <v>23770</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -8551,7 +7271,7 @@
         <v>172</v>
       </c>
       <c r="B156" t="s">
-        <v>1123</v>
+        <v>693</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>10</v>
@@ -8568,8 +7288,8 @@
       <c r="G156" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H156" s="1" t="s">
-        <v>691</v>
+      <c r="H156" s="5">
+        <v>32647</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -8577,7 +7297,7 @@
         <v>173</v>
       </c>
       <c r="B157" t="s">
-        <v>1124</v>
+        <v>694</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>7</v>
@@ -8594,8 +7314,8 @@
       <c r="G157" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H157" s="1" t="s">
-        <v>692</v>
+      <c r="H157" s="5">
+        <v>32669</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
@@ -8603,7 +7323,7 @@
         <v>174</v>
       </c>
       <c r="B158" t="s">
-        <v>1125</v>
+        <v>695</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>12</v>
@@ -8620,8 +7340,8 @@
       <c r="G158" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H158" s="1" t="s">
-        <v>693</v>
+      <c r="H158" s="5">
+        <v>27614</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
@@ -8629,7 +7349,7 @@
         <v>175</v>
       </c>
       <c r="B159" t="s">
-        <v>1126</v>
+        <v>696</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>7</v>
@@ -8646,8 +7366,8 @@
       <c r="G159" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H159" s="1" t="s">
-        <v>694</v>
+      <c r="H159" s="5">
+        <v>30091</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
@@ -8655,7 +7375,7 @@
         <v>176</v>
       </c>
       <c r="B160" t="s">
-        <v>1127</v>
+        <v>697</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>11</v>
@@ -8672,8 +7392,8 @@
       <c r="G160" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H160" s="1" t="s">
-        <v>695</v>
+      <c r="H160" s="5">
+        <v>34355</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
@@ -8681,7 +7401,7 @@
         <v>177</v>
       </c>
       <c r="B161" t="s">
-        <v>1128</v>
+        <v>698</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>12</v>
@@ -8698,8 +7418,8 @@
       <c r="G161" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H161" s="1" t="s">
-        <v>696</v>
+      <c r="H161" s="5">
+        <v>23508</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -8707,7 +7427,7 @@
         <v>178</v>
       </c>
       <c r="B162" t="s">
-        <v>1129</v>
+        <v>699</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>7</v>
@@ -8724,8 +7444,8 @@
       <c r="G162" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H162" s="1" t="s">
-        <v>697</v>
+      <c r="H162" s="5">
+        <v>35036</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
@@ -8733,7 +7453,7 @@
         <v>179</v>
       </c>
       <c r="B163" t="s">
-        <v>1130</v>
+        <v>700</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>7</v>
@@ -8750,8 +7470,8 @@
       <c r="G163" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H163" s="1" t="s">
-        <v>698</v>
+      <c r="H163" s="5">
+        <v>30951</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
@@ -8759,7 +7479,7 @@
         <v>180</v>
       </c>
       <c r="B164" t="s">
-        <v>1131</v>
+        <v>701</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>18</v>
@@ -8776,8 +7496,8 @@
       <c r="G164" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H164" s="1" t="s">
-        <v>699</v>
+      <c r="H164" s="5">
+        <v>21692</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
@@ -8785,7 +7505,7 @@
         <v>181</v>
       </c>
       <c r="B165" t="s">
-        <v>1132</v>
+        <v>702</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>17</v>
@@ -8802,8 +7522,8 @@
       <c r="G165" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H165" s="1" t="s">
-        <v>700</v>
+      <c r="H165" s="5">
+        <v>27715</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
@@ -8811,7 +7531,7 @@
         <v>182</v>
       </c>
       <c r="B166" t="s">
-        <v>1133</v>
+        <v>703</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>7</v>
@@ -8828,8 +7548,8 @@
       <c r="G166" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H166" s="1" t="s">
-        <v>701</v>
+      <c r="H166" s="5">
+        <v>30821</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
@@ -8837,7 +7557,7 @@
         <v>183</v>
       </c>
       <c r="B167" t="s">
-        <v>1134</v>
+        <v>704</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>7</v>
@@ -8854,8 +7574,8 @@
       <c r="G167" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H167" s="1" t="s">
-        <v>702</v>
+      <c r="H167" s="5">
+        <v>31600</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
@@ -8863,7 +7583,7 @@
         <v>184</v>
       </c>
       <c r="B168" t="s">
-        <v>1135</v>
+        <v>705</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>7</v>
@@ -8880,8 +7600,8 @@
       <c r="G168" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H168" s="1" t="s">
-        <v>703</v>
+      <c r="H168" s="5">
+        <v>31740</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
@@ -8889,7 +7609,7 @@
         <v>185</v>
       </c>
       <c r="B169" t="s">
-        <v>1136</v>
+        <v>706</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>7</v>
@@ -8906,8 +7626,8 @@
       <c r="G169" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H169" s="1" t="s">
-        <v>704</v>
+      <c r="H169" s="5">
+        <v>31978</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
@@ -8915,7 +7635,7 @@
         <v>186</v>
       </c>
       <c r="B170" t="s">
-        <v>1137</v>
+        <v>707</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>7</v>
@@ -8932,8 +7652,8 @@
       <c r="G170" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H170" s="1" t="s">
-        <v>705</v>
+      <c r="H170" s="5">
+        <v>33775</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
@@ -8941,7 +7661,7 @@
         <v>187</v>
       </c>
       <c r="B171" t="s">
-        <v>1138</v>
+        <v>708</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>10</v>
@@ -8958,8 +7678,8 @@
       <c r="G171" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H171" s="1" t="s">
-        <v>706</v>
+      <c r="H171" s="5">
+        <v>34067</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
@@ -8967,7 +7687,7 @@
         <v>188</v>
       </c>
       <c r="B172" t="s">
-        <v>1139</v>
+        <v>709</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>8</v>
@@ -8984,8 +7704,8 @@
       <c r="G172" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H172" s="1" t="s">
-        <v>707</v>
+      <c r="H172" s="5">
+        <v>34523</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
@@ -8993,7 +7713,7 @@
         <v>189</v>
       </c>
       <c r="B173" t="s">
-        <v>1140</v>
+        <v>710</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>8</v>
@@ -9010,8 +7730,8 @@
       <c r="G173" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H173" s="1" t="s">
-        <v>708</v>
+      <c r="H173" s="5">
+        <v>37539</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
@@ -9019,7 +7739,7 @@
         <v>190</v>
       </c>
       <c r="B174" t="s">
-        <v>1141</v>
+        <v>711</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>12</v>
@@ -9036,8 +7756,8 @@
       <c r="G174" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H174" s="1" t="s">
-        <v>709</v>
+      <c r="H174" s="5">
+        <v>33611</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
@@ -9045,7 +7765,7 @@
         <v>191</v>
       </c>
       <c r="B175" t="s">
-        <v>1142</v>
+        <v>712</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>7</v>
@@ -9062,8 +7782,8 @@
       <c r="G175" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H175" s="1" t="s">
-        <v>710</v>
+      <c r="H175" s="5">
+        <v>33376</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
@@ -9071,7 +7791,7 @@
         <v>192</v>
       </c>
       <c r="B176" t="s">
-        <v>1143</v>
+        <v>713</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>11</v>
@@ -9088,8 +7808,8 @@
       <c r="G176" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H176" s="1" t="s">
-        <v>711</v>
+      <c r="H176" s="5">
+        <v>35618</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
@@ -9097,7 +7817,7 @@
         <v>193</v>
       </c>
       <c r="B177" t="s">
-        <v>1144</v>
+        <v>714</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>11</v>
@@ -9114,8 +7834,8 @@
       <c r="G177" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H177" s="1" t="s">
-        <v>712</v>
+      <c r="H177" s="5">
+        <v>30633</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
@@ -9123,7 +7843,7 @@
         <v>194</v>
       </c>
       <c r="B178" t="s">
-        <v>1145</v>
+        <v>715</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>11</v>
@@ -9140,8 +7860,8 @@
       <c r="G178" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H178" s="1" t="s">
-        <v>713</v>
+      <c r="H178" s="5">
+        <v>30426</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
@@ -9149,7 +7869,7 @@
         <v>195</v>
       </c>
       <c r="B179" t="s">
-        <v>1146</v>
+        <v>716</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>11</v>
@@ -9166,8 +7886,8 @@
       <c r="G179" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H179" s="1" t="s">
-        <v>714</v>
+      <c r="H179" s="5">
+        <v>35089</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
@@ -9175,7 +7895,7 @@
         <v>196</v>
       </c>
       <c r="B180" t="s">
-        <v>1147</v>
+        <v>717</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>10</v>
@@ -9192,8 +7912,8 @@
       <c r="G180" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H180" s="1" t="s">
-        <v>715</v>
+      <c r="H180" s="5">
+        <v>36330</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
@@ -9201,7 +7921,7 @@
         <v>197</v>
       </c>
       <c r="B181" t="s">
-        <v>1148</v>
+        <v>718</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>13</v>
@@ -9218,8 +7938,8 @@
       <c r="G181" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H181" s="1" t="s">
-        <v>716</v>
+      <c r="H181" s="5">
+        <v>30840</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
@@ -9227,7 +7947,7 @@
         <v>198</v>
       </c>
       <c r="B182" t="s">
-        <v>1149</v>
+        <v>719</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>7</v>
@@ -9244,8 +7964,8 @@
       <c r="G182" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H182" s="1" t="s">
-        <v>717</v>
+      <c r="H182" s="5">
+        <v>33154</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
@@ -9253,7 +7973,7 @@
         <v>199</v>
       </c>
       <c r="B183" t="s">
-        <v>1150</v>
+        <v>720</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>10</v>
@@ -9270,8 +7990,8 @@
       <c r="G183" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H183" s="1" t="s">
-        <v>718</v>
+      <c r="H183" s="5">
+        <v>30440</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
@@ -9279,7 +7999,7 @@
         <v>200</v>
       </c>
       <c r="B184" t="s">
-        <v>1151</v>
+        <v>721</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>10</v>
@@ -9296,8 +8016,8 @@
       <c r="G184" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H184" s="1" t="s">
-        <v>719</v>
+      <c r="H184" s="5">
+        <v>36150</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
@@ -9305,7 +8025,7 @@
         <v>201</v>
       </c>
       <c r="B185" t="s">
-        <v>1152</v>
+        <v>722</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>11</v>
@@ -9322,8 +8042,8 @@
       <c r="G185" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H185" s="1" t="s">
-        <v>720</v>
+      <c r="H185" s="5">
+        <v>26017</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
@@ -9331,7 +8051,7 @@
         <v>202</v>
       </c>
       <c r="B186" t="s">
-        <v>1153</v>
+        <v>723</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>14</v>
@@ -9348,8 +8068,8 @@
       <c r="G186" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H186" s="1" t="s">
-        <v>721</v>
+      <c r="H186" s="5">
+        <v>27405</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
@@ -9357,7 +8077,7 @@
         <v>203</v>
       </c>
       <c r="B187" t="s">
-        <v>1154</v>
+        <v>724</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>11</v>
@@ -9374,8 +8094,8 @@
       <c r="G187" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H187" s="1" t="s">
-        <v>722</v>
+      <c r="H187" s="5">
+        <v>28103</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
@@ -9383,7 +8103,7 @@
         <v>204</v>
       </c>
       <c r="B188" t="s">
-        <v>1155</v>
+        <v>725</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>7</v>
@@ -9400,8 +8120,8 @@
       <c r="G188" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H188" s="1" t="s">
-        <v>723</v>
+      <c r="H188" s="5">
+        <v>30996</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
@@ -9409,7 +8129,7 @@
         <v>205</v>
       </c>
       <c r="B189" t="s">
-        <v>1156</v>
+        <v>726</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>7</v>
@@ -9426,8 +8146,8 @@
       <c r="G189" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H189" s="1" t="s">
-        <v>724</v>
+      <c r="H189" s="5">
+        <v>35137</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
@@ -9435,7 +8155,7 @@
         <v>206</v>
       </c>
       <c r="B190" t="s">
-        <v>1157</v>
+        <v>727</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>10</v>
@@ -9452,8 +8172,8 @@
       <c r="G190" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H190" s="1" t="s">
-        <v>725</v>
+      <c r="H190" s="5">
+        <v>25448</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
@@ -9461,7 +8181,7 @@
         <v>207</v>
       </c>
       <c r="B191" t="s">
-        <v>1158</v>
+        <v>728</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>10</v>
@@ -9478,8 +8198,8 @@
       <c r="G191" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H191" s="1" t="s">
-        <v>726</v>
+      <c r="H191" s="5">
+        <v>34392</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
@@ -9487,7 +8207,7 @@
         <v>208</v>
       </c>
       <c r="B192" t="s">
-        <v>1159</v>
+        <v>729</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>10</v>
@@ -9504,8 +8224,8 @@
       <c r="G192" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H192" s="1" t="s">
-        <v>660</v>
+      <c r="H192" s="5">
+        <v>23435</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
@@ -9513,7 +8233,7 @@
         <v>209</v>
       </c>
       <c r="B193" t="s">
-        <v>1160</v>
+        <v>730</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>11</v>
@@ -9530,8 +8250,8 @@
       <c r="G193" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H193" s="1" t="s">
-        <v>727</v>
+      <c r="H193" s="5">
+        <v>26621</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
@@ -9539,7 +8259,7 @@
         <v>210</v>
       </c>
       <c r="B194" t="s">
-        <v>1161</v>
+        <v>731</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>7</v>
@@ -9556,8 +8276,8 @@
       <c r="G194" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H194" s="1" t="s">
-        <v>728</v>
+      <c r="H194" s="5">
+        <v>33520</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
@@ -9565,7 +8285,7 @@
         <v>211</v>
       </c>
       <c r="B195" t="s">
-        <v>1162</v>
+        <v>732</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>7</v>
@@ -9582,8 +8302,8 @@
       <c r="G195" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H195" s="1" t="s">
-        <v>729</v>
+      <c r="H195" s="5">
+        <v>33350</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
@@ -9591,7 +8311,7 @@
         <v>212</v>
       </c>
       <c r="B196" t="s">
-        <v>1163</v>
+        <v>733</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>17</v>
@@ -9608,8 +8328,8 @@
       <c r="G196" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H196" s="1" t="s">
-        <v>730</v>
+      <c r="H196" s="5">
+        <v>29791</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
@@ -9617,7 +8337,7 @@
         <v>213</v>
       </c>
       <c r="B197" t="s">
-        <v>1164</v>
+        <v>734</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>19</v>
@@ -9634,8 +8354,8 @@
       <c r="G197" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H197" s="1" t="s">
-        <v>731</v>
+      <c r="H197" s="5">
+        <v>33517</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
@@ -9643,7 +8363,7 @@
         <v>214</v>
       </c>
       <c r="B198" t="s">
-        <v>1165</v>
+        <v>735</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>12</v>
@@ -9660,8 +8380,8 @@
       <c r="G198" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H198" s="1" t="s">
-        <v>732</v>
+      <c r="H198" s="5">
+        <v>22381</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
@@ -9669,7 +8389,7 @@
         <v>215</v>
       </c>
       <c r="B199" t="s">
-        <v>1166</v>
+        <v>736</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>10</v>
@@ -9686,8 +8406,8 @@
       <c r="G199" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H199" s="1" t="s">
-        <v>733</v>
+      <c r="H199" s="5">
+        <v>32700</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
@@ -9695,7 +8415,7 @@
         <v>216</v>
       </c>
       <c r="B200" t="s">
-        <v>1167</v>
+        <v>737</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>7</v>
@@ -9712,8 +8432,8 @@
       <c r="G200" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H200" s="1" t="s">
-        <v>734</v>
+      <c r="H200" s="5">
+        <v>34579</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
@@ -9721,7 +8441,7 @@
         <v>217</v>
       </c>
       <c r="B201" t="s">
-        <v>1168</v>
+        <v>738</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>12</v>
@@ -9738,8 +8458,8 @@
       <c r="G201" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H201" s="1" t="s">
-        <v>735</v>
+      <c r="H201" s="5">
+        <v>34730</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
@@ -9747,7 +8467,7 @@
         <v>218</v>
       </c>
       <c r="B202" t="s">
-        <v>1169</v>
+        <v>739</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>9</v>
@@ -9764,8 +8484,8 @@
       <c r="G202" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H202" s="1" t="s">
-        <v>736</v>
+      <c r="H202" s="5">
+        <v>29912</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
@@ -9773,7 +8493,7 @@
         <v>219</v>
       </c>
       <c r="B203" t="s">
-        <v>1170</v>
+        <v>740</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>10</v>
@@ -9790,8 +8510,8 @@
       <c r="G203" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H203" s="1" t="s">
-        <v>737</v>
+      <c r="H203" s="5">
+        <v>32794</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
@@ -9799,7 +8519,7 @@
         <v>220</v>
       </c>
       <c r="B204" t="s">
-        <v>1171</v>
+        <v>741</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>7</v>
@@ -9816,8 +8536,8 @@
       <c r="G204" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H204" s="1" t="s">
-        <v>738</v>
+      <c r="H204" s="5">
+        <v>33543</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
@@ -9825,7 +8545,7 @@
         <v>221</v>
       </c>
       <c r="B205" t="s">
-        <v>1172</v>
+        <v>742</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>7</v>
@@ -9842,8 +8562,8 @@
       <c r="G205" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H205" s="1" t="s">
-        <v>739</v>
+      <c r="H205" s="5">
+        <v>31243</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
@@ -9851,7 +8571,7 @@
         <v>222</v>
       </c>
       <c r="B206" t="s">
-        <v>1173</v>
+        <v>743</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>7</v>
@@ -9868,8 +8588,8 @@
       <c r="G206" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H206" s="1" t="s">
-        <v>740</v>
+      <c r="H206" s="5">
+        <v>34312</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
@@ -9877,7 +8597,7 @@
         <v>223</v>
       </c>
       <c r="B207" t="s">
-        <v>1174</v>
+        <v>744</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>9</v>
@@ -9894,8 +8614,8 @@
       <c r="G207" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H207" s="1" t="s">
-        <v>741</v>
+      <c r="H207" s="5">
+        <v>27629</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
@@ -9903,7 +8623,7 @@
         <v>224</v>
       </c>
       <c r="B208" t="s">
-        <v>1175</v>
+        <v>745</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>9</v>
@@ -9920,8 +8640,8 @@
       <c r="G208" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H208" s="1" t="s">
-        <v>742</v>
+      <c r="H208" s="5">
+        <v>28160</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
@@ -9929,7 +8649,7 @@
         <v>225</v>
       </c>
       <c r="B209" t="s">
-        <v>1176</v>
+        <v>746</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>7</v>
@@ -9946,8 +8666,8 @@
       <c r="G209" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H209" s="1" t="s">
-        <v>743</v>
+      <c r="H209" s="5">
+        <v>34024</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
@@ -9955,7 +8675,7 @@
         <v>226</v>
       </c>
       <c r="B210" t="s">
-        <v>1177</v>
+        <v>747</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>7</v>
@@ -9972,8 +8692,8 @@
       <c r="G210" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H210" s="1" t="s">
-        <v>744</v>
+      <c r="H210" s="5">
+        <v>32983</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
@@ -9981,7 +8701,7 @@
         <v>227</v>
       </c>
       <c r="B211" t="s">
-        <v>1178</v>
+        <v>748</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>8</v>
@@ -9998,8 +8718,8 @@
       <c r="G211" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H211" s="1" t="s">
-        <v>745</v>
+      <c r="H211" s="5">
+        <v>37206</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
@@ -10007,7 +8727,7 @@
         <v>228</v>
       </c>
       <c r="B212" t="s">
-        <v>1179</v>
+        <v>749</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>7</v>
@@ -10024,8 +8744,8 @@
       <c r="G212" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H212" s="1" t="s">
-        <v>746</v>
+      <c r="H212" s="5">
+        <v>27763</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
@@ -10033,7 +8753,7 @@
         <v>229</v>
       </c>
       <c r="B213" t="s">
-        <v>1180</v>
+        <v>750</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>12</v>
@@ -10050,8 +8770,8 @@
       <c r="G213" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H213" s="1" t="s">
-        <v>747</v>
+      <c r="H213" s="5">
+        <v>30352</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
@@ -10059,7 +8779,7 @@
         <v>230</v>
       </c>
       <c r="B214" t="s">
-        <v>1181</v>
+        <v>751</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>10</v>
@@ -10076,8 +8796,8 @@
       <c r="G214" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H214" s="1" t="s">
-        <v>748</v>
+      <c r="H214" s="5">
+        <v>27920</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
@@ -10085,7 +8805,7 @@
         <v>231</v>
       </c>
       <c r="B215" t="s">
-        <v>1182</v>
+        <v>752</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>8</v>
@@ -10102,8 +8822,8 @@
       <c r="G215" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H215" s="1" t="s">
-        <v>749</v>
+      <c r="H215" s="5">
+        <v>27742</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
@@ -10111,7 +8831,7 @@
         <v>232</v>
       </c>
       <c r="B216" t="s">
-        <v>1183</v>
+        <v>753</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>17</v>
@@ -10128,8 +8848,8 @@
       <c r="G216" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H216" s="1" t="s">
-        <v>750</v>
+      <c r="H216" s="5">
+        <v>24180</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
@@ -10137,7 +8857,7 @@
         <v>233</v>
       </c>
       <c r="B217" t="s">
-        <v>1184</v>
+        <v>754</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>10</v>
@@ -10154,8 +8874,8 @@
       <c r="G217" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H217" s="1" t="s">
-        <v>751</v>
+      <c r="H217" s="5">
+        <v>31784</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
@@ -10163,7 +8883,7 @@
         <v>234</v>
       </c>
       <c r="B218" t="s">
-        <v>1185</v>
+        <v>755</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>17</v>
@@ -10180,8 +8900,8 @@
       <c r="G218" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H218" s="1" t="s">
-        <v>752</v>
+      <c r="H218" s="5">
+        <v>30438</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
@@ -10189,7 +8909,7 @@
         <v>235</v>
       </c>
       <c r="B219" t="s">
-        <v>1186</v>
+        <v>756</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>19</v>
@@ -10206,8 +8926,8 @@
       <c r="G219" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H219" s="1" t="s">
-        <v>753</v>
+      <c r="H219" s="5">
+        <v>31190</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
@@ -10215,7 +8935,7 @@
         <v>236</v>
       </c>
       <c r="B220" t="s">
-        <v>1187</v>
+        <v>757</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>7</v>
@@ -10232,8 +8952,8 @@
       <c r="G220" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H220" s="1" t="s">
-        <v>754</v>
+      <c r="H220" s="5">
+        <v>33664</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
@@ -10241,7 +8961,7 @@
         <v>237</v>
       </c>
       <c r="B221" t="s">
-        <v>1188</v>
+        <v>758</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>8</v>
@@ -10258,8 +8978,8 @@
       <c r="G221" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H221" s="1" t="s">
-        <v>755</v>
+      <c r="H221" s="5">
+        <v>33051</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
@@ -10267,7 +8987,7 @@
         <v>238</v>
       </c>
       <c r="B222" t="s">
-        <v>1189</v>
+        <v>759</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>10</v>
@@ -10284,8 +9004,8 @@
       <c r="G222" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H222" s="1" t="s">
-        <v>756</v>
+      <c r="H222" s="5">
+        <v>28550</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
@@ -10293,7 +9013,7 @@
         <v>239</v>
       </c>
       <c r="B223" t="s">
-        <v>1190</v>
+        <v>760</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>7</v>
@@ -10310,8 +9030,8 @@
       <c r="G223" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H223" s="1" t="s">
-        <v>757</v>
+      <c r="H223" s="5">
+        <v>29558</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
@@ -10319,7 +9039,7 @@
         <v>240</v>
       </c>
       <c r="B224" t="s">
-        <v>1191</v>
+        <v>761</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>7</v>
@@ -10336,8 +9056,8 @@
       <c r="G224" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H224" s="1" t="s">
-        <v>758</v>
+      <c r="H224" s="5">
+        <v>31063</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
@@ -10345,7 +9065,7 @@
         <v>241</v>
       </c>
       <c r="B225" t="s">
-        <v>1192</v>
+        <v>762</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>7</v>
@@ -10362,8 +9082,8 @@
       <c r="G225" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H225" s="1" t="s">
-        <v>759</v>
+      <c r="H225" s="5">
+        <v>33043</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
@@ -10371,7 +9091,7 @@
         <v>242</v>
       </c>
       <c r="B226" t="s">
-        <v>1193</v>
+        <v>763</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>7</v>
@@ -10388,8 +9108,8 @@
       <c r="G226" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H226" s="1" t="s">
-        <v>760</v>
+      <c r="H226" s="5">
+        <v>33379</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
@@ -10397,7 +9117,7 @@
         <v>243</v>
       </c>
       <c r="B227" t="s">
-        <v>1194</v>
+        <v>764</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>11</v>
@@ -10414,8 +9134,8 @@
       <c r="G227" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H227" s="1" t="s">
-        <v>761</v>
+      <c r="H227" s="5">
+        <v>34347</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
@@ -10423,7 +9143,7 @@
         <v>244</v>
       </c>
       <c r="B228" t="s">
-        <v>1195</v>
+        <v>765</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>11</v>
@@ -10440,8 +9160,8 @@
       <c r="G228" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H228" s="1" t="s">
-        <v>762</v>
+      <c r="H228" s="5">
+        <v>35691</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
@@ -10449,7 +9169,7 @@
         <v>245</v>
       </c>
       <c r="B229" t="s">
-        <v>1196</v>
+        <v>766</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>7</v>
@@ -10466,8 +9186,8 @@
       <c r="G229" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H229" s="1" t="s">
-        <v>763</v>
+      <c r="H229" s="5">
+        <v>21783</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.2">
@@ -10475,7 +9195,7 @@
         <v>246</v>
       </c>
       <c r="B230" t="s">
-        <v>1197</v>
+        <v>767</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>9</v>
@@ -10492,8 +9212,8 @@
       <c r="G230" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H230" s="1" t="s">
-        <v>764</v>
+      <c r="H230" s="5">
+        <v>33360</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.2">
@@ -10501,7 +9221,7 @@
         <v>247</v>
       </c>
       <c r="B231" t="s">
-        <v>1198</v>
+        <v>768</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>7</v>
@@ -10518,8 +9238,8 @@
       <c r="G231" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H231" s="1" t="s">
-        <v>765</v>
+      <c r="H231" s="5">
+        <v>30600</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.2">
@@ -10527,7 +9247,7 @@
         <v>248</v>
       </c>
       <c r="B232" t="s">
-        <v>1199</v>
+        <v>769</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>7</v>
@@ -10544,8 +9264,8 @@
       <c r="G232" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H232" s="1" t="s">
-        <v>766</v>
+      <c r="H232" s="5">
+        <v>29120</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
@@ -10553,7 +9273,7 @@
         <v>249</v>
       </c>
       <c r="B233" t="s">
-        <v>1200</v>
+        <v>770</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>11</v>
@@ -10570,8 +9290,8 @@
       <c r="G233" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H233" s="1" t="s">
-        <v>767</v>
+      <c r="H233" s="5">
+        <v>26918</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
@@ -10579,7 +9299,7 @@
         <v>250</v>
       </c>
       <c r="B234" t="s">
-        <v>1201</v>
+        <v>771</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>9</v>
@@ -10596,8 +9316,8 @@
       <c r="G234" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H234" s="1" t="s">
-        <v>768</v>
+      <c r="H234" s="5">
+        <v>31379</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
@@ -10605,7 +9325,7 @@
         <v>251</v>
       </c>
       <c r="B235" t="s">
-        <v>1202</v>
+        <v>772</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>7</v>
@@ -10622,8 +9342,8 @@
       <c r="G235" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H235" s="1" t="s">
-        <v>769</v>
+      <c r="H235" s="5">
+        <v>34170</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
@@ -10631,7 +9351,7 @@
         <v>252</v>
       </c>
       <c r="B236" t="s">
-        <v>1203</v>
+        <v>773</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>7</v>
@@ -10648,8 +9368,8 @@
       <c r="G236" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H236" s="1" t="s">
-        <v>770</v>
+      <c r="H236" s="5">
+        <v>27417</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
@@ -10657,7 +9377,7 @@
         <v>253</v>
       </c>
       <c r="B237" t="s">
-        <v>1204</v>
+        <v>774</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>9</v>
@@ -10674,8 +9394,8 @@
       <c r="G237" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H237" s="1" t="s">
-        <v>771</v>
+      <c r="H237" s="5">
+        <v>27684</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
@@ -10683,7 +9403,7 @@
         <v>254</v>
       </c>
       <c r="B238" t="s">
-        <v>1205</v>
+        <v>775</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>7</v>
@@ -10700,8 +9420,8 @@
       <c r="G238" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H238" s="1" t="s">
-        <v>772</v>
+      <c r="H238" s="5">
+        <v>23224</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
@@ -10709,7 +9429,7 @@
         <v>255</v>
       </c>
       <c r="B239" t="s">
-        <v>1206</v>
+        <v>776</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>7</v>
@@ -10726,8 +9446,8 @@
       <c r="G239" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H239" s="1" t="s">
-        <v>773</v>
+      <c r="H239" s="5">
+        <v>27120</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
@@ -10735,7 +9455,7 @@
         <v>256</v>
       </c>
       <c r="B240" t="s">
-        <v>1207</v>
+        <v>777</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>8</v>
@@ -10752,8 +9472,8 @@
       <c r="G240" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H240" s="1" t="s">
-        <v>774</v>
+      <c r="H240" s="5">
+        <v>33728</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
@@ -10761,7 +9481,7 @@
         <v>257</v>
       </c>
       <c r="B241" t="s">
-        <v>1208</v>
+        <v>778</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>12</v>
@@ -10778,8 +9498,8 @@
       <c r="G241" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H241" s="1" t="s">
-        <v>775</v>
+      <c r="H241" s="5">
+        <v>32934</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
@@ -10787,7 +9507,7 @@
         <v>258</v>
       </c>
       <c r="B242" t="s">
-        <v>1209</v>
+        <v>779</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>12</v>
@@ -10804,8 +9524,8 @@
       <c r="G242" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H242" s="1" t="s">
-        <v>776</v>
+      <c r="H242" s="5">
+        <v>30222</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
@@ -10813,7 +9533,7 @@
         <v>259</v>
       </c>
       <c r="B243" t="s">
-        <v>1210</v>
+        <v>780</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>10</v>
@@ -10830,8 +9550,8 @@
       <c r="G243" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H243" s="1" t="s">
-        <v>777</v>
+      <c r="H243" s="5">
+        <v>24063</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
@@ -10839,7 +9559,7 @@
         <v>260</v>
       </c>
       <c r="B244" t="s">
-        <v>1211</v>
+        <v>781</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>7</v>
@@ -10856,8 +9576,8 @@
       <c r="G244" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H244" s="1" t="s">
-        <v>778</v>
+      <c r="H244" s="5">
+        <v>27155</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
@@ -10865,7 +9585,7 @@
         <v>261</v>
       </c>
       <c r="B245" t="s">
-        <v>1212</v>
+        <v>782</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>7</v>
@@ -10882,8 +9602,8 @@
       <c r="G245" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H245" s="1" t="s">
-        <v>779</v>
+      <c r="H245" s="5">
+        <v>27626</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
@@ -10891,7 +9611,7 @@
         <v>262</v>
       </c>
       <c r="B246" t="s">
-        <v>1213</v>
+        <v>783</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>10</v>
@@ -10908,8 +9628,8 @@
       <c r="G246" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H246" s="1" t="s">
-        <v>780</v>
+      <c r="H246" s="5">
+        <v>29222</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
@@ -10917,7 +9637,7 @@
         <v>263</v>
       </c>
       <c r="B247" t="s">
-        <v>1214</v>
+        <v>784</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>7</v>
@@ -10934,8 +9654,8 @@
       <c r="G247" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H247" s="1" t="s">
-        <v>781</v>
+      <c r="H247" s="5">
+        <v>28722</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -10943,7 +9663,7 @@
         <v>264</v>
       </c>
       <c r="B248" t="s">
-        <v>1215</v>
+        <v>785</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>11</v>
@@ -10960,8 +9680,8 @@
       <c r="G248" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H248" s="1" t="s">
-        <v>782</v>
+      <c r="H248" s="5">
+        <v>32714</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
@@ -10969,7 +9689,7 @@
         <v>265</v>
       </c>
       <c r="B249" t="s">
-        <v>1216</v>
+        <v>786</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>7</v>
@@ -10986,8 +9706,8 @@
       <c r="G249" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H249" s="1" t="s">
-        <v>783</v>
+      <c r="H249" s="5">
+        <v>27577</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -10995,7 +9715,7 @@
         <v>266</v>
       </c>
       <c r="B250" t="s">
-        <v>1217</v>
+        <v>787</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>17</v>
@@ -11012,8 +9732,8 @@
       <c r="G250" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H250" s="1" t="s">
-        <v>784</v>
+      <c r="H250" s="5">
+        <v>31325</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
@@ -11021,7 +9741,7 @@
         <v>267</v>
       </c>
       <c r="B251" t="s">
-        <v>1218</v>
+        <v>788</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>7</v>
@@ -11038,8 +9758,8 @@
       <c r="G251" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H251" s="1" t="s">
-        <v>785</v>
+      <c r="H251" s="5">
+        <v>34850</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -11047,7 +9767,7 @@
         <v>268</v>
       </c>
       <c r="B252" t="s">
-        <v>1219</v>
+        <v>789</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>7</v>
@@ -11064,8 +9784,8 @@
       <c r="G252" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H252" s="1" t="s">
-        <v>786</v>
+      <c r="H252" s="5">
+        <v>30918</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -11073,7 +9793,7 @@
         <v>269</v>
       </c>
       <c r="B253" t="s">
-        <v>1220</v>
+        <v>790</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>7</v>
@@ -11090,8 +9810,8 @@
       <c r="G253" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H253" s="1" t="s">
-        <v>787</v>
+      <c r="H253" s="5">
+        <v>22491</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
@@ -11099,7 +9819,7 @@
         <v>270</v>
       </c>
       <c r="B254" t="s">
-        <v>1221</v>
+        <v>791</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>7</v>
@@ -11116,8 +9836,8 @@
       <c r="G254" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H254" s="1" t="s">
-        <v>788</v>
+      <c r="H254" s="5">
+        <v>23407</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
@@ -11125,7 +9845,7 @@
         <v>271</v>
       </c>
       <c r="B255" t="s">
-        <v>1222</v>
+        <v>792</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>10</v>
@@ -11142,8 +9862,8 @@
       <c r="G255" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H255" s="1" t="s">
-        <v>789</v>
+      <c r="H255" s="5">
+        <v>32422</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
@@ -11151,7 +9871,7 @@
         <v>272</v>
       </c>
       <c r="B256" t="s">
-        <v>1223</v>
+        <v>793</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>11</v>
@@ -11168,8 +9888,8 @@
       <c r="G256" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H256" s="1" t="s">
-        <v>790</v>
+      <c r="H256" s="5">
+        <v>34891</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
@@ -11177,7 +9897,7 @@
         <v>273</v>
       </c>
       <c r="B257" t="s">
-        <v>1224</v>
+        <v>794</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>9</v>
@@ -11194,8 +9914,8 @@
       <c r="G257" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H257" s="1" t="s">
-        <v>791</v>
+      <c r="H257" s="5">
+        <v>29048</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
@@ -11203,7 +9923,7 @@
         <v>274</v>
       </c>
       <c r="B258" t="s">
-        <v>1225</v>
+        <v>795</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>7</v>
@@ -11220,8 +9940,8 @@
       <c r="G258" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H258" s="1" t="s">
-        <v>792</v>
+      <c r="H258" s="5">
+        <v>32596</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
@@ -11229,7 +9949,7 @@
         <v>275</v>
       </c>
       <c r="B259" t="s">
-        <v>1226</v>
+        <v>796</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>11</v>
@@ -11246,8 +9966,8 @@
       <c r="G259" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H259" s="1" t="s">
-        <v>793</v>
+      <c r="H259" s="5">
+        <v>36627</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
@@ -11255,7 +9975,7 @@
         <v>276</v>
       </c>
       <c r="B260" t="s">
-        <v>1227</v>
+        <v>797</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>7</v>
@@ -11272,8 +9992,8 @@
       <c r="G260" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H260" s="1" t="s">
-        <v>794</v>
+      <c r="H260" s="5">
+        <v>24450</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
@@ -11281,7 +10001,7 @@
         <v>277</v>
       </c>
       <c r="B261" t="s">
-        <v>1228</v>
+        <v>798</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>7</v>
@@ -11298,8 +10018,8 @@
       <c r="G261" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H261" s="1" t="s">
-        <v>795</v>
+      <c r="H261" s="5">
+        <v>25279</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
@@ -11307,7 +10027,7 @@
         <v>278</v>
       </c>
       <c r="B262" t="s">
-        <v>1229</v>
+        <v>799</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>7</v>
@@ -11324,8 +10044,8 @@
       <c r="G262" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H262" s="1" t="s">
-        <v>796</v>
+      <c r="H262" s="5">
+        <v>30614</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
@@ -11333,7 +10053,7 @@
         <v>279</v>
       </c>
       <c r="B263" t="s">
-        <v>1230</v>
+        <v>800</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>7</v>
@@ -11350,8 +10070,8 @@
       <c r="G263" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H263" s="1" t="s">
-        <v>797</v>
+      <c r="H263" s="5">
+        <v>31801</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
@@ -11359,7 +10079,7 @@
         <v>280</v>
       </c>
       <c r="B264" t="s">
-        <v>1231</v>
+        <v>801</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>7</v>
@@ -11376,8 +10096,8 @@
       <c r="G264" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H264" s="1" t="s">
-        <v>798</v>
+      <c r="H264" s="5">
+        <v>26074</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
@@ -11385,7 +10105,7 @@
         <v>281</v>
       </c>
       <c r="B265" t="s">
-        <v>1232</v>
+        <v>802</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>12</v>
@@ -11402,8 +10122,8 @@
       <c r="G265" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H265" s="1" t="s">
-        <v>799</v>
+      <c r="H265" s="5">
+        <v>31007</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
@@ -11411,7 +10131,7 @@
         <v>282</v>
       </c>
       <c r="B266" t="s">
-        <v>1233</v>
+        <v>803</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>7</v>
@@ -11428,8 +10148,8 @@
       <c r="G266" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H266" s="1" t="s">
-        <v>800</v>
+      <c r="H266" s="5">
+        <v>24200</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
@@ -11437,7 +10157,7 @@
         <v>283</v>
       </c>
       <c r="B267" t="s">
-        <v>1234</v>
+        <v>804</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>7</v>
@@ -11454,8 +10174,8 @@
       <c r="G267" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H267" s="1" t="s">
-        <v>553</v>
+      <c r="H267" s="5">
+        <v>30211</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.2">
@@ -11463,7 +10183,7 @@
         <v>284</v>
       </c>
       <c r="B268" t="s">
-        <v>1235</v>
+        <v>805</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>12</v>
@@ -11480,8 +10200,8 @@
       <c r="G268" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H268" s="1" t="s">
-        <v>801</v>
+      <c r="H268" s="5">
+        <v>30731</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.2">
@@ -11489,7 +10209,7 @@
         <v>285</v>
       </c>
       <c r="B269" t="s">
-        <v>1236</v>
+        <v>806</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>8</v>
@@ -11506,8 +10226,8 @@
       <c r="G269" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H269" s="1" t="s">
-        <v>802</v>
+      <c r="H269" s="5">
+        <v>33480</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.2">
@@ -11515,7 +10235,7 @@
         <v>286</v>
       </c>
       <c r="B270" t="s">
-        <v>1237</v>
+        <v>807</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>7</v>
@@ -11532,8 +10252,8 @@
       <c r="G270" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H270" s="1" t="s">
-        <v>803</v>
+      <c r="H270" s="5">
+        <v>29425</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.2">
@@ -11541,7 +10261,7 @@
         <v>287</v>
       </c>
       <c r="B271" t="s">
-        <v>1238</v>
+        <v>808</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>9</v>
@@ -11558,8 +10278,8 @@
       <c r="G271" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H271" s="1" t="s">
-        <v>804</v>
+      <c r="H271" s="5">
+        <v>34169</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.2">
@@ -11567,7 +10287,7 @@
         <v>287</v>
       </c>
       <c r="B272" t="s">
-        <v>1238</v>
+        <v>808</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>10</v>
@@ -11584,8 +10304,8 @@
       <c r="G272" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H272" s="1" t="s">
-        <v>804</v>
+      <c r="H272" s="5">
+        <v>34169</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.2">
@@ -11593,7 +10313,7 @@
         <v>287</v>
       </c>
       <c r="B273" t="s">
-        <v>1238</v>
+        <v>808</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>7</v>
@@ -11610,8 +10330,8 @@
       <c r="G273" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H273" s="1" t="s">
-        <v>804</v>
+      <c r="H273" s="5">
+        <v>34169</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.2">
@@ -11619,7 +10339,7 @@
         <v>288</v>
       </c>
       <c r="B274" t="s">
-        <v>1239</v>
+        <v>809</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>7</v>
@@ -11636,8 +10356,8 @@
       <c r="G274" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H274" s="1" t="s">
-        <v>805</v>
+      <c r="H274" s="5">
+        <v>33194</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
@@ -11645,7 +10365,7 @@
         <v>289</v>
       </c>
       <c r="B275" t="s">
-        <v>1240</v>
+        <v>810</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>7</v>
@@ -11662,8 +10382,8 @@
       <c r="G275" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H275" s="1" t="s">
-        <v>806</v>
+      <c r="H275" s="5">
+        <v>27885</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.2">
@@ -11671,7 +10391,7 @@
         <v>290</v>
       </c>
       <c r="B276" t="s">
-        <v>1241</v>
+        <v>811</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>9</v>
@@ -11688,8 +10408,8 @@
       <c r="G276" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H276" s="1" t="s">
-        <v>807</v>
+      <c r="H276" s="5">
+        <v>22961</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.2">
@@ -11697,7 +10417,7 @@
         <v>291</v>
       </c>
       <c r="B277" t="s">
-        <v>1242</v>
+        <v>812</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>7</v>
@@ -11714,8 +10434,8 @@
       <c r="G277" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H277" s="1" t="s">
-        <v>808</v>
+      <c r="H277" s="5">
+        <v>36344</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.2">
@@ -11723,7 +10443,7 @@
         <v>292</v>
       </c>
       <c r="B278" t="s">
-        <v>1243</v>
+        <v>813</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>7</v>
@@ -11740,8 +10460,8 @@
       <c r="G278" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H278" s="1" t="s">
-        <v>809</v>
+      <c r="H278" s="5">
+        <v>23470</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
@@ -11749,7 +10469,7 @@
         <v>293</v>
       </c>
       <c r="B279" t="s">
-        <v>1244</v>
+        <v>814</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>9</v>
@@ -11766,8 +10486,8 @@
       <c r="G279" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H279" s="1" t="s">
-        <v>810</v>
+      <c r="H279" s="5">
+        <v>27210</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.2">
@@ -11775,7 +10495,7 @@
         <v>294</v>
       </c>
       <c r="B280" t="s">
-        <v>1245</v>
+        <v>815</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>9</v>
@@ -11792,8 +10512,8 @@
       <c r="G280" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H280" s="1" t="s">
-        <v>811</v>
+      <c r="H280" s="5">
+        <v>29959</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
@@ -11801,7 +10521,7 @@
         <v>295</v>
       </c>
       <c r="B281" t="s">
-        <v>1246</v>
+        <v>816</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>8</v>
@@ -11818,8 +10538,8 @@
       <c r="G281" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H281" s="1" t="s">
-        <v>812</v>
+      <c r="H281" s="5">
+        <v>31762</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.2">
@@ -11827,7 +10547,7 @@
         <v>296</v>
       </c>
       <c r="B282" t="s">
-        <v>1247</v>
+        <v>817</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>7</v>
@@ -11844,8 +10564,8 @@
       <c r="G282" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H282" s="1" t="s">
-        <v>813</v>
+      <c r="H282" s="5">
+        <v>34493</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.2">
@@ -11853,7 +10573,7 @@
         <v>297</v>
       </c>
       <c r="B283" t="s">
-        <v>1248</v>
+        <v>818</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>10</v>
@@ -11870,8 +10590,8 @@
       <c r="G283" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H283" s="1" t="s">
-        <v>814</v>
+      <c r="H283" s="5">
+        <v>35087</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.2">
@@ -11879,7 +10599,7 @@
         <v>298</v>
       </c>
       <c r="B284" t="s">
-        <v>1249</v>
+        <v>819</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>7</v>
@@ -11896,8 +10616,8 @@
       <c r="G284" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H284" s="1" t="s">
-        <v>815</v>
+      <c r="H284" s="5">
+        <v>32992</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.2">
@@ -11905,7 +10625,7 @@
         <v>299</v>
       </c>
       <c r="B285" t="s">
-        <v>1250</v>
+        <v>820</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>11</v>
@@ -11922,8 +10642,8 @@
       <c r="G285" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H285" s="1" t="s">
-        <v>816</v>
+      <c r="H285" s="5">
+        <v>29820</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
@@ -11931,7 +10651,7 @@
         <v>300</v>
       </c>
       <c r="B286" t="s">
-        <v>1251</v>
+        <v>821</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>7</v>
@@ -11948,8 +10668,8 @@
       <c r="G286" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H286" s="1" t="s">
-        <v>817</v>
+      <c r="H286" s="5">
+        <v>33788</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.2">
@@ -11957,7 +10677,7 @@
         <v>301</v>
       </c>
       <c r="B287" t="s">
-        <v>1252</v>
+        <v>822</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>7</v>
@@ -11974,8 +10694,8 @@
       <c r="G287" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H287" s="1" t="s">
-        <v>818</v>
+      <c r="H287" s="5">
+        <v>31062</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.2">
@@ -11983,7 +10703,7 @@
         <v>302</v>
       </c>
       <c r="B288" t="s">
-        <v>1253</v>
+        <v>823</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>10</v>
@@ -12000,8 +10720,8 @@
       <c r="G288" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H288" s="1" t="s">
-        <v>819</v>
+      <c r="H288" s="5">
+        <v>34886</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.2">
@@ -12009,7 +10729,7 @@
         <v>303</v>
       </c>
       <c r="B289" t="s">
-        <v>1254</v>
+        <v>824</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>8</v>
@@ -12026,8 +10746,8 @@
       <c r="G289" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H289" s="1" t="s">
-        <v>820</v>
+      <c r="H289" s="5">
+        <v>30196</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.2">
@@ -12035,7 +10755,7 @@
         <v>304</v>
       </c>
       <c r="B290" t="s">
-        <v>1255</v>
+        <v>825</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>9</v>
@@ -12052,8 +10772,8 @@
       <c r="G290" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H290" s="1" t="s">
-        <v>821</v>
+      <c r="H290" s="5">
+        <v>31107</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
@@ -12061,7 +10781,7 @@
         <v>305</v>
       </c>
       <c r="B291" t="s">
-        <v>1256</v>
+        <v>826</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>17</v>
@@ -12078,8 +10798,8 @@
       <c r="G291" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H291" s="1" t="s">
-        <v>822</v>
+      <c r="H291" s="5">
+        <v>33921</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.2">
@@ -12087,7 +10807,7 @@
         <v>306</v>
       </c>
       <c r="B292" t="s">
-        <v>1257</v>
+        <v>827</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>7</v>
@@ -12104,8 +10824,8 @@
       <c r="G292" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H292" s="1" t="s">
-        <v>823</v>
+      <c r="H292" s="5">
+        <v>33452</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.2">
@@ -12113,7 +10833,7 @@
         <v>307</v>
       </c>
       <c r="B293" t="s">
-        <v>1258</v>
+        <v>828</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>10</v>
@@ -12130,8 +10850,8 @@
       <c r="G293" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H293" s="1" t="s">
-        <v>824</v>
+      <c r="H293" s="5">
+        <v>35719</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
@@ -12139,7 +10859,7 @@
         <v>308</v>
       </c>
       <c r="B294" t="s">
-        <v>1259</v>
+        <v>829</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>10</v>
@@ -12156,8 +10876,8 @@
       <c r="G294" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H294" s="1" t="s">
-        <v>825</v>
+      <c r="H294" s="5">
+        <v>28954</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.2">
@@ -12165,7 +10885,7 @@
         <v>309</v>
       </c>
       <c r="B295" t="s">
-        <v>1260</v>
+        <v>830</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>12</v>
@@ -12182,8 +10902,8 @@
       <c r="G295" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H295" s="1" t="s">
-        <v>826</v>
+      <c r="H295" s="5">
+        <v>29081</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
@@ -12191,7 +10911,7 @@
         <v>310</v>
       </c>
       <c r="B296" t="s">
-        <v>1261</v>
+        <v>831</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>7</v>
@@ -12208,8 +10928,8 @@
       <c r="G296" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H296" s="1" t="s">
-        <v>827</v>
+      <c r="H296" s="5">
+        <v>32737</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.2">
@@ -12217,7 +10937,7 @@
         <v>311</v>
       </c>
       <c r="B297" t="s">
-        <v>1262</v>
+        <v>832</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>7</v>
@@ -12234,8 +10954,8 @@
       <c r="G297" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H297" s="1" t="s">
-        <v>828</v>
+      <c r="H297" s="5">
+        <v>29818</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.2">
@@ -12243,7 +10963,7 @@
         <v>312</v>
       </c>
       <c r="B298" t="s">
-        <v>1263</v>
+        <v>833</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>12</v>
@@ -12260,8 +10980,8 @@
       <c r="G298" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H298" s="1" t="s">
-        <v>829</v>
+      <c r="H298" s="5">
+        <v>34876</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.2">
@@ -12269,7 +10989,7 @@
         <v>313</v>
       </c>
       <c r="B299" t="s">
-        <v>1264</v>
+        <v>834</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>7</v>
@@ -12286,8 +11006,8 @@
       <c r="G299" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H299" s="1" t="s">
-        <v>830</v>
+      <c r="H299" s="5">
+        <v>33793</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.2">
@@ -12295,7 +11015,7 @@
         <v>314</v>
       </c>
       <c r="B300" t="s">
-        <v>1265</v>
+        <v>835</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>8</v>
@@ -12312,8 +11032,8 @@
       <c r="G300" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H300" s="1" t="s">
-        <v>831</v>
+      <c r="H300" s="5">
+        <v>33661</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.2">
@@ -12321,7 +11041,7 @@
         <v>315</v>
       </c>
       <c r="B301" t="s">
-        <v>1266</v>
+        <v>836</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>14</v>
@@ -12338,8 +11058,8 @@
       <c r="G301" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H301" s="1" t="s">
-        <v>832</v>
+      <c r="H301" s="5">
+        <v>29061</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.2">
@@ -12347,7 +11067,7 @@
         <v>316</v>
       </c>
       <c r="B302" t="s">
-        <v>1267</v>
+        <v>837</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>11</v>
@@ -12364,8 +11084,8 @@
       <c r="G302" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H302" s="1" t="s">
-        <v>833</v>
+      <c r="H302" s="5">
+        <v>33939</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.2">
@@ -12373,7 +11093,7 @@
         <v>317</v>
       </c>
       <c r="B303" t="s">
-        <v>1268</v>
+        <v>838</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>11</v>
@@ -12390,8 +11110,8 @@
       <c r="G303" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H303" s="1" t="s">
-        <v>834</v>
+      <c r="H303" s="5">
+        <v>29277</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.2">
@@ -12399,7 +11119,7 @@
         <v>317</v>
       </c>
       <c r="B304" t="s">
-        <v>1268</v>
+        <v>838</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>9</v>
@@ -12416,8 +11136,8 @@
       <c r="G304" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H304" s="1" t="s">
-        <v>834</v>
+      <c r="H304" s="5">
+        <v>29277</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.2">
@@ -12425,7 +11145,7 @@
         <v>318</v>
       </c>
       <c r="B305" t="s">
-        <v>1269</v>
+        <v>839</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>10</v>
@@ -12442,8 +11162,8 @@
       <c r="G305" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H305" s="1" t="s">
-        <v>835</v>
+      <c r="H305" s="5">
+        <v>29438</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.2">
@@ -12451,7 +11171,7 @@
         <v>319</v>
       </c>
       <c r="B306" t="s">
-        <v>1270</v>
+        <v>840</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>14</v>
@@ -12468,8 +11188,8 @@
       <c r="G306" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H306" s="1" t="s">
-        <v>836</v>
+      <c r="H306" s="5">
+        <v>33065</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.2">
@@ -12477,7 +11197,7 @@
         <v>320</v>
       </c>
       <c r="B307" t="s">
-        <v>1271</v>
+        <v>841</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>8</v>
@@ -12494,8 +11214,8 @@
       <c r="G307" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H307" s="1" t="s">
-        <v>837</v>
+      <c r="H307" s="5">
+        <v>29826</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.2">
@@ -12503,7 +11223,7 @@
         <v>321</v>
       </c>
       <c r="B308" t="s">
-        <v>1272</v>
+        <v>842</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>10</v>
@@ -12520,8 +11240,8 @@
       <c r="G308" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H308" s="1" t="s">
-        <v>838</v>
+      <c r="H308" s="5">
+        <v>34257</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.2">
@@ -12529,7 +11249,7 @@
         <v>322</v>
       </c>
       <c r="B309" t="s">
-        <v>1273</v>
+        <v>843</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>7</v>
@@ -12546,8 +11266,8 @@
       <c r="G309" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H309" s="1" t="s">
-        <v>839</v>
+      <c r="H309" s="5">
+        <v>24186</v>
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.2">
@@ -12555,7 +11275,7 @@
         <v>323</v>
       </c>
       <c r="B310" t="s">
-        <v>1274</v>
+        <v>844</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>12</v>
@@ -12572,8 +11292,8 @@
       <c r="G310" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H310" s="1" t="s">
-        <v>840</v>
+      <c r="H310" s="5">
+        <v>35382</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.2">
@@ -12581,7 +11301,7 @@
         <v>324</v>
       </c>
       <c r="B311" t="s">
-        <v>1275</v>
+        <v>845</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>17</v>
@@ -12598,8 +11318,8 @@
       <c r="G311" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H311" s="1" t="s">
-        <v>841</v>
+      <c r="H311" s="5">
+        <v>36529</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.2">
@@ -12607,7 +11327,7 @@
         <v>325</v>
       </c>
       <c r="B312" t="s">
-        <v>1276</v>
+        <v>846</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>11</v>
@@ -12624,8 +11344,8 @@
       <c r="G312" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H312" s="1" t="s">
-        <v>842</v>
+      <c r="H312" s="5">
+        <v>31262</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
@@ -12633,7 +11353,7 @@
         <v>326</v>
       </c>
       <c r="B313" t="s">
-        <v>1277</v>
+        <v>847</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>7</v>
@@ -12650,8 +11370,8 @@
       <c r="G313" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H313" s="1" t="s">
-        <v>843</v>
+      <c r="H313" s="5">
+        <v>33882</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
@@ -12659,7 +11379,7 @@
         <v>327</v>
       </c>
       <c r="B314" t="s">
-        <v>1278</v>
+        <v>848</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>7</v>
@@ -12676,8 +11396,8 @@
       <c r="G314" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H314" s="1" t="s">
-        <v>844</v>
+      <c r="H314" s="5">
+        <v>34506</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
@@ -12685,7 +11405,7 @@
         <v>328</v>
       </c>
       <c r="B315" t="s">
-        <v>1279</v>
+        <v>849</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>10</v>
@@ -12702,8 +11422,8 @@
       <c r="G315" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H315" s="1" t="s">
-        <v>845</v>
+      <c r="H315" s="5">
+        <v>32261</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.2">
@@ -12711,7 +11431,7 @@
         <v>329</v>
       </c>
       <c r="B316" t="s">
-        <v>1280</v>
+        <v>850</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>7</v>
@@ -12728,8 +11448,8 @@
       <c r="G316" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H316" s="1" t="s">
-        <v>846</v>
+      <c r="H316" s="5">
+        <v>33613</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.2">
@@ -12737,7 +11457,7 @@
         <v>330</v>
       </c>
       <c r="B317" t="s">
-        <v>1281</v>
+        <v>851</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>7</v>
@@ -12754,8 +11474,8 @@
       <c r="G317" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H317" s="1" t="s">
-        <v>847</v>
+      <c r="H317" s="5">
+        <v>23237</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
@@ -12763,7 +11483,7 @@
         <v>331</v>
       </c>
       <c r="B318" t="s">
-        <v>1282</v>
+        <v>852</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>12</v>
@@ -12780,8 +11500,8 @@
       <c r="G318" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H318" s="1" t="s">
-        <v>848</v>
+      <c r="H318" s="5">
+        <v>24608</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
@@ -12789,7 +11509,7 @@
         <v>332</v>
       </c>
       <c r="B319" t="s">
-        <v>1283</v>
+        <v>853</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>11</v>
@@ -12806,8 +11526,8 @@
       <c r="G319" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H319" s="1" t="s">
-        <v>849</v>
+      <c r="H319" s="5">
+        <v>34448</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
@@ -12815,7 +11535,7 @@
         <v>333</v>
       </c>
       <c r="B320" t="s">
-        <v>1284</v>
+        <v>854</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>11</v>
@@ -12832,8 +11552,8 @@
       <c r="G320" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H320" s="1" t="s">
-        <v>850</v>
+      <c r="H320" s="5">
+        <v>34614</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.2">
@@ -12841,7 +11561,7 @@
         <v>334</v>
       </c>
       <c r="B321" t="s">
-        <v>1285</v>
+        <v>855</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>7</v>
@@ -12858,8 +11578,8 @@
       <c r="G321" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H321" s="1" t="s">
-        <v>851</v>
+      <c r="H321" s="5">
+        <v>28714</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">
@@ -12867,7 +11587,7 @@
         <v>335</v>
       </c>
       <c r="B322" t="s">
-        <v>1286</v>
+        <v>856</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>10</v>
@@ -12884,8 +11604,8 @@
       <c r="G322" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H322" s="1" t="s">
-        <v>852</v>
+      <c r="H322" s="5">
+        <v>31000</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
@@ -12893,7 +11613,7 @@
         <v>336</v>
       </c>
       <c r="B323" t="s">
-        <v>1287</v>
+        <v>857</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>18</v>
@@ -12910,8 +11630,8 @@
       <c r="G323" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H323" s="1" t="s">
-        <v>853</v>
+      <c r="H323" s="5">
+        <v>32576</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.2">
@@ -12919,7 +11639,7 @@
         <v>337</v>
       </c>
       <c r="B324" t="s">
-        <v>1288</v>
+        <v>858</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>7</v>
@@ -12936,8 +11656,8 @@
       <c r="G324" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H324" s="1" t="s">
-        <v>854</v>
+      <c r="H324" s="5">
+        <v>34478</v>
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
@@ -12945,7 +11665,7 @@
         <v>338</v>
       </c>
       <c r="B325" t="s">
-        <v>1289</v>
+        <v>859</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>11</v>
@@ -12962,8 +11682,8 @@
       <c r="G325" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H325" s="1" t="s">
-        <v>855</v>
+      <c r="H325" s="5">
+        <v>29635</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
@@ -12971,7 +11691,7 @@
         <v>339</v>
       </c>
       <c r="B326" t="s">
-        <v>1290</v>
+        <v>860</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>7</v>
@@ -12988,8 +11708,8 @@
       <c r="G326" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H326" s="1" t="s">
-        <v>856</v>
+      <c r="H326" s="5">
+        <v>33975</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
@@ -12997,7 +11717,7 @@
         <v>340</v>
       </c>
       <c r="B327" t="s">
-        <v>1291</v>
+        <v>861</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>7</v>
@@ -13014,8 +11734,8 @@
       <c r="G327" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H327" s="1" t="s">
-        <v>857</v>
+      <c r="H327" s="5">
+        <v>32890</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
@@ -13023,7 +11743,7 @@
         <v>341</v>
       </c>
       <c r="B328" t="s">
-        <v>1292</v>
+        <v>862</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>16</v>
@@ -13040,8 +11760,8 @@
       <c r="G328" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H328" s="1" t="s">
-        <v>858</v>
+      <c r="H328" s="5">
+        <v>28935</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
@@ -13049,7 +11769,7 @@
         <v>342</v>
       </c>
       <c r="B329" t="s">
-        <v>1293</v>
+        <v>863</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>12</v>
@@ -13066,8 +11786,8 @@
       <c r="G329" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H329" s="1" t="s">
-        <v>859</v>
+      <c r="H329" s="5">
+        <v>34979</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
@@ -13075,7 +11795,7 @@
         <v>343</v>
       </c>
       <c r="B330" t="s">
-        <v>1294</v>
+        <v>864</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>17</v>
@@ -13092,8 +11812,8 @@
       <c r="G330" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H330" s="1" t="s">
-        <v>860</v>
+      <c r="H330" s="5">
+        <v>35989</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
@@ -13101,7 +11821,7 @@
         <v>344</v>
       </c>
       <c r="B331" t="s">
-        <v>1295</v>
+        <v>865</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>17</v>
@@ -13118,8 +11838,8 @@
       <c r="G331" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H331" s="1" t="s">
-        <v>861</v>
+      <c r="H331" s="5">
+        <v>29320</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
@@ -13127,7 +11847,7 @@
         <v>345</v>
       </c>
       <c r="B332" t="s">
-        <v>1296</v>
+        <v>866</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>7</v>
@@ -13144,8 +11864,8 @@
       <c r="G332" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H332" s="1" t="s">
-        <v>862</v>
+      <c r="H332" s="5">
+        <v>33853</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
@@ -13153,7 +11873,7 @@
         <v>346</v>
       </c>
       <c r="B333" t="s">
-        <v>1297</v>
+        <v>867</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>10</v>
@@ -13170,8 +11890,8 @@
       <c r="G333" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H333" s="1" t="s">
-        <v>863</v>
+      <c r="H333" s="5">
+        <v>26479</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
@@ -13179,7 +11899,7 @@
         <v>347</v>
       </c>
       <c r="B334" t="s">
-        <v>1298</v>
+        <v>868</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>10</v>
@@ -13196,8 +11916,8 @@
       <c r="G334" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H334" s="1" t="s">
-        <v>864</v>
+      <c r="H334" s="5">
+        <v>33812</v>
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
@@ -13205,7 +11925,7 @@
         <v>348</v>
       </c>
       <c r="B335" t="s">
-        <v>1299</v>
+        <v>869</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>7</v>
@@ -13222,8 +11942,8 @@
       <c r="G335" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H335" s="1" t="s">
-        <v>865</v>
+      <c r="H335" s="5">
+        <v>25282</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
@@ -13231,7 +11951,7 @@
         <v>349</v>
       </c>
       <c r="B336" t="s">
-        <v>1300</v>
+        <v>870</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>7</v>
@@ -13248,8 +11968,8 @@
       <c r="G336" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H336" s="1" t="s">
-        <v>866</v>
+      <c r="H336" s="5">
+        <v>33725</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
@@ -13257,7 +11977,7 @@
         <v>350</v>
       </c>
       <c r="B337" t="s">
-        <v>1301</v>
+        <v>871</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>7</v>
@@ -13274,8 +11994,8 @@
       <c r="G337" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H337" s="1" t="s">
-        <v>867</v>
+      <c r="H337" s="5">
+        <v>34909</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
@@ -13283,7 +12003,7 @@
         <v>351</v>
       </c>
       <c r="B338" t="s">
-        <v>1302</v>
+        <v>872</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>13</v>
@@ -13300,8 +12020,8 @@
       <c r="G338" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H338" s="1" t="s">
-        <v>868</v>
+      <c r="H338" s="5">
+        <v>35096</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
@@ -13309,7 +12029,7 @@
         <v>352</v>
       </c>
       <c r="B339" t="s">
-        <v>1303</v>
+        <v>873</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>7</v>
@@ -13326,8 +12046,8 @@
       <c r="G339" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H339" s="1" t="s">
-        <v>869</v>
+      <c r="H339" s="5">
+        <v>29764</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
@@ -13335,7 +12055,7 @@
         <v>353</v>
       </c>
       <c r="B340" t="s">
-        <v>1304</v>
+        <v>874</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>8</v>
@@ -13352,8 +12072,8 @@
       <c r="G340" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H340" s="1" t="s">
-        <v>870</v>
+      <c r="H340" s="5">
+        <v>32362</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
@@ -13361,7 +12081,7 @@
         <v>354</v>
       </c>
       <c r="B341" t="s">
-        <v>1305</v>
+        <v>875</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>12</v>
@@ -13378,8 +12098,8 @@
       <c r="G341" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H341" s="1" t="s">
-        <v>871</v>
+      <c r="H341" s="5">
+        <v>32483</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
@@ -13387,7 +12107,7 @@
         <v>355</v>
       </c>
       <c r="B342" t="s">
-        <v>1306</v>
+        <v>876</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>7</v>
@@ -13404,8 +12124,8 @@
       <c r="G342" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H342" s="1" t="s">
-        <v>872</v>
+      <c r="H342" s="5">
+        <v>33180</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
@@ -13413,7 +12133,7 @@
         <v>356</v>
       </c>
       <c r="B343" t="s">
-        <v>1307</v>
+        <v>877</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>7</v>
@@ -13430,8 +12150,8 @@
       <c r="G343" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H343" s="1" t="s">
-        <v>873</v>
+      <c r="H343" s="5">
+        <v>34139</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
@@ -13439,7 +12159,7 @@
         <v>357</v>
       </c>
       <c r="B344" t="s">
-        <v>1308</v>
+        <v>878</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>10</v>
@@ -13456,8 +12176,8 @@
       <c r="G344" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H344" s="1" t="s">
-        <v>874</v>
+      <c r="H344" s="5">
+        <v>30737</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
@@ -13465,7 +12185,7 @@
         <v>358</v>
       </c>
       <c r="B345" t="s">
-        <v>1309</v>
+        <v>879</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>7</v>
@@ -13482,8 +12202,8 @@
       <c r="G345" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H345" s="1" t="s">
-        <v>875</v>
+      <c r="H345" s="5">
+        <v>25300</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
@@ -13491,7 +12211,7 @@
         <v>359</v>
       </c>
       <c r="B346" t="s">
-        <v>1310</v>
+        <v>880</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>9</v>
@@ -13508,8 +12228,8 @@
       <c r="G346" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H346" s="1" t="s">
-        <v>876</v>
+      <c r="H346" s="5">
+        <v>32097</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
@@ -13517,7 +12237,7 @@
         <v>360</v>
       </c>
       <c r="B347" t="s">
-        <v>1311</v>
+        <v>881</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>7</v>
@@ -13534,8 +12254,8 @@
       <c r="G347" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H347" s="1" t="s">
-        <v>877</v>
+      <c r="H347" s="5">
+        <v>26603</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
@@ -13543,7 +12263,7 @@
         <v>361</v>
       </c>
       <c r="B348" t="s">
-        <v>1312</v>
+        <v>882</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>10</v>
@@ -13560,8 +12280,8 @@
       <c r="G348" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H348" s="1" t="s">
-        <v>878</v>
+      <c r="H348" s="5">
+        <v>30218</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
@@ -13569,7 +12289,7 @@
         <v>362</v>
       </c>
       <c r="B349" t="s">
-        <v>1313</v>
+        <v>883</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>11</v>
@@ -13586,8 +12306,8 @@
       <c r="G349" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H349" s="1" t="s">
-        <v>879</v>
+      <c r="H349" s="5">
+        <v>34743</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
@@ -13595,7 +12315,7 @@
         <v>363</v>
       </c>
       <c r="B350" t="s">
-        <v>1314</v>
+        <v>884</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>10</v>
@@ -13612,8 +12332,8 @@
       <c r="G350" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H350" s="1" t="s">
-        <v>880</v>
+      <c r="H350" s="5">
+        <v>32131</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
@@ -13621,7 +12341,7 @@
         <v>364</v>
       </c>
       <c r="B351" t="s">
-        <v>1315</v>
+        <v>885</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>7</v>
@@ -13638,8 +12358,8 @@
       <c r="G351" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H351" s="1" t="s">
-        <v>881</v>
+      <c r="H351" s="5">
+        <v>24062</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
@@ -13647,7 +12367,7 @@
         <v>365</v>
       </c>
       <c r="B352" t="s">
-        <v>1316</v>
+        <v>886</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>7</v>
@@ -13664,8 +12384,8 @@
       <c r="G352" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H352" s="1" t="s">
-        <v>882</v>
+      <c r="H352" s="5">
+        <v>34125</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
@@ -13673,7 +12393,7 @@
         <v>366</v>
       </c>
       <c r="B353" t="s">
-        <v>1317</v>
+        <v>887</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>7</v>
@@ -13690,8 +12410,8 @@
       <c r="G353" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H353" s="1" t="s">
-        <v>883</v>
+      <c r="H353" s="5">
+        <v>28081</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
@@ -13699,7 +12419,7 @@
         <v>367</v>
       </c>
       <c r="B354" t="s">
-        <v>1318</v>
+        <v>888</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>10</v>
@@ -13716,8 +12436,8 @@
       <c r="G354" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H354" s="1" t="s">
-        <v>884</v>
+      <c r="H354" s="5">
+        <v>32911</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
@@ -13725,7 +12445,7 @@
         <v>368</v>
       </c>
       <c r="B355" t="s">
-        <v>1319</v>
+        <v>889</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>7</v>
@@ -13742,8 +12462,8 @@
       <c r="G355" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H355" s="1" t="s">
-        <v>885</v>
+      <c r="H355" s="5">
+        <v>31669</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
@@ -13751,7 +12471,7 @@
         <v>369</v>
       </c>
       <c r="B356" t="s">
-        <v>1320</v>
+        <v>890</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>7</v>
@@ -13768,8 +12488,8 @@
       <c r="G356" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H356" s="1" t="s">
-        <v>886</v>
+      <c r="H356" s="5">
+        <v>32725</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
@@ -13777,7 +12497,7 @@
         <v>370</v>
       </c>
       <c r="B357" t="s">
-        <v>1321</v>
+        <v>891</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>12</v>
@@ -13794,8 +12514,8 @@
       <c r="G357" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H357" s="1" t="s">
-        <v>887</v>
+      <c r="H357" s="5">
+        <v>32376</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
@@ -13803,7 +12523,7 @@
         <v>371</v>
       </c>
       <c r="B358" t="s">
-        <v>1322</v>
+        <v>892</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>7</v>
@@ -13820,8 +12540,8 @@
       <c r="G358" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H358" s="1" t="s">
-        <v>888</v>
+      <c r="H358" s="5">
+        <v>33428</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
@@ -13829,7 +12549,7 @@
         <v>372</v>
       </c>
       <c r="B359" t="s">
-        <v>1323</v>
+        <v>893</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>7</v>
@@ -13846,8 +12566,8 @@
       <c r="G359" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H359" s="1" t="s">
-        <v>889</v>
+      <c r="H359" s="5">
+        <v>31765</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
@@ -13855,7 +12575,7 @@
         <v>373</v>
       </c>
       <c r="B360" t="s">
-        <v>1324</v>
+        <v>894</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>8</v>
@@ -13872,8 +12592,8 @@
       <c r="G360" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H360" s="1" t="s">
-        <v>890</v>
+      <c r="H360" s="5">
+        <v>33594</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
@@ -13881,7 +12601,7 @@
         <v>374</v>
       </c>
       <c r="B361" t="s">
-        <v>1325</v>
+        <v>895</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>8</v>
@@ -13898,8 +12618,8 @@
       <c r="G361" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H361" s="1" t="s">
-        <v>891</v>
+      <c r="H361" s="5">
+        <v>36118</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
@@ -13907,7 +12627,7 @@
         <v>375</v>
       </c>
       <c r="B362" t="s">
-        <v>1326</v>
+        <v>896</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>7</v>
@@ -13924,8 +12644,8 @@
       <c r="G362" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H362" s="1" t="s">
-        <v>892</v>
+      <c r="H362" s="5">
+        <v>32493</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
@@ -13933,7 +12653,7 @@
         <v>376</v>
       </c>
       <c r="B363" t="s">
-        <v>1327</v>
+        <v>897</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>12</v>
@@ -13950,8 +12670,8 @@
       <c r="G363" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H363" s="1" t="s">
-        <v>893</v>
+      <c r="H363" s="5">
+        <v>31203</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
@@ -13959,7 +12679,7 @@
         <v>377</v>
       </c>
       <c r="B364" t="s">
-        <v>1328</v>
+        <v>898</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>10</v>
@@ -13976,8 +12696,8 @@
       <c r="G364" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H364" s="1" t="s">
-        <v>894</v>
+      <c r="H364" s="5">
+        <v>32489</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
@@ -13985,7 +12705,7 @@
         <v>378</v>
       </c>
       <c r="B365" t="s">
-        <v>1329</v>
+        <v>899</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>10</v>
@@ -14002,8 +12722,8 @@
       <c r="G365" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H365" s="1" t="s">
-        <v>895</v>
+      <c r="H365" s="5">
+        <v>34524</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
@@ -14011,7 +12731,7 @@
         <v>379</v>
       </c>
       <c r="B366" t="s">
-        <v>1330</v>
+        <v>900</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>10</v>
@@ -14028,8 +12748,8 @@
       <c r="G366" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H366" s="1" t="s">
-        <v>896</v>
+      <c r="H366" s="5">
+        <v>26049</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
@@ -14037,7 +12757,7 @@
         <v>380</v>
       </c>
       <c r="B367" t="s">
-        <v>1331</v>
+        <v>901</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>7</v>
@@ -14054,8 +12774,8 @@
       <c r="G367" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H367" s="1" t="s">
-        <v>897</v>
+      <c r="H367" s="5">
+        <v>28998</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
@@ -14063,7 +12783,7 @@
         <v>381</v>
       </c>
       <c r="B368" t="s">
-        <v>1332</v>
+        <v>902</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>11</v>
@@ -14080,8 +12800,8 @@
       <c r="G368" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H368" s="1" t="s">
-        <v>898</v>
+      <c r="H368" s="5">
+        <v>22998</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
@@ -14089,7 +12809,7 @@
         <v>382</v>
       </c>
       <c r="B369" t="s">
-        <v>1333</v>
+        <v>903</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>8</v>
@@ -14106,8 +12826,8 @@
       <c r="G369" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H369" s="1" t="s">
-        <v>899</v>
+      <c r="H369" s="5">
+        <v>33620</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
@@ -14115,7 +12835,7 @@
         <v>383</v>
       </c>
       <c r="B370" t="s">
-        <v>1334</v>
+        <v>904</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>10</v>
@@ -14132,8 +12852,8 @@
       <c r="G370" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H370" s="1" t="s">
-        <v>900</v>
+      <c r="H370" s="5">
+        <v>33943</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
@@ -14141,7 +12861,7 @@
         <v>384</v>
       </c>
       <c r="B371" t="s">
-        <v>1335</v>
+        <v>905</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>7</v>
@@ -14158,8 +12878,8 @@
       <c r="G371" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H371" s="1" t="s">
-        <v>901</v>
+      <c r="H371" s="5">
+        <v>25821</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
@@ -14167,7 +12887,7 @@
         <v>385</v>
       </c>
       <c r="B372" t="s">
-        <v>1336</v>
+        <v>906</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>7</v>
@@ -14184,8 +12904,8 @@
       <c r="G372" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H372" s="1" t="s">
-        <v>879</v>
+      <c r="H372" s="5">
+        <v>34743</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
@@ -14193,7 +12913,7 @@
         <v>386</v>
       </c>
       <c r="B373" t="s">
-        <v>1337</v>
+        <v>907</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>10</v>
@@ -14210,8 +12930,8 @@
       <c r="G373" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H373" s="1" t="s">
-        <v>824</v>
+      <c r="H373" s="5">
+        <v>35719</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
@@ -14219,7 +12939,7 @@
         <v>387</v>
       </c>
       <c r="B374" t="s">
-        <v>1338</v>
+        <v>908</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>11</v>
@@ -14236,8 +12956,8 @@
       <c r="G374" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H374" s="1" t="s">
-        <v>902</v>
+      <c r="H374" s="5">
+        <v>25141</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
@@ -14245,7 +12965,7 @@
         <v>388</v>
       </c>
       <c r="B375" t="s">
-        <v>1339</v>
+        <v>909</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>7</v>
@@ -14262,8 +12982,8 @@
       <c r="G375" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H375" s="1" t="s">
-        <v>903</v>
+      <c r="H375" s="5">
+        <v>26883</v>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
@@ -14271,7 +12991,7 @@
         <v>389</v>
       </c>
       <c r="B376" t="s">
-        <v>1340</v>
+        <v>910</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>8</v>
@@ -14288,8 +13008,8 @@
       <c r="G376" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H376" s="1" t="s">
-        <v>904</v>
+      <c r="H376" s="5">
+        <v>29542</v>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
@@ -14297,7 +13017,7 @@
         <v>390</v>
       </c>
       <c r="B377" t="s">
-        <v>1341</v>
+        <v>911</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>7</v>
@@ -14314,8 +13034,8 @@
       <c r="G377" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H377" s="1" t="s">
-        <v>905</v>
+      <c r="H377" s="5">
+        <v>33104</v>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
@@ -14323,7 +13043,7 @@
         <v>391</v>
       </c>
       <c r="B378" t="s">
-        <v>1342</v>
+        <v>912</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>7</v>
@@ -14340,8 +13060,8 @@
       <c r="G378" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H378" s="1" t="s">
-        <v>906</v>
+      <c r="H378" s="5">
+        <v>33044</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
@@ -14349,7 +13069,7 @@
         <v>392</v>
       </c>
       <c r="B379" t="s">
-        <v>1343</v>
+        <v>913</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>7</v>
@@ -14366,8 +13086,8 @@
       <c r="G379" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H379" s="1" t="s">
-        <v>907</v>
+      <c r="H379" s="5">
+        <v>34029</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
@@ -14375,7 +13095,7 @@
         <v>393</v>
       </c>
       <c r="B380" t="s">
-        <v>1344</v>
+        <v>914</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>11</v>
@@ -14392,8 +13112,8 @@
       <c r="G380" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H380" s="1" t="s">
-        <v>908</v>
+      <c r="H380" s="5">
+        <v>35728</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
@@ -14401,7 +13121,7 @@
         <v>394</v>
       </c>
       <c r="B381" t="s">
-        <v>1345</v>
+        <v>915</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>7</v>
@@ -14418,8 +13138,8 @@
       <c r="G381" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H381" s="1" t="s">
-        <v>909</v>
+      <c r="H381" s="5">
+        <v>29393</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
@@ -14427,7 +13147,7 @@
         <v>395</v>
       </c>
       <c r="B382" t="s">
-        <v>1346</v>
+        <v>916</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>10</v>
@@ -14444,8 +13164,8 @@
       <c r="G382" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H382" s="1" t="s">
-        <v>910</v>
+      <c r="H382" s="5">
+        <v>33010</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
@@ -14453,7 +13173,7 @@
         <v>396</v>
       </c>
       <c r="B383" t="s">
-        <v>1347</v>
+        <v>917</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>7</v>
@@ -14470,8 +13190,8 @@
       <c r="G383" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H383" s="1" t="s">
-        <v>911</v>
+      <c r="H383" s="5">
+        <v>33124</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.2">
@@ -14479,7 +13199,7 @@
         <v>397</v>
       </c>
       <c r="B384" t="s">
-        <v>1348</v>
+        <v>918</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>8</v>
@@ -14496,8 +13216,8 @@
       <c r="G384" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H384" s="1" t="s">
-        <v>912</v>
+      <c r="H384" s="5">
+        <v>33511</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.2">
@@ -14505,7 +13225,7 @@
         <v>398</v>
       </c>
       <c r="B385" t="s">
-        <v>1349</v>
+        <v>919</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>9</v>
@@ -14522,8 +13242,8 @@
       <c r="G385" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H385" s="1" t="s">
-        <v>687</v>
+      <c r="H385" s="5">
+        <v>33742</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.2">
@@ -14531,7 +13251,7 @@
         <v>399</v>
       </c>
       <c r="B386" t="s">
-        <v>1350</v>
+        <v>920</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>12</v>
@@ -14548,8 +13268,8 @@
       <c r="G386" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H386" s="1" t="s">
-        <v>913</v>
+      <c r="H386" s="5">
+        <v>21758</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
@@ -14557,7 +13277,7 @@
         <v>400</v>
       </c>
       <c r="B387" t="s">
-        <v>1351</v>
+        <v>921</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>7</v>
@@ -14574,8 +13294,8 @@
       <c r="G387" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H387" s="1" t="s">
-        <v>914</v>
+      <c r="H387" s="5">
+        <v>29479</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.2">
@@ -14583,7 +13303,7 @@
         <v>401</v>
       </c>
       <c r="B388" t="s">
-        <v>1352</v>
+        <v>922</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>7</v>
@@ -14600,8 +13320,8 @@
       <c r="G388" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H388" s="1" t="s">
-        <v>915</v>
+      <c r="H388" s="5">
+        <v>22970</v>
       </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
@@ -14609,7 +13329,7 @@
         <v>402</v>
       </c>
       <c r="B389" t="s">
-        <v>1353</v>
+        <v>923</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>11</v>
@@ -14626,8 +13346,8 @@
       <c r="G389" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H389" s="1" t="s">
-        <v>916</v>
+      <c r="H389" s="5">
+        <v>32984</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.2">
@@ -14635,7 +13355,7 @@
         <v>403</v>
       </c>
       <c r="B390" t="s">
-        <v>1354</v>
+        <v>924</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>7</v>
@@ -14652,8 +13372,8 @@
       <c r="G390" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H390" s="1" t="s">
-        <v>917</v>
+      <c r="H390" s="5">
+        <v>34292</v>
       </c>
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.2">
@@ -14661,7 +13381,7 @@
         <v>404</v>
       </c>
       <c r="B391" t="s">
-        <v>1355</v>
+        <v>925</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>11</v>
@@ -14678,8 +13398,8 @@
       <c r="G391" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H391" s="1" t="s">
-        <v>918</v>
+      <c r="H391" s="5">
+        <v>32752</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
@@ -14687,7 +13407,7 @@
         <v>405</v>
       </c>
       <c r="B392" t="s">
-        <v>1356</v>
+        <v>926</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>10</v>
@@ -14704,8 +13424,8 @@
       <c r="G392" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H392" s="1" t="s">
-        <v>919</v>
+      <c r="H392" s="5">
+        <v>24518</v>
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.2">
@@ -14730,8 +13450,8 @@
       <c r="G393" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H393" s="1" t="s">
-        <v>920</v>
+      <c r="H393" s="5">
+        <v>30316</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
@@ -14756,8 +13476,8 @@
       <c r="G394" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H394" s="1" t="s">
-        <v>921</v>
+      <c r="H394" s="5">
+        <v>33519</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.2">
@@ -14782,8 +13502,8 @@
       <c r="G395" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H395" s="1" t="s">
-        <v>922</v>
+      <c r="H395" s="5">
+        <v>34281</v>
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.2">
@@ -14808,8 +13528,8 @@
       <c r="G396" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H396" s="1" t="s">
-        <v>923</v>
+      <c r="H396" s="5">
+        <v>32828</v>
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.2">
@@ -14834,8 +13554,8 @@
       <c r="G397" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H397" s="1" t="s">
-        <v>924</v>
+      <c r="H397" s="5">
+        <v>34552</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.2">
@@ -14860,8 +13580,8 @@
       <c r="G398" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H398" s="1" t="s">
-        <v>925</v>
+      <c r="H398" s="5">
+        <v>30099</v>
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.2">
@@ -14886,8 +13606,8 @@
       <c r="G399" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H399" s="1" t="s">
-        <v>926</v>
+      <c r="H399" s="5">
+        <v>30130</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.2">
@@ -14912,8 +13632,8 @@
       <c r="G400" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H400" s="1" t="s">
-        <v>927</v>
+      <c r="H400" s="5">
+        <v>33773</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
@@ -14938,8 +13658,8 @@
       <c r="G401" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H401" s="1" t="s">
-        <v>928</v>
+      <c r="H401" s="5">
+        <v>28189</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.2">
@@ -14964,8 +13684,8 @@
       <c r="G402" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H402" s="1" t="s">
-        <v>929</v>
+      <c r="H402" s="5">
+        <v>29151</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
@@ -14990,8 +13710,8 @@
       <c r="G403" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H403" s="1" t="s">
-        <v>930</v>
+      <c r="H403" s="5">
+        <v>30953</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.2">
@@ -15016,8 +13736,8 @@
       <c r="G404" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H404" s="1" t="s">
-        <v>931</v>
+      <c r="H404" s="5">
+        <v>33831</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.2">
@@ -15042,8 +13762,8 @@
       <c r="G405" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H405" s="1" t="s">
-        <v>932</v>
+      <c r="H405" s="5">
+        <v>34986</v>
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.2">
@@ -15068,8 +13788,8 @@
       <c r="G406" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H406" s="1" t="s">
-        <v>933</v>
+      <c r="H406" s="5">
+        <v>37625</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.2">
@@ -15094,8 +13814,8 @@
       <c r="G407" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H407" s="1" t="s">
-        <v>934</v>
+      <c r="H407" s="5">
+        <v>33884</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.2">
@@ -15120,8 +13840,8 @@
       <c r="G408" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H408" s="1" t="s">
-        <v>935</v>
+      <c r="H408" s="5">
+        <v>28712</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
@@ -15146,8 +13866,8 @@
       <c r="G409" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H409" s="1" t="s">
-        <v>936</v>
+      <c r="H409" s="5">
+        <v>31957</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
@@ -15172,8 +13892,8 @@
       <c r="G410" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H410" s="1" t="s">
-        <v>937</v>
+      <c r="H410" s="5">
+        <v>25038</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.2">
@@ -15198,8 +13918,8 @@
       <c r="G411" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H411" s="1" t="s">
-        <v>938</v>
+      <c r="H411" s="5">
+        <v>23743</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
@@ -15224,8 +13944,8 @@
       <c r="G412" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H412" s="1" t="s">
-        <v>939</v>
+      <c r="H412" s="5">
+        <v>33259</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
@@ -15250,8 +13970,8 @@
       <c r="G413" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H413" s="1" t="s">
-        <v>940</v>
+      <c r="H413" s="5">
+        <v>33971</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
@@ -15276,8 +13996,8 @@
       <c r="G414" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H414" s="1" t="s">
-        <v>941</v>
+      <c r="H414" s="5">
+        <v>29437</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
@@ -15302,8 +14022,8 @@
       <c r="G415" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H415" s="1" t="s">
-        <v>942</v>
+      <c r="H415" s="5">
+        <v>27271</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
@@ -15328,8 +14048,8 @@
       <c r="G416" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H416" s="1" t="s">
-        <v>943</v>
+      <c r="H416" s="5">
+        <v>30278</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.2">
@@ -15354,8 +14074,8 @@
       <c r="G417" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H417" s="1" t="s">
-        <v>944</v>
+      <c r="H417" s="5">
+        <v>23444</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.2">
@@ -15380,8 +14100,8 @@
       <c r="G418" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H418" s="1" t="s">
-        <v>945</v>
+      <c r="H418" s="5">
+        <v>27917</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.2">
@@ -15406,8 +14126,8 @@
       <c r="G419" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H419" s="1" t="s">
-        <v>946</v>
+      <c r="H419" s="5">
+        <v>28958</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.2">
@@ -15432,8 +14152,8 @@
       <c r="G420" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H420" s="1" t="s">
-        <v>947</v>
+      <c r="H420" s="5">
+        <v>25426</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.2">
@@ -15458,8 +14178,8 @@
       <c r="G421" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H421" s="1" t="s">
-        <v>948</v>
+      <c r="H421" s="5">
+        <v>24959</v>
       </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.2">
@@ -15484,8 +14204,8 @@
       <c r="G422" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H422" s="1" t="s">
-        <v>949</v>
+      <c r="H422" s="5">
+        <v>33954</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.2">
@@ -15510,8 +14230,8 @@
       <c r="G423" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H423" s="1" t="s">
-        <v>950</v>
+      <c r="H423" s="5">
+        <v>33904</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.2">
@@ -15536,8 +14256,8 @@
       <c r="G424" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H424" s="1" t="s">
-        <v>951</v>
+      <c r="H424" s="5">
+        <v>32036</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.2">
@@ -15562,8 +14282,8 @@
       <c r="G425" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H425" s="1" t="s">
-        <v>952</v>
+      <c r="H425" s="5">
+        <v>27639</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.2">
@@ -15588,8 +14308,8 @@
       <c r="G426" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H426" s="1" t="s">
-        <v>953</v>
+      <c r="H426" s="5">
+        <v>28431</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.2">
@@ -15614,8 +14334,8 @@
       <c r="G427" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H427" s="1" t="s">
-        <v>954</v>
+      <c r="H427" s="5">
+        <v>30013</v>
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
@@ -15640,8 +14360,8 @@
       <c r="G428" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H428" s="1" t="s">
-        <v>955</v>
+      <c r="H428" s="5">
+        <v>31808</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
@@ -15666,8 +14386,8 @@
       <c r="G429" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H429" s="1" t="s">
-        <v>956</v>
+      <c r="H429" s="5">
+        <v>29930</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
@@ -15692,8 +14412,8 @@
       <c r="G430" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H430" s="1" t="s">
-        <v>957</v>
+      <c r="H430" s="5">
+        <v>32069</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
@@ -15718,8 +14438,8 @@
       <c r="G431" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H431" s="1" t="s">
-        <v>958</v>
+      <c r="H431" s="5">
+        <v>29647</v>
       </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
@@ -15744,8 +14464,8 @@
       <c r="G432" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H432" s="1" t="s">
-        <v>959</v>
+      <c r="H432" s="5">
+        <v>28854</v>
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.2">
@@ -15770,8 +14490,8 @@
       <c r="G433" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H433" s="1" t="s">
-        <v>960</v>
+      <c r="H433" s="5">
+        <v>28878</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
@@ -15796,8 +14516,8 @@
       <c r="G434" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H434" s="1" t="s">
-        <v>961</v>
+      <c r="H434" s="5">
+        <v>26870</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
@@ -15822,8 +14542,8 @@
       <c r="G435" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H435" s="1" t="s">
-        <v>962</v>
+      <c r="H435" s="5">
+        <v>32177</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
@@ -15848,8 +14568,8 @@
       <c r="G436" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H436" s="1" t="s">
-        <v>963</v>
+      <c r="H436" s="5">
+        <v>31041</v>
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
@@ -15874,8 +14594,8 @@
       <c r="G437" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H437" s="1" t="s">
-        <v>964</v>
+      <c r="H437" s="5">
+        <v>23948</v>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
@@ -15900,8 +14620,8 @@
       <c r="G438" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H438" s="1" t="s">
-        <v>965</v>
+      <c r="H438" s="5">
+        <v>23461</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
@@ -15926,8 +14646,8 @@
       <c r="G439" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H439" s="1" t="s">
-        <v>873</v>
+      <c r="H439" s="5">
+        <v>34139</v>
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
@@ -15952,8 +14672,8 @@
       <c r="G440" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H440" s="1" t="s">
-        <v>966</v>
+      <c r="H440" s="5">
+        <v>31370</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
@@ -15978,8 +14698,8 @@
       <c r="G441" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H441" s="1" t="s">
-        <v>967</v>
+      <c r="H441" s="5">
+        <v>32607</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
@@ -16004,8 +14724,8 @@
       <c r="G442" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="H442" s="1" t="s">
-        <v>968</v>
+      <c r="H442" s="5">
+        <v>31703</v>
       </c>
     </row>
   </sheetData>

--- a/BASE DATOS MODO APS.xlsx
+++ b/BASE DATOS MODO APS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanvidalp/Documents/clon carrera funcionaria/carrera-aps-digital/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B112CC2A-96BF-EE4A-90E2-8984ECD6D2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A4FF23-A9AB-8F4C-8CC6-159B411B38CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30240" yWindow="1480" windowWidth="30240" windowHeight="18980" xr2:uid="{A9505C21-DF7A-114D-A7E6-2CB0B98403BE}"/>
   </bookViews>
@@ -2826,9 +2826,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -2880,17 +2877,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3233,7 +3229,7 @@
     <col min="3" max="3" width="39.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="19.83203125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="19.1640625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3278,7 +3274,7 @@
       <c r="E2" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="1" t="s">
         <v>532</v>
       </c>
       <c r="G2" s="1" t="s">

--- a/BASE DATOS MODO APS.xlsx
+++ b/BASE DATOS MODO APS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanvidalp/Documents/clon carrera funcionaria/carrera-aps-digital/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A4FF23-A9AB-8F4C-8CC6-159B411B38CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B103A0-598C-2349-9DA3-E57CE6A575F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30240" yWindow="1480" windowWidth="30240" windowHeight="18980" xr2:uid="{A9505C21-DF7A-114D-A7E6-2CB0B98403BE}"/>
   </bookViews>
@@ -2826,6 +2826,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -2877,21 +2880,154 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2902,6 +3038,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{295653C2-543A-3242-AC88-B07A27B84D8D}" name="Tabla2" displayName="Tabla2" ref="A1:H442" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:H442" xr:uid="{295653C2-543A-3242-AC88-B07A27B84D8D}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{B37AE236-64D2-614F-995B-667452BE6B5F}" name="RUT" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{A61045C6-6455-9B46-B60D-6273BA4D7AEA}" name="NOMBRE"/>
+    <tableColumn id="3" xr3:uid="{AF558316-47E5-FE45-A078-9EF04A4DFC4B}" name="Establecimiento" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{F3DFD452-EA04-D749-B980-7F229697155D}" name="Categoría" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{D1D00D42-53FA-F44A-82B4-5776848CF6FD}" name=" Profesión" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{56286FD2-BD2C-B24F-BC6D-CA7C58A5C9B3}" name="Nacionalidad" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{A0198422-0804-DD43-9BD8-F5191267A456}" name="Tipo Contrato" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{E5EB52D8-7F4C-ED44-AA40-35686055C1FA}" name="Fecha Nacimiento" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3224,16 +3377,17 @@
   <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.1640625" customWidth="1"/>
+    <col min="1" max="1" width="22.1640625" style="8" customWidth="1"/>
     <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="19.1640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -3259,7 +3413,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B2" t="s">
@@ -3285,7 +3439,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B3" t="s">
@@ -3311,7 +3465,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B4" t="s">
@@ -3337,7 +3491,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B5" t="s">
@@ -3363,7 +3517,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="8" t="s">
         <v>24</v>
       </c>
       <c r="B6" t="s">
@@ -3389,7 +3543,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
@@ -3415,7 +3569,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B8" t="s">
@@ -3441,7 +3595,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B9" t="s">
@@ -3467,7 +3621,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
@@ -3493,7 +3647,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B11" t="s">
@@ -3519,7 +3673,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="8" t="s">
         <v>30</v>
       </c>
       <c r="B12" t="s">
@@ -3545,7 +3699,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="8" t="s">
         <v>31</v>
       </c>
       <c r="B13" t="s">
@@ -3571,7 +3725,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="8" t="s">
         <v>32</v>
       </c>
       <c r="B14" t="s">
@@ -3597,7 +3751,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="8" t="s">
         <v>33</v>
       </c>
       <c r="B15" t="s">
@@ -3623,7 +3777,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="A16" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B16" t="s">
@@ -3649,7 +3803,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="8" t="s">
         <v>35</v>
       </c>
       <c r="B17" t="s">
@@ -3675,7 +3829,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="8" t="s">
         <v>36</v>
       </c>
       <c r="B18" t="s">
@@ -3701,7 +3855,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="A19" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B19" t="s">
@@ -3727,7 +3881,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B20" t="s">
@@ -3753,7 +3907,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="A21" s="8" t="s">
         <v>39</v>
       </c>
       <c r="B21" t="s">
@@ -3779,7 +3933,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B22" t="s">
@@ -3805,7 +3959,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="A23" s="8" t="s">
         <v>41</v>
       </c>
       <c r="B23" t="s">
@@ -3831,7 +3985,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="A24" s="8" t="s">
         <v>42</v>
       </c>
       <c r="B24" t="s">
@@ -3857,7 +4011,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" s="8" t="s">
         <v>43</v>
       </c>
       <c r="B25" t="s">
@@ -3883,7 +4037,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="A26" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B26" t="s">
@@ -3909,7 +4063,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="A27" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B27" t="s">
@@ -3935,7 +4089,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="A28" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B28" t="s">
@@ -3961,7 +4115,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="A29" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B29" t="s">
@@ -3987,7 +4141,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="A30" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B30" t="s">
@@ -4013,7 +4167,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="A31" s="8" t="s">
         <v>49</v>
       </c>
       <c r="B31" t="s">
@@ -4039,7 +4193,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="A32" s="8" t="s">
         <v>50</v>
       </c>
       <c r="B32" t="s">
@@ -4065,7 +4219,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="A33" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B33" t="s">
@@ -4091,7 +4245,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="A34" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B34" t="s">
@@ -4117,7 +4271,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="A35" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B35" t="s">
@@ -4143,7 +4297,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="A36" s="8" t="s">
         <v>54</v>
       </c>
       <c r="B36" t="s">
@@ -4169,7 +4323,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="A37" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B37" t="s">
@@ -4195,7 +4349,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="A38" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B38" t="s">
@@ -4221,7 +4375,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="A39" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B39" t="s">
@@ -4247,7 +4401,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="A40" s="8" t="s">
         <v>58</v>
       </c>
       <c r="B40" t="s">
@@ -4273,7 +4427,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="A41" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B41" t="s">
@@ -4299,7 +4453,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="A42" s="8" t="s">
         <v>60</v>
       </c>
       <c r="B42" t="s">
@@ -4325,7 +4479,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="A43" s="8" t="s">
         <v>61</v>
       </c>
       <c r="B43" t="s">
@@ -4351,7 +4505,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="A44" s="8" t="s">
         <v>62</v>
       </c>
       <c r="B44" t="s">
@@ -4377,7 +4531,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="A45" s="8" t="s">
         <v>63</v>
       </c>
       <c r="B45" t="s">
@@ -4403,7 +4557,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="A46" s="8" t="s">
         <v>64</v>
       </c>
       <c r="B46" t="s">
@@ -4429,7 +4583,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="A47" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B47" t="s">
@@ -4455,7 +4609,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="A48" s="8" t="s">
         <v>66</v>
       </c>
       <c r="B48" t="s">
@@ -4481,7 +4635,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="A49" s="8" t="s">
         <v>67</v>
       </c>
       <c r="B49" t="s">
@@ -4507,7 +4661,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+      <c r="A50" s="8" t="s">
         <v>68</v>
       </c>
       <c r="B50" t="s">
@@ -4533,7 +4687,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+      <c r="A51" s="8" t="s">
         <v>69</v>
       </c>
       <c r="B51" t="s">
@@ -4559,7 +4713,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="A52" s="8" t="s">
         <v>70</v>
       </c>
       <c r="B52" t="s">
@@ -4585,7 +4739,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+      <c r="A53" s="8" t="s">
         <v>71</v>
       </c>
       <c r="B53" t="s">
@@ -4611,7 +4765,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+      <c r="A54" s="8" t="s">
         <v>72</v>
       </c>
       <c r="B54" t="s">
@@ -4637,7 +4791,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="A55" s="8" t="s">
         <v>73</v>
       </c>
       <c r="B55" t="s">
@@ -4663,7 +4817,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+      <c r="A56" s="8" t="s">
         <v>74</v>
       </c>
       <c r="B56" t="s">
@@ -4689,7 +4843,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="A57" s="8" t="s">
         <v>75</v>
       </c>
       <c r="B57" t="s">
@@ -4715,7 +4869,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+      <c r="A58" s="8" t="s">
         <v>76</v>
       </c>
       <c r="B58" t="s">
@@ -4741,7 +4895,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+      <c r="A59" s="8" t="s">
         <v>77</v>
       </c>
       <c r="B59" t="s">
@@ -4767,7 +4921,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+      <c r="A60" s="8" t="s">
         <v>78</v>
       </c>
       <c r="B60" t="s">
@@ -4793,7 +4947,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="A61" s="8" t="s">
         <v>79</v>
       </c>
       <c r="B61" t="s">
@@ -4819,7 +4973,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+      <c r="A62" s="8" t="s">
         <v>79</v>
       </c>
       <c r="B62" t="s">
@@ -4845,7 +4999,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+      <c r="A63" s="8" t="s">
         <v>80</v>
       </c>
       <c r="B63" t="s">
@@ -4871,7 +5025,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+      <c r="A64" s="8" t="s">
         <v>81</v>
       </c>
       <c r="B64" t="s">
@@ -4897,7 +5051,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+      <c r="A65" s="8" t="s">
         <v>82</v>
       </c>
       <c r="B65" t="s">
@@ -4923,7 +5077,7 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="A66" s="8" t="s">
         <v>83</v>
       </c>
       <c r="B66" t="s">
@@ -4949,7 +5103,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+      <c r="A67" s="8" t="s">
         <v>84</v>
       </c>
       <c r="B67" t="s">
@@ -4975,7 +5129,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+      <c r="A68" s="8" t="s">
         <v>85</v>
       </c>
       <c r="B68" t="s">
@@ -5001,7 +5155,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="A69" s="8" t="s">
         <v>86</v>
       </c>
       <c r="B69" t="s">
@@ -5027,7 +5181,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+      <c r="A70" s="8" t="s">
         <v>87</v>
       </c>
       <c r="B70" t="s">
@@ -5053,7 +5207,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="A71" s="8" t="s">
         <v>88</v>
       </c>
       <c r="B71" t="s">
@@ -5079,7 +5233,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+      <c r="A72" s="8" t="s">
         <v>89</v>
       </c>
       <c r="B72" t="s">
@@ -5105,7 +5259,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+      <c r="A73" s="8" t="s">
         <v>90</v>
       </c>
       <c r="B73" t="s">
@@ -5131,7 +5285,7 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+      <c r="A74" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B74" t="s">
@@ -5157,7 +5311,7 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+      <c r="A75" s="8" t="s">
         <v>92</v>
       </c>
       <c r="B75" t="s">
@@ -5183,7 +5337,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+      <c r="A76" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B76" t="s">
@@ -5209,7 +5363,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+      <c r="A77" s="8" t="s">
         <v>94</v>
       </c>
       <c r="B77" t="s">
@@ -5235,7 +5389,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+      <c r="A78" s="8" t="s">
         <v>95</v>
       </c>
       <c r="B78" t="s">
@@ -5261,7 +5415,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+      <c r="A79" s="8" t="s">
         <v>96</v>
       </c>
       <c r="B79" t="s">
@@ -5287,7 +5441,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+      <c r="A80" s="8" t="s">
         <v>97</v>
       </c>
       <c r="B80" t="s">
@@ -5313,7 +5467,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
+      <c r="A81" s="8" t="s">
         <v>98</v>
       </c>
       <c r="B81" t="s">
@@ -5339,7 +5493,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+      <c r="A82" s="8" t="s">
         <v>99</v>
       </c>
       <c r="B82" t="s">
@@ -5365,7 +5519,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+      <c r="A83" s="8" t="s">
         <v>100</v>
       </c>
       <c r="B83" t="s">
@@ -5391,7 +5545,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+      <c r="A84" s="8" t="s">
         <v>101</v>
       </c>
       <c r="B84" t="s">
@@ -5417,7 +5571,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+      <c r="A85" s="8" t="s">
         <v>102</v>
       </c>
       <c r="B85" t="s">
@@ -5443,7 +5597,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
+      <c r="A86" s="8" t="s">
         <v>103</v>
       </c>
       <c r="B86" t="s">
@@ -5469,7 +5623,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+      <c r="A87" s="8" t="s">
         <v>104</v>
       </c>
       <c r="B87" t="s">
@@ -5495,7 +5649,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+      <c r="A88" s="8" t="s">
         <v>105</v>
       </c>
       <c r="B88" t="s">
@@ -5521,7 +5675,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+      <c r="A89" s="8" t="s">
         <v>106</v>
       </c>
       <c r="B89" t="s">
@@ -5547,7 +5701,7 @@
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+      <c r="A90" s="8" t="s">
         <v>107</v>
       </c>
       <c r="B90" t="s">
@@ -5573,7 +5727,7 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
+      <c r="A91" s="8" t="s">
         <v>108</v>
       </c>
       <c r="B91" t="s">
@@ -5599,7 +5753,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+      <c r="A92" s="8" t="s">
         <v>109</v>
       </c>
       <c r="B92" t="s">
@@ -5625,7 +5779,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+      <c r="A93" s="8" t="s">
         <v>110</v>
       </c>
       <c r="B93" t="s">
@@ -5651,7 +5805,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
+      <c r="A94" s="8" t="s">
         <v>111</v>
       </c>
       <c r="B94" t="s">
@@ -5677,7 +5831,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
+      <c r="A95" s="8" t="s">
         <v>112</v>
       </c>
       <c r="B95" t="s">
@@ -5703,7 +5857,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
+      <c r="A96" s="8" t="s">
         <v>113</v>
       </c>
       <c r="B96" t="s">
@@ -5729,7 +5883,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
+      <c r="A97" s="8" t="s">
         <v>114</v>
       </c>
       <c r="B97" t="s">
@@ -5755,7 +5909,7 @@
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
+      <c r="A98" s="8" t="s">
         <v>115</v>
       </c>
       <c r="B98" t="s">
@@ -5781,7 +5935,7 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
+      <c r="A99" s="8" t="s">
         <v>116</v>
       </c>
       <c r="B99" t="s">
@@ -5807,7 +5961,7 @@
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
+      <c r="A100" s="8" t="s">
         <v>117</v>
       </c>
       <c r="B100" t="s">
@@ -5833,7 +5987,7 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
+      <c r="A101" s="8" t="s">
         <v>118</v>
       </c>
       <c r="B101" t="s">
@@ -5859,7 +6013,7 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
+      <c r="A102" s="8" t="s">
         <v>119</v>
       </c>
       <c r="B102" t="s">
@@ -5885,7 +6039,7 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
+      <c r="A103" s="8" t="s">
         <v>120</v>
       </c>
       <c r="B103" t="s">
@@ -5911,7 +6065,7 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
+      <c r="A104" s="8" t="s">
         <v>121</v>
       </c>
       <c r="B104" t="s">
@@ -5937,7 +6091,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
+      <c r="A105" s="8" t="s">
         <v>122</v>
       </c>
       <c r="B105" t="s">
@@ -5963,7 +6117,7 @@
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
+      <c r="A106" s="8" t="s">
         <v>123</v>
       </c>
       <c r="B106" t="s">
@@ -5989,7 +6143,7 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
+      <c r="A107" s="8" t="s">
         <v>124</v>
       </c>
       <c r="B107" t="s">
@@ -6015,7 +6169,7 @@
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
+      <c r="A108" s="8" t="s">
         <v>125</v>
       </c>
       <c r="B108" t="s">
@@ -6041,7 +6195,7 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
+      <c r="A109" s="8" t="s">
         <v>126</v>
       </c>
       <c r="B109" t="s">
@@ -6067,7 +6221,7 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
+      <c r="A110" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B110" t="s">
@@ -6093,7 +6247,7 @@
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
+      <c r="A111" s="8" t="s">
         <v>128</v>
       </c>
       <c r="B111" t="s">
@@ -6119,7 +6273,7 @@
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
+      <c r="A112" s="8" t="s">
         <v>129</v>
       </c>
       <c r="B112" t="s">
@@ -6145,7 +6299,7 @@
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
+      <c r="A113" s="8" t="s">
         <v>130</v>
       </c>
       <c r="B113" t="s">
@@ -6171,7 +6325,7 @@
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
+      <c r="A114" s="8" t="s">
         <v>131</v>
       </c>
       <c r="B114" t="s">
@@ -6197,7 +6351,7 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
+      <c r="A115" s="8" t="s">
         <v>132</v>
       </c>
       <c r="B115" t="s">
@@ -6223,7 +6377,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
+      <c r="A116" s="8" t="s">
         <v>133</v>
       </c>
       <c r="B116" t="s">
@@ -6249,7 +6403,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
+      <c r="A117" s="8" t="s">
         <v>134</v>
       </c>
       <c r="B117" t="s">
@@ -6275,7 +6429,7 @@
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
+      <c r="A118" s="8" t="s">
         <v>135</v>
       </c>
       <c r="B118" t="s">
@@ -6301,7 +6455,7 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
+      <c r="A119" s="8" t="s">
         <v>136</v>
       </c>
       <c r="B119" t="s">
@@ -6327,7 +6481,7 @@
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
+      <c r="A120" s="8" t="s">
         <v>137</v>
       </c>
       <c r="B120" t="s">
@@ -6353,7 +6507,7 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
+      <c r="A121" s="8" t="s">
         <v>138</v>
       </c>
       <c r="B121" t="s">
@@ -6379,7 +6533,7 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
+      <c r="A122" s="8" t="s">
         <v>139</v>
       </c>
       <c r="B122" t="s">
@@ -6405,7 +6559,7 @@
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
+      <c r="A123" s="8" t="s">
         <v>140</v>
       </c>
       <c r="B123" t="s">
@@ -6431,7 +6585,7 @@
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
+      <c r="A124" s="8" t="s">
         <v>141</v>
       </c>
       <c r="B124" t="s">
@@ -6457,7 +6611,7 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
+      <c r="A125" s="8" t="s">
         <v>142</v>
       </c>
       <c r="B125" t="s">
@@ -6483,7 +6637,7 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
+      <c r="A126" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B126" t="s">
@@ -6509,7 +6663,7 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
+      <c r="A127" s="8" t="s">
         <v>144</v>
       </c>
       <c r="B127" t="s">
@@ -6535,7 +6689,7 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
+      <c r="A128" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B128" t="s">
@@ -6561,7 +6715,7 @@
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
+      <c r="A129" s="8" t="s">
         <v>145</v>
       </c>
       <c r="B129" t="s">
@@ -6587,7 +6741,7 @@
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
+      <c r="A130" s="8" t="s">
         <v>146</v>
       </c>
       <c r="B130" t="s">
@@ -6613,7 +6767,7 @@
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
+      <c r="A131" s="8" t="s">
         <v>147</v>
       </c>
       <c r="B131" t="s">
@@ -6639,7 +6793,7 @@
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
+      <c r="A132" s="8" t="s">
         <v>148</v>
       </c>
       <c r="B132" t="s">
@@ -6665,7 +6819,7 @@
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
+      <c r="A133" s="8" t="s">
         <v>149</v>
       </c>
       <c r="B133" t="s">
@@ -6691,7 +6845,7 @@
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
+      <c r="A134" s="8" t="s">
         <v>150</v>
       </c>
       <c r="B134" t="s">
@@ -6717,7 +6871,7 @@
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
+      <c r="A135" s="8" t="s">
         <v>151</v>
       </c>
       <c r="B135" t="s">
@@ -6743,7 +6897,7 @@
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
+      <c r="A136" s="8" t="s">
         <v>152</v>
       </c>
       <c r="B136" t="s">
@@ -6769,7 +6923,7 @@
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
+      <c r="A137" s="8" t="s">
         <v>153</v>
       </c>
       <c r="B137" t="s">
@@ -6795,7 +6949,7 @@
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
+      <c r="A138" s="8" t="s">
         <v>154</v>
       </c>
       <c r="B138" t="s">
@@ -6821,7 +6975,7 @@
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
+      <c r="A139" s="8" t="s">
         <v>155</v>
       </c>
       <c r="B139" t="s">
@@ -6847,7 +7001,7 @@
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
+      <c r="A140" s="8" t="s">
         <v>156</v>
       </c>
       <c r="B140" t="s">
@@ -6873,7 +7027,7 @@
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
+      <c r="A141" s="8" t="s">
         <v>157</v>
       </c>
       <c r="B141" t="s">
@@ -6899,7 +7053,7 @@
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
+      <c r="A142" s="8" t="s">
         <v>158</v>
       </c>
       <c r="B142" t="s">
@@ -6925,7 +7079,7 @@
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
+      <c r="A143" s="8" t="s">
         <v>159</v>
       </c>
       <c r="B143" t="s">
@@ -6951,7 +7105,7 @@
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
+      <c r="A144" s="8" t="s">
         <v>160</v>
       </c>
       <c r="B144" t="s">
@@ -6977,7 +7131,7 @@
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
+      <c r="A145" s="8" t="s">
         <v>161</v>
       </c>
       <c r="B145" t="s">
@@ -7003,7 +7157,7 @@
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
+      <c r="A146" s="8" t="s">
         <v>162</v>
       </c>
       <c r="B146" t="s">
@@ -7029,7 +7183,7 @@
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
+      <c r="A147" s="8" t="s">
         <v>163</v>
       </c>
       <c r="B147" t="s">
@@ -7055,7 +7209,7 @@
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
+      <c r="A148" s="8" t="s">
         <v>164</v>
       </c>
       <c r="B148" t="s">
@@ -7081,7 +7235,7 @@
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
+      <c r="A149" s="8" t="s">
         <v>165</v>
       </c>
       <c r="B149" t="s">
@@ -7107,7 +7261,7 @@
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
+      <c r="A150" s="8" t="s">
         <v>166</v>
       </c>
       <c r="B150" t="s">
@@ -7133,7 +7287,7 @@
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
+      <c r="A151" s="8" t="s">
         <v>167</v>
       </c>
       <c r="B151" t="s">
@@ -7159,7 +7313,7 @@
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
+      <c r="A152" s="8" t="s">
         <v>168</v>
       </c>
       <c r="B152" t="s">
@@ -7185,7 +7339,7 @@
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
+      <c r="A153" s="8" t="s">
         <v>169</v>
       </c>
       <c r="B153" t="s">
@@ -7211,7 +7365,7 @@
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
+      <c r="A154" s="8" t="s">
         <v>170</v>
       </c>
       <c r="B154" t="s">
@@ -7237,7 +7391,7 @@
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
+      <c r="A155" s="8" t="s">
         <v>171</v>
       </c>
       <c r="B155" t="s">
@@ -7263,7 +7417,7 @@
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
+      <c r="A156" s="8" t="s">
         <v>172</v>
       </c>
       <c r="B156" t="s">
@@ -7289,7 +7443,7 @@
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
+      <c r="A157" s="8" t="s">
         <v>173</v>
       </c>
       <c r="B157" t="s">
@@ -7315,7 +7469,7 @@
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
+      <c r="A158" s="8" t="s">
         <v>174</v>
       </c>
       <c r="B158" t="s">
@@ -7341,7 +7495,7 @@
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
+      <c r="A159" s="8" t="s">
         <v>175</v>
       </c>
       <c r="B159" t="s">
@@ -7367,7 +7521,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
+      <c r="A160" s="8" t="s">
         <v>176</v>
       </c>
       <c r="B160" t="s">
@@ -7393,7 +7547,7 @@
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A161" t="s">
+      <c r="A161" s="8" t="s">
         <v>177</v>
       </c>
       <c r="B161" t="s">
@@ -7419,7 +7573,7 @@
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
+      <c r="A162" s="8" t="s">
         <v>178</v>
       </c>
       <c r="B162" t="s">
@@ -7445,7 +7599,7 @@
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
+      <c r="A163" s="8" t="s">
         <v>179</v>
       </c>
       <c r="B163" t="s">
@@ -7471,7 +7625,7 @@
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A164" t="s">
+      <c r="A164" s="8" t="s">
         <v>180</v>
       </c>
       <c r="B164" t="s">
@@ -7497,7 +7651,7 @@
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
+      <c r="A165" s="8" t="s">
         <v>181</v>
       </c>
       <c r="B165" t="s">
@@ -7523,7 +7677,7 @@
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A166" t="s">
+      <c r="A166" s="8" t="s">
         <v>182</v>
       </c>
       <c r="B166" t="s">
@@ -7549,7 +7703,7 @@
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A167" t="s">
+      <c r="A167" s="8" t="s">
         <v>183</v>
       </c>
       <c r="B167" t="s">
@@ -7575,7 +7729,7 @@
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A168" t="s">
+      <c r="A168" s="8" t="s">
         <v>184</v>
       </c>
       <c r="B168" t="s">
@@ -7601,7 +7755,7 @@
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A169" t="s">
+      <c r="A169" s="8" t="s">
         <v>185</v>
       </c>
       <c r="B169" t="s">
@@ -7627,7 +7781,7 @@
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A170" t="s">
+      <c r="A170" s="8" t="s">
         <v>186</v>
       </c>
       <c r="B170" t="s">
@@ -7653,7 +7807,7 @@
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A171" t="s">
+      <c r="A171" s="8" t="s">
         <v>187</v>
       </c>
       <c r="B171" t="s">
@@ -7679,7 +7833,7 @@
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A172" t="s">
+      <c r="A172" s="8" t="s">
         <v>188</v>
       </c>
       <c r="B172" t="s">
@@ -7705,7 +7859,7 @@
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A173" t="s">
+      <c r="A173" s="8" t="s">
         <v>189</v>
       </c>
       <c r="B173" t="s">
@@ -7731,7 +7885,7 @@
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
+      <c r="A174" s="8" t="s">
         <v>190</v>
       </c>
       <c r="B174" t="s">
@@ -7757,7 +7911,7 @@
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A175" t="s">
+      <c r="A175" s="8" t="s">
         <v>191</v>
       </c>
       <c r="B175" t="s">
@@ -7783,7 +7937,7 @@
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A176" t="s">
+      <c r="A176" s="8" t="s">
         <v>192</v>
       </c>
       <c r="B176" t="s">
@@ -7809,7 +7963,7 @@
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A177" t="s">
+      <c r="A177" s="8" t="s">
         <v>193</v>
       </c>
       <c r="B177" t="s">
@@ -7835,7 +7989,7 @@
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A178" t="s">
+      <c r="A178" s="8" t="s">
         <v>194</v>
       </c>
       <c r="B178" t="s">
@@ -7861,7 +8015,7 @@
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A179" t="s">
+      <c r="A179" s="8" t="s">
         <v>195</v>
       </c>
       <c r="B179" t="s">
@@ -7887,7 +8041,7 @@
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
+      <c r="A180" s="8" t="s">
         <v>196</v>
       </c>
       <c r="B180" t="s">
@@ -7913,7 +8067,7 @@
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
+      <c r="A181" s="8" t="s">
         <v>197</v>
       </c>
       <c r="B181" t="s">
@@ -7939,7 +8093,7 @@
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
+      <c r="A182" s="8" t="s">
         <v>198</v>
       </c>
       <c r="B182" t="s">
@@ -7965,7 +8119,7 @@
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A183" t="s">
+      <c r="A183" s="8" t="s">
         <v>199</v>
       </c>
       <c r="B183" t="s">
@@ -7991,7 +8145,7 @@
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A184" t="s">
+      <c r="A184" s="8" t="s">
         <v>200</v>
       </c>
       <c r="B184" t="s">
@@ -8017,7 +8171,7 @@
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A185" t="s">
+      <c r="A185" s="8" t="s">
         <v>201</v>
       </c>
       <c r="B185" t="s">
@@ -8043,7 +8197,7 @@
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A186" t="s">
+      <c r="A186" s="8" t="s">
         <v>202</v>
       </c>
       <c r="B186" t="s">
@@ -8069,7 +8223,7 @@
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A187" t="s">
+      <c r="A187" s="8" t="s">
         <v>203</v>
       </c>
       <c r="B187" t="s">
@@ -8095,7 +8249,7 @@
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A188" t="s">
+      <c r="A188" s="8" t="s">
         <v>204</v>
       </c>
       <c r="B188" t="s">
@@ -8121,7 +8275,7 @@
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A189" t="s">
+      <c r="A189" s="8" t="s">
         <v>205</v>
       </c>
       <c r="B189" t="s">
@@ -8147,7 +8301,7 @@
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A190" t="s">
+      <c r="A190" s="8" t="s">
         <v>206</v>
       </c>
       <c r="B190" t="s">
@@ -8173,7 +8327,7 @@
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A191" t="s">
+      <c r="A191" s="8" t="s">
         <v>207</v>
       </c>
       <c r="B191" t="s">
@@ -8199,7 +8353,7 @@
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A192" t="s">
+      <c r="A192" s="8" t="s">
         <v>208</v>
       </c>
       <c r="B192" t="s">
@@ -8225,7 +8379,7 @@
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A193" t="s">
+      <c r="A193" s="8" t="s">
         <v>209</v>
       </c>
       <c r="B193" t="s">
@@ -8251,7 +8405,7 @@
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A194" t="s">
+      <c r="A194" s="8" t="s">
         <v>210</v>
       </c>
       <c r="B194" t="s">
@@ -8277,7 +8431,7 @@
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A195" t="s">
+      <c r="A195" s="8" t="s">
         <v>211</v>
       </c>
       <c r="B195" t="s">
@@ -8303,7 +8457,7 @@
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A196" t="s">
+      <c r="A196" s="8" t="s">
         <v>212</v>
       </c>
       <c r="B196" t="s">
@@ -8329,7 +8483,7 @@
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A197" t="s">
+      <c r="A197" s="8" t="s">
         <v>213</v>
       </c>
       <c r="B197" t="s">
@@ -8355,7 +8509,7 @@
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A198" t="s">
+      <c r="A198" s="8" t="s">
         <v>214</v>
       </c>
       <c r="B198" t="s">
@@ -8381,7 +8535,7 @@
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A199" t="s">
+      <c r="A199" s="8" t="s">
         <v>215</v>
       </c>
       <c r="B199" t="s">
@@ -8407,7 +8561,7 @@
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A200" t="s">
+      <c r="A200" s="8" t="s">
         <v>216</v>
       </c>
       <c r="B200" t="s">
@@ -8433,7 +8587,7 @@
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A201" t="s">
+      <c r="A201" s="8" t="s">
         <v>217</v>
       </c>
       <c r="B201" t="s">
@@ -8459,7 +8613,7 @@
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A202" t="s">
+      <c r="A202" s="8" t="s">
         <v>218</v>
       </c>
       <c r="B202" t="s">
@@ -8485,7 +8639,7 @@
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A203" t="s">
+      <c r="A203" s="8" t="s">
         <v>219</v>
       </c>
       <c r="B203" t="s">
@@ -8511,7 +8665,7 @@
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A204" t="s">
+      <c r="A204" s="8" t="s">
         <v>220</v>
       </c>
       <c r="B204" t="s">
@@ -8537,7 +8691,7 @@
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A205" t="s">
+      <c r="A205" s="8" t="s">
         <v>221</v>
       </c>
       <c r="B205" t="s">
@@ -8563,7 +8717,7 @@
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A206" t="s">
+      <c r="A206" s="8" t="s">
         <v>222</v>
       </c>
       <c r="B206" t="s">
@@ -8589,7 +8743,7 @@
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A207" t="s">
+      <c r="A207" s="8" t="s">
         <v>223</v>
       </c>
       <c r="B207" t="s">
@@ -8615,7 +8769,7 @@
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A208" t="s">
+      <c r="A208" s="8" t="s">
         <v>224</v>
       </c>
       <c r="B208" t="s">
@@ -8641,7 +8795,7 @@
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A209" t="s">
+      <c r="A209" s="8" t="s">
         <v>225</v>
       </c>
       <c r="B209" t="s">
@@ -8667,7 +8821,7 @@
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A210" t="s">
+      <c r="A210" s="8" t="s">
         <v>226</v>
       </c>
       <c r="B210" t="s">
@@ -8693,7 +8847,7 @@
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A211" t="s">
+      <c r="A211" s="8" t="s">
         <v>227</v>
       </c>
       <c r="B211" t="s">
@@ -8719,7 +8873,7 @@
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A212" t="s">
+      <c r="A212" s="8" t="s">
         <v>228</v>
       </c>
       <c r="B212" t="s">
@@ -8745,7 +8899,7 @@
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A213" t="s">
+      <c r="A213" s="8" t="s">
         <v>229</v>
       </c>
       <c r="B213" t="s">
@@ -8771,7 +8925,7 @@
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A214" t="s">
+      <c r="A214" s="8" t="s">
         <v>230</v>
       </c>
       <c r="B214" t="s">
@@ -8797,7 +8951,7 @@
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A215" t="s">
+      <c r="A215" s="8" t="s">
         <v>231</v>
       </c>
       <c r="B215" t="s">
@@ -8823,7 +8977,7 @@
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A216" t="s">
+      <c r="A216" s="8" t="s">
         <v>232</v>
       </c>
       <c r="B216" t="s">
@@ -8849,7 +9003,7 @@
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A217" t="s">
+      <c r="A217" s="8" t="s">
         <v>233</v>
       </c>
       <c r="B217" t="s">
@@ -8875,7 +9029,7 @@
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A218" t="s">
+      <c r="A218" s="8" t="s">
         <v>234</v>
       </c>
       <c r="B218" t="s">
@@ -8901,7 +9055,7 @@
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A219" t="s">
+      <c r="A219" s="8" t="s">
         <v>235</v>
       </c>
       <c r="B219" t="s">
@@ -8927,7 +9081,7 @@
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A220" t="s">
+      <c r="A220" s="8" t="s">
         <v>236</v>
       </c>
       <c r="B220" t="s">
@@ -8953,7 +9107,7 @@
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A221" t="s">
+      <c r="A221" s="8" t="s">
         <v>237</v>
       </c>
       <c r="B221" t="s">
@@ -8979,7 +9133,7 @@
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A222" t="s">
+      <c r="A222" s="8" t="s">
         <v>238</v>
       </c>
       <c r="B222" t="s">
@@ -9005,7 +9159,7 @@
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A223" t="s">
+      <c r="A223" s="8" t="s">
         <v>239</v>
       </c>
       <c r="B223" t="s">
@@ -9031,7 +9185,7 @@
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A224" t="s">
+      <c r="A224" s="8" t="s">
         <v>240</v>
       </c>
       <c r="B224" t="s">
@@ -9057,7 +9211,7 @@
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A225" t="s">
+      <c r="A225" s="8" t="s">
         <v>241</v>
       </c>
       <c r="B225" t="s">
@@ -9083,7 +9237,7 @@
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A226" t="s">
+      <c r="A226" s="8" t="s">
         <v>242</v>
       </c>
       <c r="B226" t="s">
@@ -9109,7 +9263,7 @@
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A227" t="s">
+      <c r="A227" s="8" t="s">
         <v>243</v>
       </c>
       <c r="B227" t="s">
@@ -9135,7 +9289,7 @@
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A228" t="s">
+      <c r="A228" s="8" t="s">
         <v>244</v>
       </c>
       <c r="B228" t="s">
@@ -9161,7 +9315,7 @@
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A229" t="s">
+      <c r="A229" s="8" t="s">
         <v>245</v>
       </c>
       <c r="B229" t="s">
@@ -9187,7 +9341,7 @@
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A230" t="s">
+      <c r="A230" s="8" t="s">
         <v>246</v>
       </c>
       <c r="B230" t="s">
@@ -9213,7 +9367,7 @@
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A231" t="s">
+      <c r="A231" s="8" t="s">
         <v>247</v>
       </c>
       <c r="B231" t="s">
@@ -9239,7 +9393,7 @@
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A232" t="s">
+      <c r="A232" s="8" t="s">
         <v>248</v>
       </c>
       <c r="B232" t="s">
@@ -9265,7 +9419,7 @@
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A233" t="s">
+      <c r="A233" s="8" t="s">
         <v>249</v>
       </c>
       <c r="B233" t="s">
@@ -9291,7 +9445,7 @@
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A234" t="s">
+      <c r="A234" s="8" t="s">
         <v>250</v>
       </c>
       <c r="B234" t="s">
@@ -9317,7 +9471,7 @@
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A235" t="s">
+      <c r="A235" s="8" t="s">
         <v>251</v>
       </c>
       <c r="B235" t="s">
@@ -9343,7 +9497,7 @@
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A236" t="s">
+      <c r="A236" s="8" t="s">
         <v>252</v>
       </c>
       <c r="B236" t="s">
@@ -9369,7 +9523,7 @@
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A237" t="s">
+      <c r="A237" s="8" t="s">
         <v>253</v>
       </c>
       <c r="B237" t="s">
@@ -9395,7 +9549,7 @@
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A238" t="s">
+      <c r="A238" s="8" t="s">
         <v>254</v>
       </c>
       <c r="B238" t="s">
@@ -9421,7 +9575,7 @@
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A239" t="s">
+      <c r="A239" s="8" t="s">
         <v>255</v>
       </c>
       <c r="B239" t="s">
@@ -9447,7 +9601,7 @@
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A240" t="s">
+      <c r="A240" s="8" t="s">
         <v>256</v>
       </c>
       <c r="B240" t="s">
@@ -9473,7 +9627,7 @@
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A241" t="s">
+      <c r="A241" s="8" t="s">
         <v>257</v>
       </c>
       <c r="B241" t="s">
@@ -9499,7 +9653,7 @@
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A242" t="s">
+      <c r="A242" s="8" t="s">
         <v>258</v>
       </c>
       <c r="B242" t="s">
@@ -9525,7 +9679,7 @@
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A243" t="s">
+      <c r="A243" s="8" t="s">
         <v>259</v>
       </c>
       <c r="B243" t="s">
@@ -9551,7 +9705,7 @@
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A244" t="s">
+      <c r="A244" s="8" t="s">
         <v>260</v>
       </c>
       <c r="B244" t="s">
@@ -9577,7 +9731,7 @@
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A245" t="s">
+      <c r="A245" s="8" t="s">
         <v>261</v>
       </c>
       <c r="B245" t="s">
@@ -9603,7 +9757,7 @@
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A246" t="s">
+      <c r="A246" s="8" t="s">
         <v>262</v>
       </c>
       <c r="B246" t="s">
@@ -9629,7 +9783,7 @@
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A247" t="s">
+      <c r="A247" s="8" t="s">
         <v>263</v>
       </c>
       <c r="B247" t="s">
@@ -9655,7 +9809,7 @@
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A248" t="s">
+      <c r="A248" s="8" t="s">
         <v>264</v>
       </c>
       <c r="B248" t="s">
@@ -9681,7 +9835,7 @@
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A249" t="s">
+      <c r="A249" s="8" t="s">
         <v>265</v>
       </c>
       <c r="B249" t="s">
@@ -9707,7 +9861,7 @@
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A250" t="s">
+      <c r="A250" s="8" t="s">
         <v>266</v>
       </c>
       <c r="B250" t="s">
@@ -9733,7 +9887,7 @@
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A251" t="s">
+      <c r="A251" s="8" t="s">
         <v>267</v>
       </c>
       <c r="B251" t="s">
@@ -9759,7 +9913,7 @@
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A252" t="s">
+      <c r="A252" s="8" t="s">
         <v>268</v>
       </c>
       <c r="B252" t="s">
@@ -9785,7 +9939,7 @@
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A253" t="s">
+      <c r="A253" s="8" t="s">
         <v>269</v>
       </c>
       <c r="B253" t="s">
@@ -9811,7 +9965,7 @@
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A254" t="s">
+      <c r="A254" s="8" t="s">
         <v>270</v>
       </c>
       <c r="B254" t="s">
@@ -9837,7 +9991,7 @@
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A255" t="s">
+      <c r="A255" s="8" t="s">
         <v>271</v>
       </c>
       <c r="B255" t="s">
@@ -9863,7 +10017,7 @@
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A256" t="s">
+      <c r="A256" s="8" t="s">
         <v>272</v>
       </c>
       <c r="B256" t="s">
@@ -9889,7 +10043,7 @@
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A257" t="s">
+      <c r="A257" s="8" t="s">
         <v>273</v>
       </c>
       <c r="B257" t="s">
@@ -9915,7 +10069,7 @@
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A258" t="s">
+      <c r="A258" s="8" t="s">
         <v>274</v>
       </c>
       <c r="B258" t="s">
@@ -9941,7 +10095,7 @@
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A259" t="s">
+      <c r="A259" s="8" t="s">
         <v>275</v>
       </c>
       <c r="B259" t="s">
@@ -9967,7 +10121,7 @@
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A260" t="s">
+      <c r="A260" s="8" t="s">
         <v>276</v>
       </c>
       <c r="B260" t="s">
@@ -9993,7 +10147,7 @@
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A261" t="s">
+      <c r="A261" s="8" t="s">
         <v>277</v>
       </c>
       <c r="B261" t="s">
@@ -10019,7 +10173,7 @@
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A262" t="s">
+      <c r="A262" s="8" t="s">
         <v>278</v>
       </c>
       <c r="B262" t="s">
@@ -10045,7 +10199,7 @@
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A263" t="s">
+      <c r="A263" s="8" t="s">
         <v>279</v>
       </c>
       <c r="B263" t="s">
@@ -10071,7 +10225,7 @@
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A264" t="s">
+      <c r="A264" s="8" t="s">
         <v>280</v>
       </c>
       <c r="B264" t="s">
@@ -10097,7 +10251,7 @@
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A265" t="s">
+      <c r="A265" s="8" t="s">
         <v>281</v>
       </c>
       <c r="B265" t="s">
@@ -10123,7 +10277,7 @@
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A266" t="s">
+      <c r="A266" s="8" t="s">
         <v>282</v>
       </c>
       <c r="B266" t="s">
@@ -10149,7 +10303,7 @@
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A267" t="s">
+      <c r="A267" s="8" t="s">
         <v>283</v>
       </c>
       <c r="B267" t="s">
@@ -10175,7 +10329,7 @@
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A268" t="s">
+      <c r="A268" s="8" t="s">
         <v>284</v>
       </c>
       <c r="B268" t="s">
@@ -10201,7 +10355,7 @@
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A269" t="s">
+      <c r="A269" s="8" t="s">
         <v>285</v>
       </c>
       <c r="B269" t="s">
@@ -10227,7 +10381,7 @@
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A270" t="s">
+      <c r="A270" s="8" t="s">
         <v>286</v>
       </c>
       <c r="B270" t="s">
@@ -10253,7 +10407,7 @@
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A271" t="s">
+      <c r="A271" s="8" t="s">
         <v>287</v>
       </c>
       <c r="B271" t="s">
@@ -10279,7 +10433,7 @@
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A272" t="s">
+      <c r="A272" s="8" t="s">
         <v>287</v>
       </c>
       <c r="B272" t="s">
@@ -10305,7 +10459,7 @@
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A273" t="s">
+      <c r="A273" s="8" t="s">
         <v>287</v>
       </c>
       <c r="B273" t="s">
@@ -10331,7 +10485,7 @@
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A274" t="s">
+      <c r="A274" s="8" t="s">
         <v>288</v>
       </c>
       <c r="B274" t="s">
@@ -10357,7 +10511,7 @@
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A275" t="s">
+      <c r="A275" s="8" t="s">
         <v>289</v>
       </c>
       <c r="B275" t="s">
@@ -10383,7 +10537,7 @@
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A276" t="s">
+      <c r="A276" s="8" t="s">
         <v>290</v>
       </c>
       <c r="B276" t="s">
@@ -10409,7 +10563,7 @@
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A277" t="s">
+      <c r="A277" s="8" t="s">
         <v>291</v>
       </c>
       <c r="B277" t="s">
@@ -10435,7 +10589,7 @@
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A278" t="s">
+      <c r="A278" s="8" t="s">
         <v>292</v>
       </c>
       <c r="B278" t="s">
@@ -10461,7 +10615,7 @@
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A279" t="s">
+      <c r="A279" s="8" t="s">
         <v>293</v>
       </c>
       <c r="B279" t="s">
@@ -10487,7 +10641,7 @@
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A280" t="s">
+      <c r="A280" s="8" t="s">
         <v>294</v>
       </c>
       <c r="B280" t="s">
@@ -10513,7 +10667,7 @@
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A281" t="s">
+      <c r="A281" s="8" t="s">
         <v>295</v>
       </c>
       <c r="B281" t="s">
@@ -10539,7 +10693,7 @@
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A282" t="s">
+      <c r="A282" s="8" t="s">
         <v>296</v>
       </c>
       <c r="B282" t="s">
@@ -10565,7 +10719,7 @@
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A283" t="s">
+      <c r="A283" s="8" t="s">
         <v>297</v>
       </c>
       <c r="B283" t="s">
@@ -10591,7 +10745,7 @@
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A284" t="s">
+      <c r="A284" s="8" t="s">
         <v>298</v>
       </c>
       <c r="B284" t="s">
@@ -10617,7 +10771,7 @@
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A285" t="s">
+      <c r="A285" s="8" t="s">
         <v>299</v>
       </c>
       <c r="B285" t="s">
@@ -10643,7 +10797,7 @@
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A286" t="s">
+      <c r="A286" s="8" t="s">
         <v>300</v>
       </c>
       <c r="B286" t="s">
@@ -10669,7 +10823,7 @@
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A287" t="s">
+      <c r="A287" s="8" t="s">
         <v>301</v>
       </c>
       <c r="B287" t="s">
@@ -10695,7 +10849,7 @@
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A288" t="s">
+      <c r="A288" s="8" t="s">
         <v>302</v>
       </c>
       <c r="B288" t="s">
@@ -10721,7 +10875,7 @@
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A289" t="s">
+      <c r="A289" s="8" t="s">
         <v>303</v>
       </c>
       <c r="B289" t="s">
@@ -10747,7 +10901,7 @@
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A290" t="s">
+      <c r="A290" s="8" t="s">
         <v>304</v>
       </c>
       <c r="B290" t="s">
@@ -10773,7 +10927,7 @@
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A291" t="s">
+      <c r="A291" s="8" t="s">
         <v>305</v>
       </c>
       <c r="B291" t="s">
@@ -10799,7 +10953,7 @@
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A292" t="s">
+      <c r="A292" s="8" t="s">
         <v>306</v>
       </c>
       <c r="B292" t="s">
@@ -10825,7 +10979,7 @@
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A293" t="s">
+      <c r="A293" s="8" t="s">
         <v>307</v>
       </c>
       <c r="B293" t="s">
@@ -10851,7 +11005,7 @@
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A294" t="s">
+      <c r="A294" s="8" t="s">
         <v>308</v>
       </c>
       <c r="B294" t="s">
@@ -10877,7 +11031,7 @@
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A295" t="s">
+      <c r="A295" s="8" t="s">
         <v>309</v>
       </c>
       <c r="B295" t="s">
@@ -10903,7 +11057,7 @@
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A296" t="s">
+      <c r="A296" s="8" t="s">
         <v>310</v>
       </c>
       <c r="B296" t="s">
@@ -10929,7 +11083,7 @@
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A297" t="s">
+      <c r="A297" s="8" t="s">
         <v>311</v>
       </c>
       <c r="B297" t="s">
@@ -10955,7 +11109,7 @@
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A298" t="s">
+      <c r="A298" s="8" t="s">
         <v>312</v>
       </c>
       <c r="B298" t="s">
@@ -10981,7 +11135,7 @@
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A299" t="s">
+      <c r="A299" s="8" t="s">
         <v>313</v>
       </c>
       <c r="B299" t="s">
@@ -11007,7 +11161,7 @@
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A300" t="s">
+      <c r="A300" s="8" t="s">
         <v>314</v>
       </c>
       <c r="B300" t="s">
@@ -11033,7 +11187,7 @@
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A301" t="s">
+      <c r="A301" s="8" t="s">
         <v>315</v>
       </c>
       <c r="B301" t="s">
@@ -11059,7 +11213,7 @@
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A302" t="s">
+      <c r="A302" s="8" t="s">
         <v>316</v>
       </c>
       <c r="B302" t="s">
@@ -11085,7 +11239,7 @@
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A303" t="s">
+      <c r="A303" s="8" t="s">
         <v>317</v>
       </c>
       <c r="B303" t="s">
@@ -11111,7 +11265,7 @@
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A304" t="s">
+      <c r="A304" s="8" t="s">
         <v>317</v>
       </c>
       <c r="B304" t="s">
@@ -11137,7 +11291,7 @@
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A305" t="s">
+      <c r="A305" s="8" t="s">
         <v>318</v>
       </c>
       <c r="B305" t="s">
@@ -11163,7 +11317,7 @@
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A306" t="s">
+      <c r="A306" s="8" t="s">
         <v>319</v>
       </c>
       <c r="B306" t="s">
@@ -11189,7 +11343,7 @@
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A307" t="s">
+      <c r="A307" s="8" t="s">
         <v>320</v>
       </c>
       <c r="B307" t="s">
@@ -11215,7 +11369,7 @@
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A308" t="s">
+      <c r="A308" s="8" t="s">
         <v>321</v>
       </c>
       <c r="B308" t="s">
@@ -11241,7 +11395,7 @@
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A309" t="s">
+      <c r="A309" s="8" t="s">
         <v>322</v>
       </c>
       <c r="B309" t="s">
@@ -11267,7 +11421,7 @@
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A310" t="s">
+      <c r="A310" s="8" t="s">
         <v>323</v>
       </c>
       <c r="B310" t="s">
@@ -11293,7 +11447,7 @@
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A311" t="s">
+      <c r="A311" s="8" t="s">
         <v>324</v>
       </c>
       <c r="B311" t="s">
@@ -11319,7 +11473,7 @@
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A312" t="s">
+      <c r="A312" s="8" t="s">
         <v>325</v>
       </c>
       <c r="B312" t="s">
@@ -11345,7 +11499,7 @@
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A313" t="s">
+      <c r="A313" s="8" t="s">
         <v>326</v>
       </c>
       <c r="B313" t="s">
@@ -11371,7 +11525,7 @@
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A314" t="s">
+      <c r="A314" s="8" t="s">
         <v>327</v>
       </c>
       <c r="B314" t="s">
@@ -11397,7 +11551,7 @@
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A315" t="s">
+      <c r="A315" s="8" t="s">
         <v>328</v>
       </c>
       <c r="B315" t="s">
@@ -11423,7 +11577,7 @@
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A316" t="s">
+      <c r="A316" s="8" t="s">
         <v>329</v>
       </c>
       <c r="B316" t="s">
@@ -11449,7 +11603,7 @@
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A317" t="s">
+      <c r="A317" s="8" t="s">
         <v>330</v>
       </c>
       <c r="B317" t="s">
@@ -11475,7 +11629,7 @@
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A318" t="s">
+      <c r="A318" s="8" t="s">
         <v>331</v>
       </c>
       <c r="B318" t="s">
@@ -11501,7 +11655,7 @@
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A319" t="s">
+      <c r="A319" s="8" t="s">
         <v>332</v>
       </c>
       <c r="B319" t="s">
@@ -11527,7 +11681,7 @@
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A320" t="s">
+      <c r="A320" s="8" t="s">
         <v>333</v>
       </c>
       <c r="B320" t="s">
@@ -11553,7 +11707,7 @@
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A321" t="s">
+      <c r="A321" s="8" t="s">
         <v>334</v>
       </c>
       <c r="B321" t="s">
@@ -11579,7 +11733,7 @@
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A322" t="s">
+      <c r="A322" s="8" t="s">
         <v>335</v>
       </c>
       <c r="B322" t="s">
@@ -11605,7 +11759,7 @@
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A323" t="s">
+      <c r="A323" s="8" t="s">
         <v>336</v>
       </c>
       <c r="B323" t="s">
@@ -11631,7 +11785,7 @@
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A324" t="s">
+      <c r="A324" s="8" t="s">
         <v>337</v>
       </c>
       <c r="B324" t="s">
@@ -11657,7 +11811,7 @@
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A325" t="s">
+      <c r="A325" s="8" t="s">
         <v>338</v>
       </c>
       <c r="B325" t="s">
@@ -11683,7 +11837,7 @@
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A326" t="s">
+      <c r="A326" s="8" t="s">
         <v>339</v>
       </c>
       <c r="B326" t="s">
@@ -11709,7 +11863,7 @@
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A327" t="s">
+      <c r="A327" s="8" t="s">
         <v>340</v>
       </c>
       <c r="B327" t="s">
@@ -11735,7 +11889,7 @@
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A328" t="s">
+      <c r="A328" s="8" t="s">
         <v>341</v>
       </c>
       <c r="B328" t="s">
@@ -11761,7 +11915,7 @@
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A329" t="s">
+      <c r="A329" s="8" t="s">
         <v>342</v>
       </c>
       <c r="B329" t="s">
@@ -11787,7 +11941,7 @@
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A330" t="s">
+      <c r="A330" s="8" t="s">
         <v>343</v>
       </c>
       <c r="B330" t="s">
@@ -11813,7 +11967,7 @@
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A331" t="s">
+      <c r="A331" s="8" t="s">
         <v>344</v>
       </c>
       <c r="B331" t="s">
@@ -11839,7 +11993,7 @@
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A332" t="s">
+      <c r="A332" s="8" t="s">
         <v>345</v>
       </c>
       <c r="B332" t="s">
@@ -11865,7 +12019,7 @@
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A333" t="s">
+      <c r="A333" s="8" t="s">
         <v>346</v>
       </c>
       <c r="B333" t="s">
@@ -11891,7 +12045,7 @@
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A334" t="s">
+      <c r="A334" s="8" t="s">
         <v>347</v>
       </c>
       <c r="B334" t="s">
@@ -11917,7 +12071,7 @@
       </c>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A335" t="s">
+      <c r="A335" s="8" t="s">
         <v>348</v>
       </c>
       <c r="B335" t="s">
@@ -11943,7 +12097,7 @@
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A336" t="s">
+      <c r="A336" s="8" t="s">
         <v>349</v>
       </c>
       <c r="B336" t="s">
@@ -11969,7 +12123,7 @@
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A337" t="s">
+      <c r="A337" s="8" t="s">
         <v>350</v>
       </c>
       <c r="B337" t="s">
@@ -11995,7 +12149,7 @@
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A338" t="s">
+      <c r="A338" s="8" t="s">
         <v>351</v>
       </c>
       <c r="B338" t="s">
@@ -12021,7 +12175,7 @@
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A339" t="s">
+      <c r="A339" s="8" t="s">
         <v>352</v>
       </c>
       <c r="B339" t="s">
@@ -12047,7 +12201,7 @@
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A340" t="s">
+      <c r="A340" s="8" t="s">
         <v>353</v>
       </c>
       <c r="B340" t="s">
@@ -12073,7 +12227,7 @@
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A341" t="s">
+      <c r="A341" s="8" t="s">
         <v>354</v>
       </c>
       <c r="B341" t="s">
@@ -12099,7 +12253,7 @@
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A342" t="s">
+      <c r="A342" s="8" t="s">
         <v>355</v>
       </c>
       <c r="B342" t="s">
@@ -12125,7 +12279,7 @@
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A343" t="s">
+      <c r="A343" s="8" t="s">
         <v>356</v>
       </c>
       <c r="B343" t="s">
@@ -12151,7 +12305,7 @@
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A344" t="s">
+      <c r="A344" s="8" t="s">
         <v>357</v>
       </c>
       <c r="B344" t="s">
@@ -12177,7 +12331,7 @@
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A345" t="s">
+      <c r="A345" s="8" t="s">
         <v>358</v>
       </c>
       <c r="B345" t="s">
@@ -12203,7 +12357,7 @@
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A346" t="s">
+      <c r="A346" s="8" t="s">
         <v>359</v>
       </c>
       <c r="B346" t="s">
@@ -12229,7 +12383,7 @@
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A347" t="s">
+      <c r="A347" s="8" t="s">
         <v>360</v>
       </c>
       <c r="B347" t="s">
@@ -12255,7 +12409,7 @@
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A348" t="s">
+      <c r="A348" s="8" t="s">
         <v>361</v>
       </c>
       <c r="B348" t="s">
@@ -12281,7 +12435,7 @@
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A349" t="s">
+      <c r="A349" s="8" t="s">
         <v>362</v>
       </c>
       <c r="B349" t="s">
@@ -12307,7 +12461,7 @@
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A350" t="s">
+      <c r="A350" s="8" t="s">
         <v>363</v>
       </c>
       <c r="B350" t="s">
@@ -12333,7 +12487,7 @@
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A351" t="s">
+      <c r="A351" s="8" t="s">
         <v>364</v>
       </c>
       <c r="B351" t="s">
@@ -12359,7 +12513,7 @@
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A352" t="s">
+      <c r="A352" s="8" t="s">
         <v>365</v>
       </c>
       <c r="B352" t="s">
@@ -12385,7 +12539,7 @@
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A353" t="s">
+      <c r="A353" s="8" t="s">
         <v>366</v>
       </c>
       <c r="B353" t="s">
@@ -12411,7 +12565,7 @@
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A354" t="s">
+      <c r="A354" s="8" t="s">
         <v>367</v>
       </c>
       <c r="B354" t="s">
@@ -12437,7 +12591,7 @@
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A355" t="s">
+      <c r="A355" s="8" t="s">
         <v>368</v>
       </c>
       <c r="B355" t="s">
@@ -12463,7 +12617,7 @@
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A356" t="s">
+      <c r="A356" s="8" t="s">
         <v>369</v>
       </c>
       <c r="B356" t="s">
@@ -12489,7 +12643,7 @@
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A357" t="s">
+      <c r="A357" s="8" t="s">
         <v>370</v>
       </c>
       <c r="B357" t="s">
@@ -12515,7 +12669,7 @@
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A358" t="s">
+      <c r="A358" s="8" t="s">
         <v>371</v>
       </c>
       <c r="B358" t="s">
@@ -12541,7 +12695,7 @@
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A359" t="s">
+      <c r="A359" s="8" t="s">
         <v>372</v>
       </c>
       <c r="B359" t="s">
@@ -12567,7 +12721,7 @@
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A360" t="s">
+      <c r="A360" s="8" t="s">
         <v>373</v>
       </c>
       <c r="B360" t="s">
@@ -12593,7 +12747,7 @@
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A361" t="s">
+      <c r="A361" s="8" t="s">
         <v>374</v>
       </c>
       <c r="B361" t="s">
@@ -12619,7 +12773,7 @@
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A362" t="s">
+      <c r="A362" s="8" t="s">
         <v>375</v>
       </c>
       <c r="B362" t="s">
@@ -12645,7 +12799,7 @@
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A363" t="s">
+      <c r="A363" s="8" t="s">
         <v>376</v>
       </c>
       <c r="B363" t="s">
@@ -12671,7 +12825,7 @@
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A364" t="s">
+      <c r="A364" s="8" t="s">
         <v>377</v>
       </c>
       <c r="B364" t="s">
@@ -12697,7 +12851,7 @@
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A365" t="s">
+      <c r="A365" s="8" t="s">
         <v>378</v>
       </c>
       <c r="B365" t="s">
@@ -12723,7 +12877,7 @@
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A366" t="s">
+      <c r="A366" s="8" t="s">
         <v>379</v>
       </c>
       <c r="B366" t="s">
@@ -12749,7 +12903,7 @@
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A367" t="s">
+      <c r="A367" s="8" t="s">
         <v>380</v>
       </c>
       <c r="B367" t="s">
@@ -12775,7 +12929,7 @@
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A368" t="s">
+      <c r="A368" s="8" t="s">
         <v>381</v>
       </c>
       <c r="B368" t="s">
@@ -12801,7 +12955,7 @@
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A369" t="s">
+      <c r="A369" s="8" t="s">
         <v>382</v>
       </c>
       <c r="B369" t="s">
@@ -12827,7 +12981,7 @@
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A370" t="s">
+      <c r="A370" s="8" t="s">
         <v>383</v>
       </c>
       <c r="B370" t="s">
@@ -12853,7 +13007,7 @@
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A371" t="s">
+      <c r="A371" s="8" t="s">
         <v>384</v>
       </c>
       <c r="B371" t="s">
@@ -12879,7 +13033,7 @@
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A372" t="s">
+      <c r="A372" s="8" t="s">
         <v>385</v>
       </c>
       <c r="B372" t="s">
@@ -12905,7 +13059,7 @@
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A373" t="s">
+      <c r="A373" s="8" t="s">
         <v>386</v>
       </c>
       <c r="B373" t="s">
@@ -12931,7 +13085,7 @@
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A374" t="s">
+      <c r="A374" s="8" t="s">
         <v>387</v>
       </c>
       <c r="B374" t="s">
@@ -12957,7 +13111,7 @@
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A375" t="s">
+      <c r="A375" s="8" t="s">
         <v>388</v>
       </c>
       <c r="B375" t="s">
@@ -12983,7 +13137,7 @@
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A376" t="s">
+      <c r="A376" s="8" t="s">
         <v>389</v>
       </c>
       <c r="B376" t="s">
@@ -13009,7 +13163,7 @@
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A377" t="s">
+      <c r="A377" s="8" t="s">
         <v>390</v>
       </c>
       <c r="B377" t="s">
@@ -13035,7 +13189,7 @@
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A378" t="s">
+      <c r="A378" s="8" t="s">
         <v>391</v>
       </c>
       <c r="B378" t="s">
@@ -13061,7 +13215,7 @@
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A379" t="s">
+      <c r="A379" s="8" t="s">
         <v>392</v>
       </c>
       <c r="B379" t="s">
@@ -13087,7 +13241,7 @@
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A380" t="s">
+      <c r="A380" s="8" t="s">
         <v>393</v>
       </c>
       <c r="B380" t="s">
@@ -13113,7 +13267,7 @@
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A381" t="s">
+      <c r="A381" s="8" t="s">
         <v>394</v>
       </c>
       <c r="B381" t="s">
@@ -13139,7 +13293,7 @@
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A382" t="s">
+      <c r="A382" s="8" t="s">
         <v>395</v>
       </c>
       <c r="B382" t="s">
@@ -13165,7 +13319,7 @@
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A383" t="s">
+      <c r="A383" s="8" t="s">
         <v>396</v>
       </c>
       <c r="B383" t="s">
@@ -13191,7 +13345,7 @@
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A384" t="s">
+      <c r="A384" s="8" t="s">
         <v>397</v>
       </c>
       <c r="B384" t="s">
@@ -13217,7 +13371,7 @@
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A385" t="s">
+      <c r="A385" s="8" t="s">
         <v>398</v>
       </c>
       <c r="B385" t="s">
@@ -13243,7 +13397,7 @@
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A386" t="s">
+      <c r="A386" s="8" t="s">
         <v>399</v>
       </c>
       <c r="B386" t="s">
@@ -13269,7 +13423,7 @@
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A387" t="s">
+      <c r="A387" s="8" t="s">
         <v>400</v>
       </c>
       <c r="B387" t="s">
@@ -13295,7 +13449,7 @@
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A388" t="s">
+      <c r="A388" s="8" t="s">
         <v>401</v>
       </c>
       <c r="B388" t="s">
@@ -13321,7 +13475,7 @@
       </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A389" t="s">
+      <c r="A389" s="8" t="s">
         <v>402</v>
       </c>
       <c r="B389" t="s">
@@ -13347,7 +13501,7 @@
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A390" t="s">
+      <c r="A390" s="8" t="s">
         <v>403</v>
       </c>
       <c r="B390" t="s">
@@ -13373,7 +13527,7 @@
       </c>
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A391" t="s">
+      <c r="A391" s="8" t="s">
         <v>404</v>
       </c>
       <c r="B391" t="s">
@@ -13399,7 +13553,7 @@
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A392" t="s">
+      <c r="A392" s="8" t="s">
         <v>405</v>
       </c>
       <c r="B392" t="s">
@@ -13425,7 +13579,7 @@
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A393" t="s">
+      <c r="A393" s="8" t="s">
         <v>406</v>
       </c>
       <c r="B393" t="s">
@@ -13451,7 +13605,7 @@
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A394" t="s">
+      <c r="A394" s="8" t="s">
         <v>407</v>
       </c>
       <c r="B394" t="s">
@@ -13477,7 +13631,7 @@
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A395" t="s">
+      <c r="A395" s="8" t="s">
         <v>408</v>
       </c>
       <c r="B395" t="s">
@@ -13503,7 +13657,7 @@
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A396" t="s">
+      <c r="A396" s="8" t="s">
         <v>409</v>
       </c>
       <c r="B396" t="s">
@@ -13529,7 +13683,7 @@
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A397" t="s">
+      <c r="A397" s="8" t="s">
         <v>410</v>
       </c>
       <c r="B397" t="s">
@@ -13555,7 +13709,7 @@
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A398" t="s">
+      <c r="A398" s="8" t="s">
         <v>411</v>
       </c>
       <c r="B398" t="s">
@@ -13581,7 +13735,7 @@
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A399" t="s">
+      <c r="A399" s="8" t="s">
         <v>412</v>
       </c>
       <c r="B399" t="s">
@@ -13607,7 +13761,7 @@
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A400" t="s">
+      <c r="A400" s="8" t="s">
         <v>413</v>
       </c>
       <c r="B400" t="s">
@@ -13633,7 +13787,7 @@
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A401" t="s">
+      <c r="A401" s="8" t="s">
         <v>414</v>
       </c>
       <c r="B401" t="s">
@@ -13659,7 +13813,7 @@
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A402" t="s">
+      <c r="A402" s="8" t="s">
         <v>415</v>
       </c>
       <c r="B402" t="s">
@@ -13685,7 +13839,7 @@
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A403" t="s">
+      <c r="A403" s="8" t="s">
         <v>416</v>
       </c>
       <c r="B403" t="s">
@@ -13711,7 +13865,7 @@
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A404" t="s">
+      <c r="A404" s="8" t="s">
         <v>417</v>
       </c>
       <c r="B404" t="s">
@@ -13737,7 +13891,7 @@
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A405" t="s">
+      <c r="A405" s="8" t="s">
         <v>418</v>
       </c>
       <c r="B405" t="s">
@@ -13763,7 +13917,7 @@
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A406" t="s">
+      <c r="A406" s="8" t="s">
         <v>419</v>
       </c>
       <c r="B406" t="s">
@@ -13789,7 +13943,7 @@
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A407" t="s">
+      <c r="A407" s="8" t="s">
         <v>420</v>
       </c>
       <c r="B407" t="s">
@@ -13815,7 +13969,7 @@
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A408" t="s">
+      <c r="A408" s="8" t="s">
         <v>421</v>
       </c>
       <c r="B408" t="s">
@@ -13841,7 +13995,7 @@
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A409" t="s">
+      <c r="A409" s="8" t="s">
         <v>422</v>
       </c>
       <c r="B409" t="s">
@@ -13867,7 +14021,7 @@
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A410" t="s">
+      <c r="A410" s="8" t="s">
         <v>423</v>
       </c>
       <c r="B410" t="s">
@@ -13893,7 +14047,7 @@
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A411" t="s">
+      <c r="A411" s="8" t="s">
         <v>424</v>
       </c>
       <c r="B411" t="s">
@@ -13919,7 +14073,7 @@
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A412" t="s">
+      <c r="A412" s="8" t="s">
         <v>425</v>
       </c>
       <c r="B412" t="s">
@@ -13945,7 +14099,7 @@
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A413" t="s">
+      <c r="A413" s="8" t="s">
         <v>426</v>
       </c>
       <c r="B413" t="s">
@@ -13971,7 +14125,7 @@
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A414" t="s">
+      <c r="A414" s="8" t="s">
         <v>427</v>
       </c>
       <c r="B414" t="s">
@@ -13997,7 +14151,7 @@
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A415" t="s">
+      <c r="A415" s="8" t="s">
         <v>428</v>
       </c>
       <c r="B415" t="s">
@@ -14023,7 +14177,7 @@
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A416" t="s">
+      <c r="A416" s="8" t="s">
         <v>429</v>
       </c>
       <c r="B416" t="s">
@@ -14049,7 +14203,7 @@
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A417" t="s">
+      <c r="A417" s="8" t="s">
         <v>430</v>
       </c>
       <c r="B417" t="s">
@@ -14075,7 +14229,7 @@
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A418" t="s">
+      <c r="A418" s="8" t="s">
         <v>431</v>
       </c>
       <c r="B418" t="s">
@@ -14101,7 +14255,7 @@
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A419" t="s">
+      <c r="A419" s="8" t="s">
         <v>432</v>
       </c>
       <c r="B419" t="s">
@@ -14127,7 +14281,7 @@
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A420" t="s">
+      <c r="A420" s="8" t="s">
         <v>433</v>
       </c>
       <c r="B420" t="s">
@@ -14153,7 +14307,7 @@
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A421" t="s">
+      <c r="A421" s="8" t="s">
         <v>434</v>
       </c>
       <c r="B421" t="s">
@@ -14179,7 +14333,7 @@
       </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A422" t="s">
+      <c r="A422" s="8" t="s">
         <v>435</v>
       </c>
       <c r="B422" t="s">
@@ -14205,7 +14359,7 @@
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A423" t="s">
+      <c r="A423" s="8" t="s">
         <v>436</v>
       </c>
       <c r="B423" t="s">
@@ -14231,7 +14385,7 @@
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A424" t="s">
+      <c r="A424" s="8" t="s">
         <v>437</v>
       </c>
       <c r="B424" t="s">
@@ -14257,7 +14411,7 @@
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A425" t="s">
+      <c r="A425" s="8" t="s">
         <v>438</v>
       </c>
       <c r="B425" t="s">
@@ -14283,7 +14437,7 @@
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A426" t="s">
+      <c r="A426" s="8" t="s">
         <v>439</v>
       </c>
       <c r="B426" t="s">
@@ -14309,7 +14463,7 @@
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A427" t="s">
+      <c r="A427" s="8" t="s">
         <v>440</v>
       </c>
       <c r="B427" t="s">
@@ -14335,7 +14489,7 @@
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A428" t="s">
+      <c r="A428" s="8" t="s">
         <v>441</v>
       </c>
       <c r="B428" t="s">
@@ -14361,7 +14515,7 @@
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A429" t="s">
+      <c r="A429" s="8" t="s">
         <v>442</v>
       </c>
       <c r="B429" t="s">
@@ -14387,7 +14541,7 @@
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A430" t="s">
+      <c r="A430" s="8" t="s">
         <v>443</v>
       </c>
       <c r="B430" t="s">
@@ -14413,7 +14567,7 @@
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A431" t="s">
+      <c r="A431" s="8" t="s">
         <v>444</v>
       </c>
       <c r="B431" t="s">
@@ -14439,7 +14593,7 @@
       </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A432" t="s">
+      <c r="A432" s="8" t="s">
         <v>445</v>
       </c>
       <c r="B432" t="s">
@@ -14465,7 +14619,7 @@
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A433" t="s">
+      <c r="A433" s="8" t="s">
         <v>446</v>
       </c>
       <c r="B433" t="s">
@@ -14491,7 +14645,7 @@
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A434" t="s">
+      <c r="A434" s="8" t="s">
         <v>447</v>
       </c>
       <c r="B434" t="s">
@@ -14517,7 +14671,7 @@
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A435" t="s">
+      <c r="A435" s="8" t="s">
         <v>448</v>
       </c>
       <c r="B435" t="s">
@@ -14543,7 +14697,7 @@
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A436" t="s">
+      <c r="A436" s="8" t="s">
         <v>449</v>
       </c>
       <c r="B436" t="s">
@@ -14569,7 +14723,7 @@
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A437" t="s">
+      <c r="A437" s="8" t="s">
         <v>450</v>
       </c>
       <c r="B437" t="s">
@@ -14595,7 +14749,7 @@
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A438" t="s">
+      <c r="A438" s="8" t="s">
         <v>451</v>
       </c>
       <c r="B438" t="s">
@@ -14621,7 +14775,7 @@
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A439" t="s">
+      <c r="A439" s="8" t="s">
         <v>452</v>
       </c>
       <c r="B439" t="s">
@@ -14647,7 +14801,7 @@
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A440" t="s">
+      <c r="A440" s="8" t="s">
         <v>453</v>
       </c>
       <c r="B440" t="s">
@@ -14673,7 +14827,7 @@
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A441" t="s">
+      <c r="A441" s="8" t="s">
         <v>454</v>
       </c>
       <c r="B441" t="s">
@@ -14699,7 +14853,7 @@
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A442" t="s">
+      <c r="A442" s="8" t="s">
         <v>455</v>
       </c>
       <c r="B442" t="s">
@@ -14725,7 +14879,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H442" xr:uid="{DC658449-BA0D-FB4C-A8FC-4A535294D741}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>